--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI259"/>
+  <dimension ref="A1:AI260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26795,6 +26795,109 @@
       <c r="AH259" t="inlineStr"/>
       <c r="AI259" t="inlineStr"/>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>561.38</v>
+      </c>
+      <c r="C260" t="n">
+        <v>578</v>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="n">
+        <v>512</v>
+      </c>
+      <c r="F260" t="n">
+        <v>855</v>
+      </c>
+      <c r="G260" t="n">
+        <v>500.75</v>
+      </c>
+      <c r="H260" t="n">
+        <v>553</v>
+      </c>
+      <c r="I260" t="n">
+        <v>445.75</v>
+      </c>
+      <c r="J260" t="n">
+        <v>485</v>
+      </c>
+      <c r="K260" t="n">
+        <v>880</v>
+      </c>
+      <c r="L260" t="n">
+        <v>570</v>
+      </c>
+      <c r="M260" t="n">
+        <v>910</v>
+      </c>
+      <c r="N260" t="n">
+        <v>578</v>
+      </c>
+      <c r="O260" t="n">
+        <v>520</v>
+      </c>
+      <c r="P260" t="n">
+        <v>825</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>584</v>
+      </c>
+      <c r="R260" t="n">
+        <v>533</v>
+      </c>
+      <c r="S260" t="n">
+        <v>866.5</v>
+      </c>
+      <c r="T260" t="n">
+        <v>605.5</v>
+      </c>
+      <c r="U260" t="n">
+        <v>548</v>
+      </c>
+      <c r="V260" t="n">
+        <v>893.25</v>
+      </c>
+      <c r="W260" t="n">
+        <v>578</v>
+      </c>
+      <c r="X260" t="n">
+        <v>522</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>838</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>565</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>490</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>941</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>588</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>453</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>852</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>564.65</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>575</v>
+      </c>
+      <c r="AH260" t="inlineStr"/>
+      <c r="AI260" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI260"/>
+  <dimension ref="A1:AI261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26898,6 +26898,109 @@
       <c r="AH260" t="inlineStr"/>
       <c r="AI260" t="inlineStr"/>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>600.04</v>
+      </c>
+      <c r="C261" t="n">
+        <v>628</v>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="n">
+        <v>550</v>
+      </c>
+      <c r="F261" t="n">
+        <v>945</v>
+      </c>
+      <c r="G261" t="n">
+        <v>546.75</v>
+      </c>
+      <c r="H261" t="n">
+        <v>585</v>
+      </c>
+      <c r="I261" t="n">
+        <v>511.25</v>
+      </c>
+      <c r="J261" t="n">
+        <v>540</v>
+      </c>
+      <c r="K261" t="n">
+        <v>990</v>
+      </c>
+      <c r="L261" t="n">
+        <v>595</v>
+      </c>
+      <c r="M261" t="n">
+        <v>855</v>
+      </c>
+      <c r="N261" t="n">
+        <v>620</v>
+      </c>
+      <c r="O261" t="n">
+        <v>557</v>
+      </c>
+      <c r="P261" t="n">
+        <v>905</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>625</v>
+      </c>
+      <c r="R261" t="n">
+        <v>556</v>
+      </c>
+      <c r="S261" t="n">
+        <v>967.5</v>
+      </c>
+      <c r="T261" t="n">
+        <v>690</v>
+      </c>
+      <c r="U261" t="n">
+        <v>585</v>
+      </c>
+      <c r="V261" t="n">
+        <v>994.75</v>
+      </c>
+      <c r="W261" t="n">
+        <v>620</v>
+      </c>
+      <c r="X261" t="n">
+        <v>559</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>915</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>605</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>618</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>489</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>977</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>654.9400000000001</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>665</v>
+      </c>
+      <c r="AH261" t="inlineStr"/>
+      <c r="AI261" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI261"/>
+  <dimension ref="A1:AI262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27001,6 +27001,109 @@
       <c r="AH261" t="inlineStr"/>
       <c r="AI261" t="inlineStr"/>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>615.65</v>
+      </c>
+      <c r="C262" t="n">
+        <v>655</v>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="n">
+        <v>592</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1085</v>
+      </c>
+      <c r="G262" t="n">
+        <v>518</v>
+      </c>
+      <c r="H262" t="n">
+        <v>600</v>
+      </c>
+      <c r="I262" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="J262" t="n">
+        <v>560</v>
+      </c>
+      <c r="K262" t="n">
+        <v>1005</v>
+      </c>
+      <c r="L262" t="n">
+        <v>599</v>
+      </c>
+      <c r="M262" t="n">
+        <v>858</v>
+      </c>
+      <c r="N262" t="n">
+        <v>640</v>
+      </c>
+      <c r="O262" t="n">
+        <v>612</v>
+      </c>
+      <c r="P262" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>673</v>
+      </c>
+      <c r="R262" t="n">
+        <v>625</v>
+      </c>
+      <c r="S262" t="n">
+        <v>1085.5</v>
+      </c>
+      <c r="T262" t="n">
+        <v>720</v>
+      </c>
+      <c r="U262" t="n">
+        <v>635</v>
+      </c>
+      <c r="V262" t="n">
+        <v>1138</v>
+      </c>
+      <c r="W262" t="n">
+        <v>640</v>
+      </c>
+      <c r="X262" t="n">
+        <v>614</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>1060</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>650</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>565</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>1114</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>641</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>512</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>967</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>660.12</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>670</v>
+      </c>
+      <c r="AH262" t="inlineStr"/>
+      <c r="AI262" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI262"/>
+  <dimension ref="A1:AI263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27104,6 +27104,109 @@
       <c r="AH262" t="inlineStr"/>
       <c r="AI262" t="inlineStr"/>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>643.16</v>
+      </c>
+      <c r="C263" t="n">
+        <v>693</v>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="n">
+        <v>627</v>
+      </c>
+      <c r="F263" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G263" t="n">
+        <v>550.5</v>
+      </c>
+      <c r="H263" t="n">
+        <v>610</v>
+      </c>
+      <c r="I263" t="n">
+        <v>513</v>
+      </c>
+      <c r="J263" t="n">
+        <v>576</v>
+      </c>
+      <c r="K263" t="n">
+        <v>1052</v>
+      </c>
+      <c r="L263" t="n">
+        <v>670</v>
+      </c>
+      <c r="M263" t="n">
+        <v>845</v>
+      </c>
+      <c r="N263" t="n">
+        <v>690</v>
+      </c>
+      <c r="O263" t="n">
+        <v>643</v>
+      </c>
+      <c r="P263" t="n">
+        <v>1140</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>693</v>
+      </c>
+      <c r="R263" t="n">
+        <v>650</v>
+      </c>
+      <c r="S263" t="n">
+        <v>1150</v>
+      </c>
+      <c r="T263" t="n">
+        <v>780</v>
+      </c>
+      <c r="U263" t="n">
+        <v>695</v>
+      </c>
+      <c r="V263" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="W263" t="n">
+        <v>690</v>
+      </c>
+      <c r="X263" t="n">
+        <v>645</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>650</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>580</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>1160</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>667</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>547</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1052</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>685</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>700</v>
+      </c>
+      <c r="AH263" t="inlineStr"/>
+      <c r="AI263" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI263"/>
+  <dimension ref="A1:AI264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27207,6 +27207,109 @@
       <c r="AH263" t="inlineStr"/>
       <c r="AI263" t="inlineStr"/>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>739.09</v>
+      </c>
+      <c r="C264" t="n">
+        <v>825</v>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="n">
+        <v>700</v>
+      </c>
+      <c r="F264" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G264" t="n">
+        <v>601</v>
+      </c>
+      <c r="H264" t="n">
+        <v>655</v>
+      </c>
+      <c r="I264" t="n">
+        <v>590.25</v>
+      </c>
+      <c r="J264" t="n">
+        <v>610</v>
+      </c>
+      <c r="K264" t="n">
+        <v>1085</v>
+      </c>
+      <c r="L264" t="n">
+        <v>695</v>
+      </c>
+      <c r="M264" t="n">
+        <v>850</v>
+      </c>
+      <c r="N264" t="n">
+        <v>825</v>
+      </c>
+      <c r="O264" t="n">
+        <v>740</v>
+      </c>
+      <c r="P264" t="n">
+        <v>1260</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>810</v>
+      </c>
+      <c r="R264" t="n">
+        <v>710</v>
+      </c>
+      <c r="S264" t="n">
+        <v>1200</v>
+      </c>
+      <c r="T264" t="n">
+        <v>970</v>
+      </c>
+      <c r="U264" t="n">
+        <v>820</v>
+      </c>
+      <c r="V264" t="n">
+        <v>1250</v>
+      </c>
+      <c r="W264" t="n">
+        <v>825</v>
+      </c>
+      <c r="X264" t="n">
+        <v>742</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>685</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>615</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>737</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>617</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>1117</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>759.73</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>790</v>
+      </c>
+      <c r="AH264" t="inlineStr"/>
+      <c r="AI264" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI264"/>
+  <dimension ref="A1:AI265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27310,6 +27310,109 @@
       <c r="AH264" t="inlineStr"/>
       <c r="AI264" t="inlineStr"/>
     </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>990.15</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F265" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G265" t="n">
+        <v>662.5</v>
+      </c>
+      <c r="H265" t="n">
+        <v>810</v>
+      </c>
+      <c r="I265" t="n">
+        <v>644.25</v>
+      </c>
+      <c r="J265" t="n">
+        <v>780</v>
+      </c>
+      <c r="K265" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L265" t="n">
+        <v>1150</v>
+      </c>
+      <c r="M265" t="n">
+        <v>1420</v>
+      </c>
+      <c r="N265" t="n">
+        <v>1125</v>
+      </c>
+      <c r="O265" t="n">
+        <v>995</v>
+      </c>
+      <c r="P265" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>1150</v>
+      </c>
+      <c r="R265" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S265" t="n">
+        <v>1457.5</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1350</v>
+      </c>
+      <c r="U265" t="n">
+        <v>1187</v>
+      </c>
+      <c r="V265" t="n">
+        <v>1605</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1125</v>
+      </c>
+      <c r="X265" t="n">
+        <v>997</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1460</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>850</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>740</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>1290</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>832</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>657</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1252</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>975.13</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AH265" t="inlineStr"/>
+      <c r="AI265" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI265"/>
+  <dimension ref="A1:AI266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27413,6 +27413,109 @@
       <c r="AH265" t="inlineStr"/>
       <c r="AI265" t="inlineStr"/>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>835.92</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="n">
+        <v>910</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G266" t="n">
+        <v>613.75</v>
+      </c>
+      <c r="H266" t="n">
+        <v>770</v>
+      </c>
+      <c r="I266" t="n">
+        <v>575.5</v>
+      </c>
+      <c r="J266" t="n">
+        <v>720</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1035</v>
+      </c>
+      <c r="M266" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N266" t="n">
+        <v>1110</v>
+      </c>
+      <c r="O266" t="n">
+        <v>940</v>
+      </c>
+      <c r="P266" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>1040</v>
+      </c>
+      <c r="R266" t="n">
+        <v>900</v>
+      </c>
+      <c r="S266" t="n">
+        <v>1312</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1290</v>
+      </c>
+      <c r="U266" t="n">
+        <v>1010</v>
+      </c>
+      <c r="V266" t="n">
+        <v>1600</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1110</v>
+      </c>
+      <c r="X266" t="n">
+        <v>942</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1510</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>780</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>710</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>1260</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>767</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>607</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1087</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>975.15</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AH266" t="inlineStr"/>
+      <c r="AI266" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI266"/>
+  <dimension ref="A1:AI267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27516,6 +27516,109 @@
       <c r="AH266" t="inlineStr"/>
       <c r="AI266" t="inlineStr"/>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>841.96</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="n">
+        <v>890</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1720</v>
+      </c>
+      <c r="G267" t="n">
+        <v>645.25</v>
+      </c>
+      <c r="H267" t="n">
+        <v>780</v>
+      </c>
+      <c r="I267" t="n">
+        <v>595.25</v>
+      </c>
+      <c r="J267" t="n">
+        <v>735</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L267" t="n">
+        <v>1038</v>
+      </c>
+      <c r="M267" t="n">
+        <v>1830</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1070</v>
+      </c>
+      <c r="O267" t="n">
+        <v>820</v>
+      </c>
+      <c r="P267" t="n">
+        <v>1525</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>1020</v>
+      </c>
+      <c r="R267" t="n">
+        <v>882.75</v>
+      </c>
+      <c r="S267" t="n">
+        <v>1366.5</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1410</v>
+      </c>
+      <c r="U267" t="n">
+        <v>1050</v>
+      </c>
+      <c r="V267" t="n">
+        <v>1659.25</v>
+      </c>
+      <c r="W267" t="n">
+        <v>1070</v>
+      </c>
+      <c r="X267" t="n">
+        <v>822</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1535</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>790</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>1240</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>822</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>622</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>990.12</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1035</v>
+      </c>
+      <c r="AH267" t="inlineStr"/>
+      <c r="AI267" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI267"/>
+  <dimension ref="A1:AI268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27619,6 +27619,109 @@
       <c r="AH267" t="inlineStr"/>
       <c r="AI267" t="inlineStr"/>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>932.53</v>
+      </c>
+      <c r="C268" t="n">
+        <v>1138</v>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="n">
+        <v>970</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1995.5</v>
+      </c>
+      <c r="G268" t="n">
+        <v>681</v>
+      </c>
+      <c r="H268" t="n">
+        <v>785</v>
+      </c>
+      <c r="I268" t="n">
+        <v>628.25</v>
+      </c>
+      <c r="J268" t="n">
+        <v>745</v>
+      </c>
+      <c r="K268" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L268" t="n">
+        <v>1090</v>
+      </c>
+      <c r="M268" t="n">
+        <v>1772</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1125</v>
+      </c>
+      <c r="O268" t="n">
+        <v>925</v>
+      </c>
+      <c r="P268" t="n">
+        <v>1680</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>1111</v>
+      </c>
+      <c r="R268" t="n">
+        <v>940</v>
+      </c>
+      <c r="S268" t="n">
+        <v>1630.25</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1498.75</v>
+      </c>
+      <c r="U268" t="n">
+        <v>1200</v>
+      </c>
+      <c r="V268" t="n">
+        <v>1931</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1125</v>
+      </c>
+      <c r="X268" t="n">
+        <v>927</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1690</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>830</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>790</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>857</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>652</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1092</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>1080.9</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>1126</v>
+      </c>
+      <c r="AH268" t="inlineStr"/>
+      <c r="AI268" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI268"/>
+  <dimension ref="A1:AI269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27722,6 +27722,109 @@
       <c r="AH268" t="inlineStr"/>
       <c r="AI268" t="inlineStr"/>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>931.01</v>
+      </c>
+      <c r="C269" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="n">
+        <v>870</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G269" t="n">
+        <v>669</v>
+      </c>
+      <c r="H269" t="n">
+        <v>800</v>
+      </c>
+      <c r="I269" t="n">
+        <v>623.5</v>
+      </c>
+      <c r="J269" t="n">
+        <v>748</v>
+      </c>
+      <c r="K269" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1169</v>
+      </c>
+      <c r="M269" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N269" t="n">
+        <v>1060</v>
+      </c>
+      <c r="O269" t="n">
+        <v>838</v>
+      </c>
+      <c r="P269" t="n">
+        <v>1580</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>1065</v>
+      </c>
+      <c r="R269" t="n">
+        <v>899</v>
+      </c>
+      <c r="S269" t="n">
+        <v>1586.25</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1450</v>
+      </c>
+      <c r="U269" t="n">
+        <v>1170</v>
+      </c>
+      <c r="V269" t="n">
+        <v>1788</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1060</v>
+      </c>
+      <c r="X269" t="n">
+        <v>840</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1590</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>850</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>780</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>1310</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>887</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>653</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>1122</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>1074.75</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>1120</v>
+      </c>
+      <c r="AH269" t="inlineStr"/>
+      <c r="AI269" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI269"/>
+  <dimension ref="A1:AI270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27825,6 +27825,109 @@
       <c r="AH269" t="inlineStr"/>
       <c r="AI269" t="inlineStr"/>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>934.9</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="n">
+        <v>840</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G270" t="n">
+        <v>671.75</v>
+      </c>
+      <c r="H270" t="n">
+        <v>780</v>
+      </c>
+      <c r="I270" t="n">
+        <v>607.25</v>
+      </c>
+      <c r="J270" t="n">
+        <v>735</v>
+      </c>
+      <c r="K270" t="n">
+        <v>1160</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1168</v>
+      </c>
+      <c r="M270" t="n">
+        <v>1701</v>
+      </c>
+      <c r="N270" t="n">
+        <v>1060</v>
+      </c>
+      <c r="O270" t="n">
+        <v>878</v>
+      </c>
+      <c r="P270" t="n">
+        <v>1580</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>1055</v>
+      </c>
+      <c r="R270" t="n">
+        <v>895</v>
+      </c>
+      <c r="S270" t="n">
+        <v>1530</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1330</v>
+      </c>
+      <c r="U270" t="n">
+        <v>1200</v>
+      </c>
+      <c r="V270" t="n">
+        <v>1709</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1060</v>
+      </c>
+      <c r="X270" t="n">
+        <v>880</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1590</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>847</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>784</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>1385</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>929</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>702</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>1279</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>1035</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AH270" t="inlineStr"/>
+      <c r="AI270" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI270"/>
+  <dimension ref="A1:AI271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27928,6 +27928,109 @@
       <c r="AH270" t="inlineStr"/>
       <c r="AI270" t="inlineStr"/>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>923.78</v>
+      </c>
+      <c r="C271" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="n">
+        <v>795</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G271" t="n">
+        <v>667.5</v>
+      </c>
+      <c r="H271" t="n">
+        <v>775</v>
+      </c>
+      <c r="I271" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="J271" t="n">
+        <v>715</v>
+      </c>
+      <c r="K271" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1115</v>
+      </c>
+      <c r="M271" t="n">
+        <v>1702</v>
+      </c>
+      <c r="N271" t="n">
+        <v>1030</v>
+      </c>
+      <c r="O271" t="n">
+        <v>853</v>
+      </c>
+      <c r="P271" t="n">
+        <v>1580</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>1030</v>
+      </c>
+      <c r="R271" t="n">
+        <v>901.5</v>
+      </c>
+      <c r="S271" t="n">
+        <v>1500</v>
+      </c>
+      <c r="T271" t="n">
+        <v>1290</v>
+      </c>
+      <c r="U271" t="n">
+        <v>1190</v>
+      </c>
+      <c r="V271" t="n">
+        <v>1735.75</v>
+      </c>
+      <c r="W271" t="n">
+        <v>1030</v>
+      </c>
+      <c r="X271" t="n">
+        <v>855</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1590</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>843</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>764</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>1390</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>911</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>694</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>1299</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>995.08</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>1040</v>
+      </c>
+      <c r="AH271" t="inlineStr"/>
+      <c r="AI271" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI271"/>
+  <dimension ref="A1:AI272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28031,6 +28031,109 @@
       <c r="AH271" t="inlineStr"/>
       <c r="AI271" t="inlineStr"/>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>936.33</v>
+      </c>
+      <c r="C272" t="n">
+        <v>990</v>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="n">
+        <v>775</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G272" t="n">
+        <v>695.25</v>
+      </c>
+      <c r="H272" t="n">
+        <v>805</v>
+      </c>
+      <c r="I272" t="n">
+        <v>647.25</v>
+      </c>
+      <c r="J272" t="n">
+        <v>745</v>
+      </c>
+      <c r="K272" t="n">
+        <v>1215</v>
+      </c>
+      <c r="L272" t="n">
+        <v>1055</v>
+      </c>
+      <c r="M272" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N272" t="n">
+        <v>1015</v>
+      </c>
+      <c r="O272" t="n">
+        <v>829</v>
+      </c>
+      <c r="P272" t="n">
+        <v>1549</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>1030</v>
+      </c>
+      <c r="R272" t="n">
+        <v>840</v>
+      </c>
+      <c r="S272" t="n">
+        <v>1465</v>
+      </c>
+      <c r="T272" t="n">
+        <v>1290</v>
+      </c>
+      <c r="U272" t="n">
+        <v>1185</v>
+      </c>
+      <c r="V272" t="n">
+        <v>1685.75</v>
+      </c>
+      <c r="W272" t="n">
+        <v>1015</v>
+      </c>
+      <c r="X272" t="n">
+        <v>831</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1559</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>845</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>790</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>1385</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>926</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>710</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>1369</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>980.04</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>1025</v>
+      </c>
+      <c r="AH272" t="inlineStr"/>
+      <c r="AI272" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI272"/>
+  <dimension ref="A1:AI273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28134,6 +28134,109 @@
       <c r="AH272" t="inlineStr"/>
       <c r="AI272" t="inlineStr"/>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1003.48</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="n">
+        <v>815</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G273" t="n">
+        <v>728.25</v>
+      </c>
+      <c r="H273" t="n">
+        <v>840</v>
+      </c>
+      <c r="I273" t="n">
+        <v>647.5</v>
+      </c>
+      <c r="J273" t="n">
+        <v>765</v>
+      </c>
+      <c r="K273" t="n">
+        <v>1340</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1105</v>
+      </c>
+      <c r="M273" t="n">
+        <v>1501</v>
+      </c>
+      <c r="N273" t="n">
+        <v>1060</v>
+      </c>
+      <c r="O273" t="n">
+        <v>850</v>
+      </c>
+      <c r="P273" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>1097</v>
+      </c>
+      <c r="R273" t="n">
+        <v>845</v>
+      </c>
+      <c r="S273" t="n">
+        <v>1600</v>
+      </c>
+      <c r="T273" t="n">
+        <v>1240</v>
+      </c>
+      <c r="U273" t="n">
+        <v>1140</v>
+      </c>
+      <c r="V273" t="n">
+        <v>1911</v>
+      </c>
+      <c r="W273" t="n">
+        <v>1060</v>
+      </c>
+      <c r="X273" t="n">
+        <v>852</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>1680</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>865</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>795</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>1480</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>772</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>1382</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>1065.1</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>1110</v>
+      </c>
+      <c r="AH273" t="inlineStr"/>
+      <c r="AI273" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI273"/>
+  <dimension ref="A1:AI274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28237,6 +28237,109 @@
       <c r="AH273" t="inlineStr"/>
       <c r="AI273" t="inlineStr"/>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>929.09</v>
+      </c>
+      <c r="C274" t="n">
+        <v>957</v>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="n">
+        <v>765</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1875.75</v>
+      </c>
+      <c r="G274" t="n">
+        <v>709.75</v>
+      </c>
+      <c r="H274" t="n">
+        <v>830</v>
+      </c>
+      <c r="I274" t="n">
+        <v>666.75</v>
+      </c>
+      <c r="J274" t="n">
+        <v>770</v>
+      </c>
+      <c r="K274" t="n">
+        <v>1380</v>
+      </c>
+      <c r="L274" t="n">
+        <v>1080</v>
+      </c>
+      <c r="M274" t="n">
+        <v>1575</v>
+      </c>
+      <c r="N274" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O274" t="n">
+        <v>795</v>
+      </c>
+      <c r="P274" t="n">
+        <v>1675</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>1030</v>
+      </c>
+      <c r="R274" t="n">
+        <v>800</v>
+      </c>
+      <c r="S274" t="n">
+        <v>1560</v>
+      </c>
+      <c r="T274" t="n">
+        <v>1150</v>
+      </c>
+      <c r="U274" t="n">
+        <v>1050</v>
+      </c>
+      <c r="V274" t="n">
+        <v>1836.5</v>
+      </c>
+      <c r="W274" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X274" t="n">
+        <v>797</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>1685</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>835</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>760</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>960</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>785</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>1422</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>990.28</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>1035</v>
+      </c>
+      <c r="AH274" t="inlineStr"/>
+      <c r="AI274" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI274"/>
+  <dimension ref="A1:AI275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28340,6 +28340,109 @@
       <c r="AH274" t="inlineStr"/>
       <c r="AI274" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>951.5599999999999</v>
+      </c>
+      <c r="C275" t="n">
+        <v>975</v>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="n">
+        <v>795</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1947.75</v>
+      </c>
+      <c r="G275" t="n">
+        <v>674</v>
+      </c>
+      <c r="H275" t="n">
+        <v>800</v>
+      </c>
+      <c r="I275" t="n">
+        <v>632</v>
+      </c>
+      <c r="J275" t="n">
+        <v>750</v>
+      </c>
+      <c r="K275" t="n">
+        <v>1370</v>
+      </c>
+      <c r="L275" t="n">
+        <v>1020</v>
+      </c>
+      <c r="M275" t="n">
+        <v>1490</v>
+      </c>
+      <c r="N275" t="n">
+        <v>990</v>
+      </c>
+      <c r="O275" t="n">
+        <v>835</v>
+      </c>
+      <c r="P275" t="n">
+        <v>1700</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>1025</v>
+      </c>
+      <c r="R275" t="n">
+        <v>862</v>
+      </c>
+      <c r="S275" t="n">
+        <v>1580</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1150</v>
+      </c>
+      <c r="U275" t="n">
+        <v>1051</v>
+      </c>
+      <c r="V275" t="n">
+        <v>1898.25</v>
+      </c>
+      <c r="W275" t="n">
+        <v>990</v>
+      </c>
+      <c r="X275" t="n">
+        <v>837</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>1710</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>840</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>755</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>937</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>752</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1317</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>1004.9</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AH275" t="inlineStr"/>
+      <c r="AI275" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI275"/>
+  <dimension ref="A1:AI276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28443,6 +28443,109 @@
       <c r="AH275" t="inlineStr"/>
       <c r="AI275" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>853.28</v>
+      </c>
+      <c r="C276" t="n">
+        <v>866</v>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="n">
+        <v>692</v>
+      </c>
+      <c r="F276" t="n">
+        <v>1742</v>
+      </c>
+      <c r="G276" t="n">
+        <v>665.5</v>
+      </c>
+      <c r="H276" t="n">
+        <v>760</v>
+      </c>
+      <c r="I276" t="n">
+        <v>634.5</v>
+      </c>
+      <c r="J276" t="n">
+        <v>720</v>
+      </c>
+      <c r="K276" t="n">
+        <v>1320</v>
+      </c>
+      <c r="L276" t="n">
+        <v>930</v>
+      </c>
+      <c r="M276" t="n">
+        <v>1470</v>
+      </c>
+      <c r="N276" t="n">
+        <v>880</v>
+      </c>
+      <c r="O276" t="n">
+        <v>745</v>
+      </c>
+      <c r="P276" t="n">
+        <v>1550</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>950</v>
+      </c>
+      <c r="R276" t="n">
+        <v>770</v>
+      </c>
+      <c r="S276" t="n">
+        <v>1380</v>
+      </c>
+      <c r="T276" t="n">
+        <v>1050</v>
+      </c>
+      <c r="U276" t="n">
+        <v>940</v>
+      </c>
+      <c r="V276" t="n">
+        <v>1712.5</v>
+      </c>
+      <c r="W276" t="n">
+        <v>880</v>
+      </c>
+      <c r="X276" t="n">
+        <v>747</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>1560</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>795</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>748</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>952</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>762</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>1347</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>905.1799999999999</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH276" t="inlineStr"/>
+      <c r="AI276" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI276"/>
+  <dimension ref="A1:AI277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28546,6 +28546,109 @@
       <c r="AH276" t="inlineStr"/>
       <c r="AI276" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>793.8099999999999</v>
+      </c>
+      <c r="C277" t="n">
+        <v>805</v>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="n">
+        <v>640</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1642.5</v>
+      </c>
+      <c r="G277" t="n">
+        <v>625.75</v>
+      </c>
+      <c r="H277" t="n">
+        <v>735</v>
+      </c>
+      <c r="I277" t="n">
+        <v>597</v>
+      </c>
+      <c r="J277" t="n">
+        <v>700</v>
+      </c>
+      <c r="K277" t="n">
+        <v>1230</v>
+      </c>
+      <c r="L277" t="n">
+        <v>850</v>
+      </c>
+      <c r="M277" t="n">
+        <v>1470</v>
+      </c>
+      <c r="N277" t="n">
+        <v>820</v>
+      </c>
+      <c r="O277" t="n">
+        <v>695</v>
+      </c>
+      <c r="P277" t="n">
+        <v>1445</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>880</v>
+      </c>
+      <c r="R277" t="n">
+        <v>680</v>
+      </c>
+      <c r="S277" t="n">
+        <v>1289.25</v>
+      </c>
+      <c r="T277" t="n">
+        <v>950</v>
+      </c>
+      <c r="U277" t="n">
+        <v>870</v>
+      </c>
+      <c r="V277" t="n">
+        <v>1612</v>
+      </c>
+      <c r="W277" t="n">
+        <v>820</v>
+      </c>
+      <c r="X277" t="n">
+        <v>697</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>765</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>730</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>884</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>742</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>1203</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>805.05</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>850</v>
+      </c>
+      <c r="AH277" t="inlineStr"/>
+      <c r="AI277" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI277"/>
+  <dimension ref="A1:AI278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28649,6 +28649,109 @@
       <c r="AH277" t="inlineStr"/>
       <c r="AI277" t="inlineStr"/>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>806.14</v>
+      </c>
+      <c r="C278" t="n">
+        <v>812</v>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="n">
+        <v>661</v>
+      </c>
+      <c r="F278" t="n">
+        <v>1622.75</v>
+      </c>
+      <c r="G278" t="n">
+        <v>652.5</v>
+      </c>
+      <c r="H278" t="n">
+        <v>730</v>
+      </c>
+      <c r="I278" t="n">
+        <v>629</v>
+      </c>
+      <c r="J278" t="n">
+        <v>670</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L278" t="n">
+        <v>850</v>
+      </c>
+      <c r="M278" t="n">
+        <v>1475</v>
+      </c>
+      <c r="N278" t="n">
+        <v>845</v>
+      </c>
+      <c r="O278" t="n">
+        <v>703</v>
+      </c>
+      <c r="P278" t="n">
+        <v>1540</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>905</v>
+      </c>
+      <c r="R278" t="n">
+        <v>714</v>
+      </c>
+      <c r="S278" t="n">
+        <v>1350</v>
+      </c>
+      <c r="T278" t="n">
+        <v>980</v>
+      </c>
+      <c r="U278" t="n">
+        <v>875</v>
+      </c>
+      <c r="V278" t="n">
+        <v>1682.25</v>
+      </c>
+      <c r="W278" t="n">
+        <v>845</v>
+      </c>
+      <c r="X278" t="n">
+        <v>705</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>1550</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>770</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>735</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>912</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>754</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>1317</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>805.1799999999999</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>850</v>
+      </c>
+      <c r="AH278" t="inlineStr"/>
+      <c r="AI278" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI278"/>
+  <dimension ref="A1:AI279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28752,6 +28752,109 @@
       <c r="AH278" t="inlineStr"/>
       <c r="AI278" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>846.23</v>
+      </c>
+      <c r="C279" t="n">
+        <v>855</v>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="n">
+        <v>720</v>
+      </c>
+      <c r="F279" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G279" t="n">
+        <v>669</v>
+      </c>
+      <c r="H279" t="n">
+        <v>760</v>
+      </c>
+      <c r="I279" t="n">
+        <v>642.25</v>
+      </c>
+      <c r="J279" t="n">
+        <v>705</v>
+      </c>
+      <c r="K279" t="n">
+        <v>1370</v>
+      </c>
+      <c r="L279" t="n">
+        <v>855</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1495</v>
+      </c>
+      <c r="N279" t="n">
+        <v>860</v>
+      </c>
+      <c r="O279" t="n">
+        <v>743</v>
+      </c>
+      <c r="P279" t="n">
+        <v>1660</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>895</v>
+      </c>
+      <c r="R279" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="S279" t="n">
+        <v>1460</v>
+      </c>
+      <c r="T279" t="n">
+        <v>980</v>
+      </c>
+      <c r="U279" t="n">
+        <v>890</v>
+      </c>
+      <c r="V279" t="n">
+        <v>1844.75</v>
+      </c>
+      <c r="W279" t="n">
+        <v>860</v>
+      </c>
+      <c r="X279" t="n">
+        <v>745</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>765</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>732</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>922</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>777</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>1337</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>830</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>875</v>
+      </c>
+      <c r="AH279" t="inlineStr"/>
+      <c r="AI279" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,181 +413,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI279"/>
+  <dimension ref="A1:AI280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>AMFSA00</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MFSPD00</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PPXDK00</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PUAFT00</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AAXYO00</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PUMFD00</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MFRDD00</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>PUABC00</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PUAFN00</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>AARTG00</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MFSAD00</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>AAXWO00</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>MFZSD00</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>BFDZA00</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>MGZSD00</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>MFHKD00</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PUAER00</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>AAXYQ00</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>MFSKD00</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>PUAGQ00</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>AAXYS00</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>MFSHD00</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>AARKD00</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>AAXYR00</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>MFGBD00</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>AAKAB00</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>AARSU00</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>MFNOD00</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>AAGQE00</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>AAWYA00</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>AMFFA00</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>MFFJD00</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>PUAXP00</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>AAXYP00</t>
         </is>
@@ -28855,6 +28843,109 @@
       <c r="AH279" t="inlineStr"/>
       <c r="AI279" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>855.5</v>
+      </c>
+      <c r="C280" t="n">
+        <v>871</v>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="n">
+        <v>741</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1895</v>
+      </c>
+      <c r="G280" t="n">
+        <v>674.75</v>
+      </c>
+      <c r="H280" t="n">
+        <v>760</v>
+      </c>
+      <c r="I280" t="n">
+        <v>644.75</v>
+      </c>
+      <c r="J280" t="n">
+        <v>708</v>
+      </c>
+      <c r="K280" t="n">
+        <v>1420</v>
+      </c>
+      <c r="L280" t="n">
+        <v>868</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1485</v>
+      </c>
+      <c r="N280" t="n">
+        <v>865</v>
+      </c>
+      <c r="O280" t="n">
+        <v>757</v>
+      </c>
+      <c r="P280" t="n">
+        <v>1720</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>910</v>
+      </c>
+      <c r="R280" t="n">
+        <v>797</v>
+      </c>
+      <c r="S280" t="n">
+        <v>1530</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1030</v>
+      </c>
+      <c r="U280" t="n">
+        <v>920</v>
+      </c>
+      <c r="V280" t="n">
+        <v>1800</v>
+      </c>
+      <c r="W280" t="n">
+        <v>865</v>
+      </c>
+      <c r="X280" t="n">
+        <v>759</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>1730</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>810</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>765</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>1560</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>937</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>779</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>1352</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>839.95</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>885</v>
+      </c>
+      <c r="AH280" t="inlineStr"/>
+      <c r="AI280" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI280"/>
+  <dimension ref="A1:AI281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28946,6 +28946,109 @@
       <c r="AH280" t="inlineStr"/>
       <c r="AI280" t="inlineStr"/>
     </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>841.14</v>
+      </c>
+      <c r="C281" t="n">
+        <v>862</v>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="n">
+        <v>700</v>
+      </c>
+      <c r="F281" t="n">
+        <v>1811</v>
+      </c>
+      <c r="G281" t="n">
+        <v>675</v>
+      </c>
+      <c r="H281" t="n">
+        <v>745</v>
+      </c>
+      <c r="I281" t="n">
+        <v>633</v>
+      </c>
+      <c r="J281" t="n">
+        <v>695</v>
+      </c>
+      <c r="K281" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L281" t="n">
+        <v>901</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1480</v>
+      </c>
+      <c r="N281" t="n">
+        <v>850</v>
+      </c>
+      <c r="O281" t="n">
+        <v>720</v>
+      </c>
+      <c r="P281" t="n">
+        <v>1650</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>899</v>
+      </c>
+      <c r="R281" t="n">
+        <v>760</v>
+      </c>
+      <c r="S281" t="n">
+        <v>1450</v>
+      </c>
+      <c r="T281" t="n">
+        <v>970</v>
+      </c>
+      <c r="U281" t="n">
+        <v>870</v>
+      </c>
+      <c r="V281" t="n">
+        <v>1740.25</v>
+      </c>
+      <c r="W281" t="n">
+        <v>850</v>
+      </c>
+      <c r="X281" t="n">
+        <v>722</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>1660</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>800</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>755</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>1550</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>912</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>764</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>1334</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>814.95</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>850</v>
+      </c>
+      <c r="AH281" t="inlineStr"/>
+      <c r="AI281" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI281"/>
+  <dimension ref="A1:AI282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29049,6 +29049,109 @@
       <c r="AH281" t="inlineStr"/>
       <c r="AI281" t="inlineStr"/>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>820.38</v>
+      </c>
+      <c r="C282" t="n">
+        <v>858</v>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="n">
+        <v>670</v>
+      </c>
+      <c r="F282" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G282" t="n">
+        <v>624.75</v>
+      </c>
+      <c r="H282" t="n">
+        <v>690</v>
+      </c>
+      <c r="I282" t="n">
+        <v>606</v>
+      </c>
+      <c r="J282" t="n">
+        <v>645</v>
+      </c>
+      <c r="K282" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L282" t="n">
+        <v>870</v>
+      </c>
+      <c r="M282" t="n">
+        <v>1476</v>
+      </c>
+      <c r="N282" t="n">
+        <v>838</v>
+      </c>
+      <c r="O282" t="n">
+        <v>690</v>
+      </c>
+      <c r="P282" t="n">
+        <v>1700</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>870</v>
+      </c>
+      <c r="R282" t="n">
+        <v>728</v>
+      </c>
+      <c r="S282" t="n">
+        <v>1500</v>
+      </c>
+      <c r="T282" t="n">
+        <v>978.5</v>
+      </c>
+      <c r="U282" t="n">
+        <v>800</v>
+      </c>
+      <c r="V282" t="n">
+        <v>1731.5</v>
+      </c>
+      <c r="W282" t="n">
+        <v>838</v>
+      </c>
+      <c r="X282" t="n">
+        <v>692</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1710</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>765</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>745</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>924</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>809</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>1342</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>805.11</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>835</v>
+      </c>
+      <c r="AH282" t="inlineStr"/>
+      <c r="AI282" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI282"/>
+  <dimension ref="A1:AI283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29152,6 +29152,109 @@
       <c r="AH282" t="inlineStr"/>
       <c r="AI282" t="inlineStr"/>
     </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>856.25</v>
+      </c>
+      <c r="C283" t="n">
+        <v>896</v>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="n">
+        <v>745</v>
+      </c>
+      <c r="F283" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G283" t="n">
+        <v>681.5</v>
+      </c>
+      <c r="H283" t="n">
+        <v>725</v>
+      </c>
+      <c r="I283" t="n">
+        <v>657.75</v>
+      </c>
+      <c r="J283" t="n">
+        <v>700</v>
+      </c>
+      <c r="K283" t="n">
+        <v>1435</v>
+      </c>
+      <c r="L283" t="n">
+        <v>891</v>
+      </c>
+      <c r="M283" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N283" t="n">
+        <v>870</v>
+      </c>
+      <c r="O283" t="n">
+        <v>765</v>
+      </c>
+      <c r="P283" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>900</v>
+      </c>
+      <c r="R283" t="n">
+        <v>788</v>
+      </c>
+      <c r="S283" t="n">
+        <v>1750</v>
+      </c>
+      <c r="T283" t="n">
+        <v>1010</v>
+      </c>
+      <c r="U283" t="n">
+        <v>854</v>
+      </c>
+      <c r="V283" t="n">
+        <v>1980.75</v>
+      </c>
+      <c r="W283" t="n">
+        <v>870</v>
+      </c>
+      <c r="X283" t="n">
+        <v>767</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>815</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>770</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>1570</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>917</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>819</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>839.9400000000001</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>870</v>
+      </c>
+      <c r="AH283" t="inlineStr"/>
+      <c r="AI283" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI283"/>
+  <dimension ref="A1:AI284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29255,6 +29255,93 @@
       <c r="AH283" t="inlineStr"/>
       <c r="AI283" t="inlineStr"/>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>840.72</v>
+      </c>
+      <c r="C284" t="n">
+        <v>878</v>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="n">
+        <v>740</v>
+      </c>
+      <c r="F284" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="n">
+        <v>865</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1487</v>
+      </c>
+      <c r="N284" t="n">
+        <v>865</v>
+      </c>
+      <c r="O284" t="n">
+        <v>758</v>
+      </c>
+      <c r="P284" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>890</v>
+      </c>
+      <c r="R284" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="S284" t="n">
+        <v>1750</v>
+      </c>
+      <c r="T284" t="n">
+        <v>980</v>
+      </c>
+      <c r="U284" t="n">
+        <v>810</v>
+      </c>
+      <c r="V284" t="n">
+        <v>2021.5</v>
+      </c>
+      <c r="W284" t="n">
+        <v>865</v>
+      </c>
+      <c r="X284" t="n">
+        <v>760</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>1985</v>
+      </c>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
+      <c r="AB284" t="inlineStr"/>
+      <c r="AC284" t="n">
+        <v>926</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>821</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>1376</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>824.97</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>855</v>
+      </c>
+      <c r="AH284" t="inlineStr"/>
+      <c r="AI284" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI284"/>
+  <dimension ref="A1:AI285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29342,6 +29342,109 @@
       <c r="AH284" t="inlineStr"/>
       <c r="AI284" t="inlineStr"/>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>833.52</v>
+      </c>
+      <c r="C285" t="n">
+        <v>867</v>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="n">
+        <v>734</v>
+      </c>
+      <c r="F285" t="n">
+        <v>1929.5</v>
+      </c>
+      <c r="G285" t="n">
+        <v>681.75</v>
+      </c>
+      <c r="H285" t="n">
+        <v>725</v>
+      </c>
+      <c r="I285" t="n">
+        <v>649.75</v>
+      </c>
+      <c r="J285" t="n">
+        <v>690</v>
+      </c>
+      <c r="K285" t="n">
+        <v>1485</v>
+      </c>
+      <c r="L285" t="n">
+        <v>862</v>
+      </c>
+      <c r="M285" t="n">
+        <v>1497</v>
+      </c>
+      <c r="N285" t="n">
+        <v>880</v>
+      </c>
+      <c r="O285" t="n">
+        <v>755</v>
+      </c>
+      <c r="P285" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>875</v>
+      </c>
+      <c r="R285" t="n">
+        <v>764</v>
+      </c>
+      <c r="S285" t="n">
+        <v>1700</v>
+      </c>
+      <c r="T285" t="n">
+        <v>960</v>
+      </c>
+      <c r="U285" t="n">
+        <v>775</v>
+      </c>
+      <c r="V285" t="n">
+        <v>1880</v>
+      </c>
+      <c r="W285" t="n">
+        <v>885</v>
+      </c>
+      <c r="X285" t="n">
+        <v>757</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>1910</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>805</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>775</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>932</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>857</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>1366</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>814.9400000000001</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>845</v>
+      </c>
+      <c r="AH285" t="inlineStr"/>
+      <c r="AI285" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI285"/>
+  <dimension ref="A1:AI286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29445,6 +29445,109 @@
       <c r="AH285" t="inlineStr"/>
       <c r="AI285" t="inlineStr"/>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>717.7</v>
+      </c>
+      <c r="C286" t="n">
+        <v>754</v>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="n">
+        <v>644</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="G286" t="n">
+        <v>597.25</v>
+      </c>
+      <c r="H286" t="n">
+        <v>665</v>
+      </c>
+      <c r="I286" t="n">
+        <v>584.75</v>
+      </c>
+      <c r="J286" t="n">
+        <v>640</v>
+      </c>
+      <c r="K286" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L286" t="n">
+        <v>746</v>
+      </c>
+      <c r="M286" t="n">
+        <v>1437</v>
+      </c>
+      <c r="N286" t="n">
+        <v>775</v>
+      </c>
+      <c r="O286" t="n">
+        <v>690</v>
+      </c>
+      <c r="P286" t="n">
+        <v>1740</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>790</v>
+      </c>
+      <c r="R286" t="n">
+        <v>690</v>
+      </c>
+      <c r="S286" t="n">
+        <v>1500</v>
+      </c>
+      <c r="T286" t="n">
+        <v>860</v>
+      </c>
+      <c r="U286" t="n">
+        <v>677</v>
+      </c>
+      <c r="V286" t="n">
+        <v>1525.25</v>
+      </c>
+      <c r="W286" t="n">
+        <v>785</v>
+      </c>
+      <c r="X286" t="n">
+        <v>692</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1750</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>720</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>797</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>822</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>1166</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>709.97</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>740</v>
+      </c>
+      <c r="AH286" t="inlineStr"/>
+      <c r="AI286" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI286"/>
+  <dimension ref="A1:AI287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29548,6 +29548,109 @@
       <c r="AH286" t="inlineStr"/>
       <c r="AI286" t="inlineStr"/>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>737.5599999999999</v>
+      </c>
+      <c r="C287" t="n">
+        <v>764</v>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="n">
+        <v>652</v>
+      </c>
+      <c r="F287" t="n">
+        <v>1622.25</v>
+      </c>
+      <c r="G287" t="n">
+        <v>613.25</v>
+      </c>
+      <c r="H287" t="n">
+        <v>670</v>
+      </c>
+      <c r="I287" t="n">
+        <v>581.75</v>
+      </c>
+      <c r="J287" t="n">
+        <v>645</v>
+      </c>
+      <c r="K287" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L287" t="n">
+        <v>760</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1441</v>
+      </c>
+      <c r="N287" t="n">
+        <v>785</v>
+      </c>
+      <c r="O287" t="n">
+        <v>704</v>
+      </c>
+      <c r="P287" t="n">
+        <v>1725</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>780</v>
+      </c>
+      <c r="R287" t="n">
+        <v>688</v>
+      </c>
+      <c r="S287" t="n">
+        <v>1530</v>
+      </c>
+      <c r="T287" t="n">
+        <v>873</v>
+      </c>
+      <c r="U287" t="n">
+        <v>677</v>
+      </c>
+      <c r="V287" t="n">
+        <v>1661.75</v>
+      </c>
+      <c r="W287" t="n">
+        <v>795</v>
+      </c>
+      <c r="X287" t="n">
+        <v>706</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>1735</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>713</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>703</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>837</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>811</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>1197</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>720.03</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>750</v>
+      </c>
+      <c r="AH287" t="inlineStr"/>
+      <c r="AI287" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI287"/>
+  <dimension ref="A1:AI288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29651,6 +29651,109 @@
       <c r="AH287" t="inlineStr"/>
       <c r="AI287" t="inlineStr"/>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>711.4</v>
+      </c>
+      <c r="C288" t="n">
+        <v>739</v>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="n">
+        <v>640</v>
+      </c>
+      <c r="F288" t="n">
+        <v>1620.75</v>
+      </c>
+      <c r="G288" t="n">
+        <v>605.25</v>
+      </c>
+      <c r="H288" t="n">
+        <v>650</v>
+      </c>
+      <c r="I288" t="n">
+        <v>570.25</v>
+      </c>
+      <c r="J288" t="n">
+        <v>615</v>
+      </c>
+      <c r="K288" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L288" t="n">
+        <v>749</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1471</v>
+      </c>
+      <c r="N288" t="n">
+        <v>755</v>
+      </c>
+      <c r="O288" t="n">
+        <v>680</v>
+      </c>
+      <c r="P288" t="n">
+        <v>1660</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>760</v>
+      </c>
+      <c r="R288" t="n">
+        <v>675</v>
+      </c>
+      <c r="S288" t="n">
+        <v>1530</v>
+      </c>
+      <c r="T288" t="n">
+        <v>847</v>
+      </c>
+      <c r="U288" t="n">
+        <v>671</v>
+      </c>
+      <c r="V288" t="n">
+        <v>1702</v>
+      </c>
+      <c r="W288" t="n">
+        <v>770</v>
+      </c>
+      <c r="X288" t="n">
+        <v>680</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>1670</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>710</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>695</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>832</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>816</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>1170</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>694</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>724</v>
+      </c>
+      <c r="AH288" t="inlineStr"/>
+      <c r="AI288" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI288"/>
+  <dimension ref="A1:AI289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29754,6 +29754,109 @@
       <c r="AH288" t="inlineStr"/>
       <c r="AI288" t="inlineStr"/>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>706.9400000000001</v>
+      </c>
+      <c r="C289" t="n">
+        <v>736</v>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="n">
+        <v>666</v>
+      </c>
+      <c r="F289" t="n">
+        <v>1470</v>
+      </c>
+      <c r="G289" t="n">
+        <v>612.25</v>
+      </c>
+      <c r="H289" t="n">
+        <v>675</v>
+      </c>
+      <c r="I289" t="n">
+        <v>574.25</v>
+      </c>
+      <c r="J289" t="n">
+        <v>635</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L289" t="n">
+        <v>723</v>
+      </c>
+      <c r="M289" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N289" t="n">
+        <v>740</v>
+      </c>
+      <c r="O289" t="n">
+        <v>690</v>
+      </c>
+      <c r="P289" t="n">
+        <v>1555</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>771.5</v>
+      </c>
+      <c r="R289" t="n">
+        <v>700</v>
+      </c>
+      <c r="S289" t="n">
+        <v>1426</v>
+      </c>
+      <c r="T289" t="n">
+        <v>820</v>
+      </c>
+      <c r="U289" t="n">
+        <v>694</v>
+      </c>
+      <c r="V289" t="n">
+        <v>1582.25</v>
+      </c>
+      <c r="W289" t="n">
+        <v>755</v>
+      </c>
+      <c r="X289" t="n">
+        <v>695</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1565</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>730</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>698</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>1395</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>837</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>787</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>1153</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>699.87</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>720</v>
+      </c>
+      <c r="AH289" t="inlineStr"/>
+      <c r="AI289" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI289"/>
+  <dimension ref="A1:AI290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29757,105 +29757,208 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>706.9400000000001</v>
+        <v>726.98</v>
       </c>
       <c r="C289" t="n">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="F289" t="n">
-        <v>1470</v>
+        <v>1590.5</v>
       </c>
       <c r="G289" t="n">
-        <v>612.25</v>
+        <v>626.25</v>
       </c>
       <c r="H289" t="n">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="I289" t="n">
-        <v>574.25</v>
+        <v>593.25</v>
       </c>
       <c r="J289" t="n">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="K289" t="n">
-        <v>1250</v>
+        <v>1290</v>
       </c>
       <c r="L289" t="n">
-        <v>723</v>
+        <v>763</v>
       </c>
       <c r="M289" t="n">
-        <v>1500</v>
+        <v>1495</v>
       </c>
       <c r="N289" t="n">
-        <v>740</v>
+        <v>770</v>
       </c>
       <c r="O289" t="n">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="P289" t="n">
-        <v>1555</v>
+        <v>1640</v>
       </c>
       <c r="Q289" t="n">
-        <v>771.5</v>
+        <v>780</v>
       </c>
       <c r="R289" t="n">
-        <v>700</v>
+        <v>717.5</v>
       </c>
       <c r="S289" t="n">
-        <v>1426</v>
+        <v>1507.5</v>
       </c>
       <c r="T289" t="n">
-        <v>820</v>
+        <v>864</v>
       </c>
       <c r="U289" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="V289" t="n">
-        <v>1582.25</v>
+        <v>1665.75</v>
       </c>
       <c r="W289" t="n">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="X289" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
       <c r="Y289" t="n">
-        <v>1565</v>
+        <v>1650</v>
       </c>
       <c r="Z289" t="n">
         <v>730</v>
       </c>
       <c r="AA289" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AB289" t="n">
-        <v>1395</v>
+        <v>1450</v>
       </c>
       <c r="AC289" t="n">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="AD289" t="n">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="AE289" t="n">
-        <v>1153</v>
+        <v>1185</v>
       </c>
       <c r="AF289" t="n">
-        <v>699.87</v>
+        <v>720.11</v>
       </c>
       <c r="AG289" t="n">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="AH289" t="inlineStr"/>
       <c r="AI289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>706.9400000000001</v>
+      </c>
+      <c r="C290" t="n">
+        <v>736</v>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="n">
+        <v>666</v>
+      </c>
+      <c r="F290" t="n">
+        <v>1470</v>
+      </c>
+      <c r="G290" t="n">
+        <v>612.25</v>
+      </c>
+      <c r="H290" t="n">
+        <v>675</v>
+      </c>
+      <c r="I290" t="n">
+        <v>574.25</v>
+      </c>
+      <c r="J290" t="n">
+        <v>635</v>
+      </c>
+      <c r="K290" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L290" t="n">
+        <v>723</v>
+      </c>
+      <c r="M290" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N290" t="n">
+        <v>740</v>
+      </c>
+      <c r="O290" t="n">
+        <v>690</v>
+      </c>
+      <c r="P290" t="n">
+        <v>1555</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>771.5</v>
+      </c>
+      <c r="R290" t="n">
+        <v>700</v>
+      </c>
+      <c r="S290" t="n">
+        <v>1426</v>
+      </c>
+      <c r="T290" t="n">
+        <v>820</v>
+      </c>
+      <c r="U290" t="n">
+        <v>694</v>
+      </c>
+      <c r="V290" t="n">
+        <v>1582.25</v>
+      </c>
+      <c r="W290" t="n">
+        <v>755</v>
+      </c>
+      <c r="X290" t="n">
+        <v>695</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1565</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>730</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>698</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>1395</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>837</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>787</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>1153</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>699.87</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>720</v>
+      </c>
+      <c r="AH290" t="inlineStr"/>
+      <c r="AI290" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI290"/>
+  <dimension ref="A1:AI291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29960,6 +29960,109 @@
       <c r="AH290" t="inlineStr"/>
       <c r="AI290" t="inlineStr"/>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>674.35</v>
+      </c>
+      <c r="C291" t="n">
+        <v>700</v>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="n">
+        <v>639</v>
+      </c>
+      <c r="F291" t="n">
+        <v>1338.25</v>
+      </c>
+      <c r="G291" t="n">
+        <v>576.25</v>
+      </c>
+      <c r="H291" t="n">
+        <v>633</v>
+      </c>
+      <c r="I291" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="J291" t="n">
+        <v>563</v>
+      </c>
+      <c r="K291" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L291" t="n">
+        <v>678</v>
+      </c>
+      <c r="M291" t="n">
+        <v>1507</v>
+      </c>
+      <c r="N291" t="n">
+        <v>710</v>
+      </c>
+      <c r="O291" t="n">
+        <v>668</v>
+      </c>
+      <c r="P291" t="n">
+        <v>1445</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>730</v>
+      </c>
+      <c r="R291" t="n">
+        <v>669</v>
+      </c>
+      <c r="S291" t="n">
+        <v>1320</v>
+      </c>
+      <c r="T291" t="n">
+        <v>786</v>
+      </c>
+      <c r="U291" t="n">
+        <v>669</v>
+      </c>
+      <c r="V291" t="n">
+        <v>1538.25</v>
+      </c>
+      <c r="W291" t="n">
+        <v>725</v>
+      </c>
+      <c r="X291" t="n">
+        <v>673</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>620</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>590</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>777</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>786</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>1011</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>680.04</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>700</v>
+      </c>
+      <c r="AH291" t="inlineStr"/>
+      <c r="AI291" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI291"/>
+  <dimension ref="A1:AI292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29963,105 +29963,208 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>674.35</v>
+        <v>675.4299999999999</v>
       </c>
       <c r="C291" t="n">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="F291" t="n">
-        <v>1338.25</v>
+        <v>1396.75</v>
       </c>
       <c r="G291" t="n">
-        <v>576.25</v>
+        <v>616.75</v>
       </c>
       <c r="H291" t="n">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="I291" t="n">
-        <v>517.75</v>
+        <v>555.25</v>
       </c>
       <c r="J291" t="n">
-        <v>563</v>
+        <v>603</v>
       </c>
       <c r="K291" t="n">
-        <v>1107</v>
+        <v>1200</v>
       </c>
       <c r="L291" t="n">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="M291" t="n">
-        <v>1507</v>
+        <v>1516</v>
       </c>
       <c r="N291" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="O291" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="P291" t="n">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="Q291" t="n">
         <v>730</v>
       </c>
       <c r="R291" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="S291" t="n">
-        <v>1320</v>
+        <v>1337</v>
       </c>
       <c r="T291" t="n">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="U291" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="V291" t="n">
-        <v>1538.25</v>
+        <v>1532</v>
       </c>
       <c r="W291" t="n">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="X291" t="n">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="Y291" t="n">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="Z291" t="n">
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="AA291" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="AB291" t="n">
-        <v>1180</v>
+        <v>1325</v>
       </c>
       <c r="AC291" t="n">
-        <v>777</v>
+        <v>824</v>
       </c>
       <c r="AD291" t="n">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="AE291" t="n">
-        <v>1011</v>
+        <v>1188</v>
       </c>
       <c r="AF291" t="n">
-        <v>680.04</v>
+        <v>681.95</v>
       </c>
       <c r="AG291" t="n">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AH291" t="inlineStr"/>
       <c r="AI291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>674.35</v>
+      </c>
+      <c r="C292" t="n">
+        <v>700</v>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="n">
+        <v>639</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1338.25</v>
+      </c>
+      <c r="G292" t="n">
+        <v>576.25</v>
+      </c>
+      <c r="H292" t="n">
+        <v>633</v>
+      </c>
+      <c r="I292" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="J292" t="n">
+        <v>563</v>
+      </c>
+      <c r="K292" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L292" t="n">
+        <v>678</v>
+      </c>
+      <c r="M292" t="n">
+        <v>1507</v>
+      </c>
+      <c r="N292" t="n">
+        <v>710</v>
+      </c>
+      <c r="O292" t="n">
+        <v>668</v>
+      </c>
+      <c r="P292" t="n">
+        <v>1445</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>730</v>
+      </c>
+      <c r="R292" t="n">
+        <v>669</v>
+      </c>
+      <c r="S292" t="n">
+        <v>1320</v>
+      </c>
+      <c r="T292" t="n">
+        <v>786</v>
+      </c>
+      <c r="U292" t="n">
+        <v>669</v>
+      </c>
+      <c r="V292" t="n">
+        <v>1538.25</v>
+      </c>
+      <c r="W292" t="n">
+        <v>725</v>
+      </c>
+      <c r="X292" t="n">
+        <v>673</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>620</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>590</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>777</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>786</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>1011</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>680.04</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>700</v>
+      </c>
+      <c r="AH292" t="inlineStr"/>
+      <c r="AI292" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI292"/>
+  <dimension ref="A1:AI293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29963,102 +29963,102 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>675.4299999999999</v>
+        <v>683.3099999999999</v>
       </c>
       <c r="C291" t="n">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F291" t="n">
-        <v>1396.75</v>
+        <v>1389</v>
       </c>
       <c r="G291" t="n">
-        <v>616.75</v>
+        <v>612.25</v>
       </c>
       <c r="H291" t="n">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="I291" t="n">
-        <v>555.25</v>
+        <v>556.75</v>
       </c>
       <c r="J291" t="n">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="K291" t="n">
-        <v>1200</v>
+        <v>1205</v>
       </c>
       <c r="L291" t="n">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="M291" t="n">
-        <v>1516</v>
+        <v>1510</v>
       </c>
       <c r="N291" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="O291" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="P291" t="n">
-        <v>1455</v>
+        <v>1460</v>
       </c>
       <c r="Q291" t="n">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="R291" t="n">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="S291" t="n">
-        <v>1337</v>
+        <v>1360</v>
       </c>
       <c r="T291" t="n">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="U291" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="V291" t="n">
-        <v>1532</v>
+        <v>1503</v>
       </c>
       <c r="W291" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="X291" t="n">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="Y291" t="n">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="Z291" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="AA291" t="n">
-        <v>670</v>
+        <v>695</v>
       </c>
       <c r="AB291" t="n">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="AC291" t="n">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="AD291" t="n">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="AE291" t="n">
-        <v>1188</v>
+        <v>1173</v>
       </c>
       <c r="AF291" t="n">
-        <v>681.95</v>
+        <v>690.08</v>
       </c>
       <c r="AG291" t="n">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="AH291" t="inlineStr"/>
       <c r="AI291" t="inlineStr"/>
@@ -30066,105 +30066,208 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>674.35</v>
+        <v>675.4299999999999</v>
       </c>
       <c r="C292" t="n">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="F292" t="n">
-        <v>1338.25</v>
+        <v>1396.75</v>
       </c>
       <c r="G292" t="n">
-        <v>576.25</v>
+        <v>616.75</v>
       </c>
       <c r="H292" t="n">
-        <v>633</v>
+        <v>665</v>
       </c>
       <c r="I292" t="n">
-        <v>517.75</v>
+        <v>555.25</v>
       </c>
       <c r="J292" t="n">
-        <v>563</v>
+        <v>603</v>
       </c>
       <c r="K292" t="n">
-        <v>1107</v>
+        <v>1200</v>
       </c>
       <c r="L292" t="n">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="M292" t="n">
-        <v>1507</v>
+        <v>1516</v>
       </c>
       <c r="N292" t="n">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="O292" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="P292" t="n">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="Q292" t="n">
         <v>730</v>
       </c>
       <c r="R292" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="S292" t="n">
-        <v>1320</v>
+        <v>1337</v>
       </c>
       <c r="T292" t="n">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="U292" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="V292" t="n">
-        <v>1538.25</v>
+        <v>1532</v>
       </c>
       <c r="W292" t="n">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="X292" t="n">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="Y292" t="n">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="Z292" t="n">
-        <v>620</v>
+        <v>700</v>
       </c>
       <c r="AA292" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="AB292" t="n">
-        <v>1180</v>
+        <v>1325</v>
       </c>
       <c r="AC292" t="n">
-        <v>777</v>
+        <v>824</v>
       </c>
       <c r="AD292" t="n">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="AE292" t="n">
-        <v>1011</v>
+        <v>1188</v>
       </c>
       <c r="AF292" t="n">
-        <v>680.04</v>
+        <v>681.95</v>
       </c>
       <c r="AG292" t="n">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AH292" t="inlineStr"/>
       <c r="AI292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>674.35</v>
+      </c>
+      <c r="C293" t="n">
+        <v>700</v>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="n">
+        <v>639</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1338.25</v>
+      </c>
+      <c r="G293" t="n">
+        <v>576.25</v>
+      </c>
+      <c r="H293" t="n">
+        <v>633</v>
+      </c>
+      <c r="I293" t="n">
+        <v>517.75</v>
+      </c>
+      <c r="J293" t="n">
+        <v>563</v>
+      </c>
+      <c r="K293" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L293" t="n">
+        <v>678</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1507</v>
+      </c>
+      <c r="N293" t="n">
+        <v>710</v>
+      </c>
+      <c r="O293" t="n">
+        <v>668</v>
+      </c>
+      <c r="P293" t="n">
+        <v>1445</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>730</v>
+      </c>
+      <c r="R293" t="n">
+        <v>669</v>
+      </c>
+      <c r="S293" t="n">
+        <v>1320</v>
+      </c>
+      <c r="T293" t="n">
+        <v>786</v>
+      </c>
+      <c r="U293" t="n">
+        <v>669</v>
+      </c>
+      <c r="V293" t="n">
+        <v>1538.25</v>
+      </c>
+      <c r="W293" t="n">
+        <v>725</v>
+      </c>
+      <c r="X293" t="n">
+        <v>673</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1455</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>620</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>590</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>777</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>786</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>1011</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>680.04</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>700</v>
+      </c>
+      <c r="AH293" t="inlineStr"/>
+      <c r="AI293" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI293"/>
+  <dimension ref="A1:AI294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30269,6 +30269,109 @@
       <c r="AH293" t="inlineStr"/>
       <c r="AI293" t="inlineStr"/>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>655.46</v>
+      </c>
+      <c r="C294" t="n">
+        <v>678</v>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="n">
+        <v>615</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1211.5</v>
+      </c>
+      <c r="G294" t="n">
+        <v>598.25</v>
+      </c>
+      <c r="H294" t="n">
+        <v>675</v>
+      </c>
+      <c r="I294" t="n">
+        <v>535.25</v>
+      </c>
+      <c r="J294" t="n">
+        <v>590</v>
+      </c>
+      <c r="K294" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L294" t="n">
+        <v>663</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1512</v>
+      </c>
+      <c r="N294" t="n">
+        <v>695</v>
+      </c>
+      <c r="O294" t="n">
+        <v>643</v>
+      </c>
+      <c r="P294" t="n">
+        <v>1340</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>711</v>
+      </c>
+      <c r="R294" t="n">
+        <v>657.5</v>
+      </c>
+      <c r="S294" t="n">
+        <v>1206</v>
+      </c>
+      <c r="T294" t="n">
+        <v>765</v>
+      </c>
+      <c r="U294" t="n">
+        <v>644</v>
+      </c>
+      <c r="V294" t="n">
+        <v>1466.25</v>
+      </c>
+      <c r="W294" t="n">
+        <v>705</v>
+      </c>
+      <c r="X294" t="n">
+        <v>648</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>1345</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>700</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>670</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>1262</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>816</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>716</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>1116</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>660.02</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>680</v>
+      </c>
+      <c r="AH294" t="inlineStr"/>
+      <c r="AI294" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI294"/>
+  <dimension ref="A1:AI295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30372,6 +30372,109 @@
       <c r="AH294" t="inlineStr"/>
       <c r="AI294" t="inlineStr"/>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>642.04</v>
+      </c>
+      <c r="C295" t="n">
+        <v>661</v>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="n">
+        <v>594</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1202.25</v>
+      </c>
+      <c r="G295" t="n">
+        <v>620.25</v>
+      </c>
+      <c r="H295" t="n">
+        <v>669</v>
+      </c>
+      <c r="I295" t="n">
+        <v>559.25</v>
+      </c>
+      <c r="J295" t="n">
+        <v>609</v>
+      </c>
+      <c r="K295" t="n">
+        <v>1156</v>
+      </c>
+      <c r="L295" t="n">
+        <v>668</v>
+      </c>
+      <c r="M295" t="n">
+        <v>1520</v>
+      </c>
+      <c r="N295" t="n">
+        <v>665</v>
+      </c>
+      <c r="O295" t="n">
+        <v>609</v>
+      </c>
+      <c r="P295" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>683</v>
+      </c>
+      <c r="R295" t="n">
+        <v>627</v>
+      </c>
+      <c r="S295" t="n">
+        <v>1175</v>
+      </c>
+      <c r="T295" t="n">
+        <v>755</v>
+      </c>
+      <c r="U295" t="n">
+        <v>655</v>
+      </c>
+      <c r="V295" t="n">
+        <v>1464.5</v>
+      </c>
+      <c r="W295" t="n">
+        <v>673</v>
+      </c>
+      <c r="X295" t="n">
+        <v>614</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>689</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>659</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>1256</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>847</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>742</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1127</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>660.05</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>680</v>
+      </c>
+      <c r="AH295" t="inlineStr"/>
+      <c r="AI295" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI295"/>
+  <dimension ref="A1:AI296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30475,6 +30475,109 @@
       <c r="AH295" t="inlineStr"/>
       <c r="AI295" t="inlineStr"/>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>686.8200000000001</v>
+      </c>
+      <c r="C296" t="n">
+        <v>703</v>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="n">
+        <v>631</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1280.5</v>
+      </c>
+      <c r="G296" t="n">
+        <v>648</v>
+      </c>
+      <c r="H296" t="n">
+        <v>674</v>
+      </c>
+      <c r="I296" t="n">
+        <v>572</v>
+      </c>
+      <c r="J296" t="n">
+        <v>610</v>
+      </c>
+      <c r="K296" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L296" t="n">
+        <v>686</v>
+      </c>
+      <c r="M296" t="n">
+        <v>1525</v>
+      </c>
+      <c r="N296" t="n">
+        <v>700</v>
+      </c>
+      <c r="O296" t="n">
+        <v>639</v>
+      </c>
+      <c r="P296" t="n">
+        <v>1365</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>705</v>
+      </c>
+      <c r="R296" t="n">
+        <v>670.5</v>
+      </c>
+      <c r="S296" t="n">
+        <v>1220</v>
+      </c>
+      <c r="T296" t="n">
+        <v>776</v>
+      </c>
+      <c r="U296" t="n">
+        <v>670</v>
+      </c>
+      <c r="V296" t="n">
+        <v>1564.75</v>
+      </c>
+      <c r="W296" t="n">
+        <v>710</v>
+      </c>
+      <c r="X296" t="n">
+        <v>644</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>1370</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>708</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>680</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>857</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>749</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>1177</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>702.1</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>722</v>
+      </c>
+      <c r="AH296" t="inlineStr"/>
+      <c r="AI296" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI296"/>
+  <dimension ref="A1:AI297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30578,6 +30578,109 @@
       <c r="AH296" t="inlineStr"/>
       <c r="AI296" t="inlineStr"/>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>714.12</v>
+      </c>
+      <c r="C297" t="n">
+        <v>732</v>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="n">
+        <v>643</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1290.75</v>
+      </c>
+      <c r="G297" t="n">
+        <v>660.5</v>
+      </c>
+      <c r="H297" t="n">
+        <v>710</v>
+      </c>
+      <c r="I297" t="n">
+        <v>578</v>
+      </c>
+      <c r="J297" t="n">
+        <v>625</v>
+      </c>
+      <c r="K297" t="n">
+        <v>1255</v>
+      </c>
+      <c r="L297" t="n">
+        <v>704</v>
+      </c>
+      <c r="M297" t="n">
+        <v>1530</v>
+      </c>
+      <c r="N297" t="n">
+        <v>720</v>
+      </c>
+      <c r="O297" t="n">
+        <v>655</v>
+      </c>
+      <c r="P297" t="n">
+        <v>1365</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>750</v>
+      </c>
+      <c r="R297" t="n">
+        <v>674</v>
+      </c>
+      <c r="S297" t="n">
+        <v>1250</v>
+      </c>
+      <c r="T297" t="n">
+        <v>825</v>
+      </c>
+      <c r="U297" t="n">
+        <v>647</v>
+      </c>
+      <c r="V297" t="n">
+        <v>1530.25</v>
+      </c>
+      <c r="W297" t="n">
+        <v>730</v>
+      </c>
+      <c r="X297" t="n">
+        <v>655</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>1370</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>745</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>690</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>852</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>760</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>1176</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>728.99</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>749</v>
+      </c>
+      <c r="AH297" t="inlineStr"/>
+      <c r="AI297" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI297"/>
+  <dimension ref="A1:AI298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30681,6 +30681,109 @@
       <c r="AH297" t="inlineStr"/>
       <c r="AI297" t="inlineStr"/>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>733.55</v>
+      </c>
+      <c r="C298" t="n">
+        <v>748</v>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="n">
+        <v>664</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1328.5</v>
+      </c>
+      <c r="G298" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="H298" t="n">
+        <v>727</v>
+      </c>
+      <c r="I298" t="n">
+        <v>597.75</v>
+      </c>
+      <c r="J298" t="n">
+        <v>640</v>
+      </c>
+      <c r="K298" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L298" t="n">
+        <v>735</v>
+      </c>
+      <c r="M298" t="n">
+        <v>1519</v>
+      </c>
+      <c r="N298" t="n">
+        <v>745</v>
+      </c>
+      <c r="O298" t="n">
+        <v>675</v>
+      </c>
+      <c r="P298" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>763</v>
+      </c>
+      <c r="R298" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="S298" t="n">
+        <v>1300</v>
+      </c>
+      <c r="T298" t="n">
+        <v>840</v>
+      </c>
+      <c r="U298" t="n">
+        <v>668</v>
+      </c>
+      <c r="V298" t="n">
+        <v>1594</v>
+      </c>
+      <c r="W298" t="n">
+        <v>758</v>
+      </c>
+      <c r="X298" t="n">
+        <v>675</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>740</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>688</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>1405</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>842</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>765</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>1235</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>775.01</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>795</v>
+      </c>
+      <c r="AH298" t="inlineStr"/>
+      <c r="AI298" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI298"/>
+  <dimension ref="A1:AI299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30784,6 +30784,109 @@
       <c r="AH298" t="inlineStr"/>
       <c r="AI298" t="inlineStr"/>
     </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>740.4</v>
+      </c>
+      <c r="C299" t="n">
+        <v>756</v>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="n">
+        <v>684</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1244</v>
+      </c>
+      <c r="G299" t="n">
+        <v>706.75</v>
+      </c>
+      <c r="H299" t="n">
+        <v>760</v>
+      </c>
+      <c r="I299" t="n">
+        <v>610</v>
+      </c>
+      <c r="J299" t="n">
+        <v>660</v>
+      </c>
+      <c r="K299" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L299" t="n">
+        <v>745</v>
+      </c>
+      <c r="M299" t="n">
+        <v>1512</v>
+      </c>
+      <c r="N299" t="n">
+        <v>752</v>
+      </c>
+      <c r="O299" t="n">
+        <v>690</v>
+      </c>
+      <c r="P299" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>777</v>
+      </c>
+      <c r="R299" t="n">
+        <v>710</v>
+      </c>
+      <c r="S299" t="n">
+        <v>1245</v>
+      </c>
+      <c r="T299" t="n">
+        <v>910</v>
+      </c>
+      <c r="U299" t="n">
+        <v>689</v>
+      </c>
+      <c r="V299" t="n">
+        <v>1420.25</v>
+      </c>
+      <c r="W299" t="n">
+        <v>765</v>
+      </c>
+      <c r="X299" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>765</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>695</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>1410</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>872</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>797</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>1167</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>791.9</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>812</v>
+      </c>
+      <c r="AH299" t="inlineStr"/>
+      <c r="AI299" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI299"/>
+  <dimension ref="A1:AI300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30684,102 +30684,102 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>733.55</v>
+        <v>733.54</v>
       </c>
       <c r="C298" t="n">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="n">
         <v>664</v>
       </c>
       <c r="F298" t="n">
-        <v>1328.5</v>
+        <v>1351.5</v>
       </c>
       <c r="G298" t="n">
-        <v>684.5</v>
+        <v>670</v>
       </c>
       <c r="H298" t="n">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="I298" t="n">
-        <v>597.75</v>
+        <v>581.75</v>
       </c>
       <c r="J298" t="n">
         <v>640</v>
       </c>
       <c r="K298" t="n">
-        <v>1310</v>
+        <v>1295</v>
       </c>
       <c r="L298" t="n">
+        <v>708</v>
+      </c>
+      <c r="M298" t="n">
+        <v>1529</v>
+      </c>
+      <c r="N298" t="n">
         <v>735</v>
       </c>
-      <c r="M298" t="n">
-        <v>1519</v>
-      </c>
-      <c r="N298" t="n">
-        <v>745</v>
-      </c>
       <c r="O298" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="P298" t="n">
-        <v>1400</v>
+        <v>1430</v>
       </c>
       <c r="Q298" t="n">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="R298" t="n">
-        <v>698.5</v>
+        <v>685</v>
       </c>
       <c r="S298" t="n">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="T298" t="n">
         <v>840</v>
       </c>
       <c r="U298" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="V298" t="n">
-        <v>1594</v>
+        <v>1601</v>
       </c>
       <c r="W298" t="n">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="X298" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="Y298" t="n">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="Z298" t="n">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="AA298" t="n">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="AB298" t="n">
-        <v>1405</v>
+        <v>1410</v>
       </c>
       <c r="AC298" t="n">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="AD298" t="n">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="AE298" t="n">
-        <v>1235</v>
+        <v>1222</v>
       </c>
       <c r="AF298" t="n">
-        <v>775.01</v>
+        <v>757.09</v>
       </c>
       <c r="AG298" t="n">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="AH298" t="inlineStr"/>
       <c r="AI298" t="inlineStr"/>
@@ -30787,105 +30787,208 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>740.4</v>
+        <v>733.55</v>
       </c>
       <c r="C299" t="n">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="n">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="F299" t="n">
-        <v>1244</v>
+        <v>1328.5</v>
       </c>
       <c r="G299" t="n">
-        <v>706.75</v>
+        <v>684.5</v>
       </c>
       <c r="H299" t="n">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="I299" t="n">
-        <v>610</v>
+        <v>597.75</v>
       </c>
       <c r="J299" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="K299" t="n">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="L299" t="n">
+        <v>735</v>
+      </c>
+      <c r="M299" t="n">
+        <v>1519</v>
+      </c>
+      <c r="N299" t="n">
         <v>745</v>
       </c>
-      <c r="M299" t="n">
-        <v>1512</v>
-      </c>
-      <c r="N299" t="n">
-        <v>752</v>
-      </c>
       <c r="O299" t="n">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="P299" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="Q299" t="n">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="R299" t="n">
-        <v>710</v>
+        <v>698.5</v>
       </c>
       <c r="S299" t="n">
-        <v>1245</v>
+        <v>1300</v>
       </c>
       <c r="T299" t="n">
-        <v>910</v>
+        <v>840</v>
       </c>
       <c r="U299" t="n">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="V299" t="n">
-        <v>1420.25</v>
+        <v>1594</v>
       </c>
       <c r="W299" t="n">
+        <v>758</v>
+      </c>
+      <c r="X299" t="n">
+        <v>675</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>1405</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>740</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>688</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>1405</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>842</v>
+      </c>
+      <c r="AD299" t="n">
         <v>765</v>
       </c>
-      <c r="X299" t="n">
-        <v>690</v>
-      </c>
-      <c r="Y299" t="n">
-        <v>1360</v>
-      </c>
-      <c r="Z299" t="n">
-        <v>765</v>
-      </c>
-      <c r="AA299" t="n">
-        <v>695</v>
-      </c>
-      <c r="AB299" t="n">
-        <v>1410</v>
-      </c>
-      <c r="AC299" t="n">
-        <v>872</v>
-      </c>
-      <c r="AD299" t="n">
-        <v>797</v>
-      </c>
       <c r="AE299" t="n">
-        <v>1167</v>
+        <v>1235</v>
       </c>
       <c r="AF299" t="n">
-        <v>791.9</v>
+        <v>775.01</v>
       </c>
       <c r="AG299" t="n">
-        <v>812</v>
+        <v>795</v>
       </c>
       <c r="AH299" t="inlineStr"/>
       <c r="AI299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>740.4</v>
+      </c>
+      <c r="C300" t="n">
+        <v>756</v>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="n">
+        <v>684</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1244</v>
+      </c>
+      <c r="G300" t="n">
+        <v>706.75</v>
+      </c>
+      <c r="H300" t="n">
+        <v>760</v>
+      </c>
+      <c r="I300" t="n">
+        <v>610</v>
+      </c>
+      <c r="J300" t="n">
+        <v>660</v>
+      </c>
+      <c r="K300" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L300" t="n">
+        <v>745</v>
+      </c>
+      <c r="M300" t="n">
+        <v>1512</v>
+      </c>
+      <c r="N300" t="n">
+        <v>752</v>
+      </c>
+      <c r="O300" t="n">
+        <v>690</v>
+      </c>
+      <c r="P300" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>777</v>
+      </c>
+      <c r="R300" t="n">
+        <v>710</v>
+      </c>
+      <c r="S300" t="n">
+        <v>1245</v>
+      </c>
+      <c r="T300" t="n">
+        <v>910</v>
+      </c>
+      <c r="U300" t="n">
+        <v>689</v>
+      </c>
+      <c r="V300" t="n">
+        <v>1420.25</v>
+      </c>
+      <c r="W300" t="n">
+        <v>765</v>
+      </c>
+      <c r="X300" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>765</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>695</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>1410</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>872</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>797</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>1167</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>791.9</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>812</v>
+      </c>
+      <c r="AH300" t="inlineStr"/>
+      <c r="AI300" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI300"/>
+  <dimension ref="A1:AI301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30990,6 +30990,109 @@
       <c r="AH300" t="inlineStr"/>
       <c r="AI300" t="inlineStr"/>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>753.86</v>
+      </c>
+      <c r="C301" t="n">
+        <v>771</v>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="n">
+        <v>680</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1292</v>
+      </c>
+      <c r="G301" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="H301" t="n">
+        <v>795</v>
+      </c>
+      <c r="I301" t="n">
+        <v>633.75</v>
+      </c>
+      <c r="J301" t="n">
+        <v>670</v>
+      </c>
+      <c r="K301" t="n">
+        <v>1320</v>
+      </c>
+      <c r="L301" t="n">
+        <v>777</v>
+      </c>
+      <c r="M301" t="n">
+        <v>1461</v>
+      </c>
+      <c r="N301" t="n">
+        <v>765</v>
+      </c>
+      <c r="O301" t="n">
+        <v>690</v>
+      </c>
+      <c r="P301" t="n">
+        <v>1366</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>790</v>
+      </c>
+      <c r="R301" t="n">
+        <v>704</v>
+      </c>
+      <c r="S301" t="n">
+        <v>1260</v>
+      </c>
+      <c r="T301" t="n">
+        <v>975</v>
+      </c>
+      <c r="U301" t="n">
+        <v>685</v>
+      </c>
+      <c r="V301" t="n">
+        <v>1468</v>
+      </c>
+      <c r="W301" t="n">
+        <v>777</v>
+      </c>
+      <c r="X301" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>1376</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>795</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>722</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>889</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>812</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>1227</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>832.1799999999999</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>852</v>
+      </c>
+      <c r="AH301" t="inlineStr"/>
+      <c r="AI301" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI301"/>
+  <dimension ref="A1:AI302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31093,6 +31093,109 @@
       <c r="AH301" t="inlineStr"/>
       <c r="AI301" t="inlineStr"/>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>786.8099999999999</v>
+      </c>
+      <c r="C302" t="n">
+        <v>804</v>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="n">
+        <v>710</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1340.5</v>
+      </c>
+      <c r="G302" t="n">
+        <v>738.25</v>
+      </c>
+      <c r="H302" t="n">
+        <v>820</v>
+      </c>
+      <c r="I302" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="J302" t="n">
+        <v>690</v>
+      </c>
+      <c r="K302" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L302" t="n">
+        <v>792</v>
+      </c>
+      <c r="M302" t="n">
+        <v>1426</v>
+      </c>
+      <c r="N302" t="n">
+        <v>796</v>
+      </c>
+      <c r="O302" t="n">
+        <v>715</v>
+      </c>
+      <c r="P302" t="n">
+        <v>1434</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>837</v>
+      </c>
+      <c r="R302" t="n">
+        <v>735</v>
+      </c>
+      <c r="S302" t="n">
+        <v>1330</v>
+      </c>
+      <c r="T302" t="n">
+        <v>1025</v>
+      </c>
+      <c r="U302" t="n">
+        <v>730</v>
+      </c>
+      <c r="V302" t="n">
+        <v>1494</v>
+      </c>
+      <c r="W302" t="n">
+        <v>808</v>
+      </c>
+      <c r="X302" t="n">
+        <v>715</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>1444</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>800</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>710</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>1475</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>862</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>808</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>1225</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>859.89</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>890</v>
+      </c>
+      <c r="AH302" t="inlineStr"/>
+      <c r="AI302" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI302"/>
+  <dimension ref="A1:AI303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31196,6 +31196,73 @@
       <c r="AH302" t="inlineStr"/>
       <c r="AI302" t="inlineStr"/>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="n">
+        <v>740</v>
+      </c>
+      <c r="H303" t="n">
+        <v>790</v>
+      </c>
+      <c r="I303" t="n">
+        <v>614.5</v>
+      </c>
+      <c r="J303" t="n">
+        <v>675</v>
+      </c>
+      <c r="K303" t="n">
+        <v>1320</v>
+      </c>
+      <c r="L303" t="n">
+        <v>750</v>
+      </c>
+      <c r="M303" t="n">
+        <v>1408</v>
+      </c>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
+      <c r="S303" t="inlineStr"/>
+      <c r="T303" t="inlineStr"/>
+      <c r="U303" t="inlineStr"/>
+      <c r="V303" t="inlineStr"/>
+      <c r="W303" t="inlineStr"/>
+      <c r="X303" t="inlineStr"/>
+      <c r="Y303" t="inlineStr"/>
+      <c r="Z303" t="n">
+        <v>795</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>705</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>857</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>801</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>1205</v>
+      </c>
+      <c r="AF303" t="inlineStr"/>
+      <c r="AG303" t="inlineStr"/>
+      <c r="AH303" t="inlineStr"/>
+      <c r="AI303" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI303"/>
+  <dimension ref="A1:AI304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31263,6 +31263,93 @@
       <c r="AH303" t="inlineStr"/>
       <c r="AI303" t="inlineStr"/>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>786.85</v>
+      </c>
+      <c r="C304" t="n">
+        <v>807</v>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="n">
+        <v>689</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1210</v>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="n">
+        <v>797</v>
+      </c>
+      <c r="M304" t="n">
+        <v>1412</v>
+      </c>
+      <c r="N304" t="n">
+        <v>793</v>
+      </c>
+      <c r="O304" t="n">
+        <v>694</v>
+      </c>
+      <c r="P304" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>906.75</v>
+      </c>
+      <c r="R304" t="n">
+        <v>714</v>
+      </c>
+      <c r="S304" t="n">
+        <v>1224</v>
+      </c>
+      <c r="T304" t="n">
+        <v>1020</v>
+      </c>
+      <c r="U304" t="n">
+        <v>708</v>
+      </c>
+      <c r="V304" t="n">
+        <v>1340.25</v>
+      </c>
+      <c r="W304" t="n">
+        <v>805</v>
+      </c>
+      <c r="X304" t="n">
+        <v>694</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Z304" t="inlineStr"/>
+      <c r="AA304" t="inlineStr"/>
+      <c r="AB304" t="inlineStr"/>
+      <c r="AC304" t="n">
+        <v>905</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>814</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>1262</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>865.09</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>895</v>
+      </c>
+      <c r="AH304" t="inlineStr"/>
+      <c r="AI304" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI304"/>
+  <dimension ref="A1:AI305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31350,6 +31350,109 @@
       <c r="AH304" t="inlineStr"/>
       <c r="AI304" t="inlineStr"/>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>757.66</v>
+      </c>
+      <c r="C305" t="n">
+        <v>769</v>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="n">
+        <v>675</v>
+      </c>
+      <c r="F305" t="n">
+        <v>1115</v>
+      </c>
+      <c r="G305" t="n">
+        <v>708</v>
+      </c>
+      <c r="H305" t="n">
+        <v>770</v>
+      </c>
+      <c r="I305" t="n">
+        <v>623</v>
+      </c>
+      <c r="J305" t="n">
+        <v>680</v>
+      </c>
+      <c r="K305" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L305" t="n">
+        <v>760</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1421</v>
+      </c>
+      <c r="N305" t="n">
+        <v>765</v>
+      </c>
+      <c r="O305" t="n">
+        <v>700</v>
+      </c>
+      <c r="P305" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>815</v>
+      </c>
+      <c r="R305" t="n">
+        <v>706</v>
+      </c>
+      <c r="S305" t="n">
+        <v>1130</v>
+      </c>
+      <c r="T305" t="n">
+        <v>980</v>
+      </c>
+      <c r="U305" t="n">
+        <v>700</v>
+      </c>
+      <c r="V305" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="W305" t="n">
+        <v>770</v>
+      </c>
+      <c r="X305" t="n">
+        <v>700</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>1240</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>755</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>699</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>833</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>787</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>1153</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>835.1900000000001</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>865</v>
+      </c>
+      <c r="AH305" t="inlineStr"/>
+      <c r="AI305" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI305"/>
+  <dimension ref="A1:AI306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31353,105 +31353,208 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>757.66</v>
+        <v>845.63</v>
       </c>
       <c r="C305" t="n">
-        <v>769</v>
+        <v>872</v>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="n">
-        <v>675</v>
+        <v>738</v>
       </c>
       <c r="F305" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G305" t="n">
+        <v>800.25</v>
+      </c>
+      <c r="H305" t="n">
+        <v>840</v>
+      </c>
+      <c r="I305" t="n">
+        <v>662.25</v>
+      </c>
+      <c r="J305" t="n">
+        <v>700</v>
+      </c>
+      <c r="K305" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L305" t="n">
+        <v>812</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1408</v>
+      </c>
+      <c r="N305" t="n">
+        <v>845</v>
+      </c>
+      <c r="O305" t="n">
+        <v>725</v>
+      </c>
+      <c r="P305" t="n">
+        <v>1370</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>935</v>
+      </c>
+      <c r="R305" t="n">
+        <v>765</v>
+      </c>
+      <c r="S305" t="n">
+        <v>1240</v>
+      </c>
+      <c r="T305" t="n">
         <v>1115</v>
       </c>
-      <c r="G305" t="n">
-        <v>708</v>
-      </c>
-      <c r="H305" t="n">
-        <v>770</v>
-      </c>
-      <c r="I305" t="n">
-        <v>623</v>
-      </c>
-      <c r="J305" t="n">
-        <v>680</v>
-      </c>
-      <c r="K305" t="n">
-        <v>1150</v>
-      </c>
-      <c r="L305" t="n">
-        <v>760</v>
-      </c>
-      <c r="M305" t="n">
-        <v>1421</v>
-      </c>
-      <c r="N305" t="n">
-        <v>765</v>
-      </c>
-      <c r="O305" t="n">
-        <v>700</v>
-      </c>
-      <c r="P305" t="n">
-        <v>1235</v>
-      </c>
-      <c r="Q305" t="n">
-        <v>815</v>
-      </c>
-      <c r="R305" t="n">
-        <v>706</v>
-      </c>
-      <c r="S305" t="n">
-        <v>1130</v>
-      </c>
-      <c r="T305" t="n">
-        <v>980</v>
-      </c>
       <c r="U305" t="n">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="V305" t="n">
-        <v>1215.5</v>
+        <v>1360.25</v>
       </c>
       <c r="W305" t="n">
-        <v>770</v>
+        <v>855</v>
       </c>
       <c r="X305" t="n">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="Y305" t="n">
-        <v>1240</v>
+        <v>1380</v>
       </c>
       <c r="Z305" t="n">
-        <v>755</v>
+        <v>835</v>
       </c>
       <c r="AA305" t="n">
-        <v>699</v>
+        <v>740</v>
       </c>
       <c r="AB305" t="n">
-        <v>1280</v>
+        <v>1460</v>
       </c>
       <c r="AC305" t="n">
-        <v>833</v>
+        <v>911</v>
       </c>
       <c r="AD305" t="n">
-        <v>787</v>
+        <v>811</v>
       </c>
       <c r="AE305" t="n">
-        <v>1153</v>
+        <v>1232</v>
       </c>
       <c r="AF305" t="n">
-        <v>835.1900000000001</v>
+        <v>919.71</v>
       </c>
       <c r="AG305" t="n">
-        <v>865</v>
+        <v>950</v>
       </c>
       <c r="AH305" t="inlineStr"/>
       <c r="AI305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>757.66</v>
+      </c>
+      <c r="C306" t="n">
+        <v>769</v>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="n">
+        <v>675</v>
+      </c>
+      <c r="F306" t="n">
+        <v>1115</v>
+      </c>
+      <c r="G306" t="n">
+        <v>708</v>
+      </c>
+      <c r="H306" t="n">
+        <v>770</v>
+      </c>
+      <c r="I306" t="n">
+        <v>623</v>
+      </c>
+      <c r="J306" t="n">
+        <v>680</v>
+      </c>
+      <c r="K306" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L306" t="n">
+        <v>760</v>
+      </c>
+      <c r="M306" t="n">
+        <v>1421</v>
+      </c>
+      <c r="N306" t="n">
+        <v>765</v>
+      </c>
+      <c r="O306" t="n">
+        <v>700</v>
+      </c>
+      <c r="P306" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>815</v>
+      </c>
+      <c r="R306" t="n">
+        <v>706</v>
+      </c>
+      <c r="S306" t="n">
+        <v>1130</v>
+      </c>
+      <c r="T306" t="n">
+        <v>980</v>
+      </c>
+      <c r="U306" t="n">
+        <v>700</v>
+      </c>
+      <c r="V306" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="W306" t="n">
+        <v>770</v>
+      </c>
+      <c r="X306" t="n">
+        <v>700</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>1240</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>755</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>699</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>833</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>787</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>1153</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>835.1900000000001</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>865</v>
+      </c>
+      <c r="AH306" t="inlineStr"/>
+      <c r="AI306" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI306"/>
+  <dimension ref="A1:AI307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31556,6 +31556,109 @@
       <c r="AH306" t="inlineStr"/>
       <c r="AI306" t="inlineStr"/>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>753.21</v>
+      </c>
+      <c r="C307" t="n">
+        <v>774</v>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="n">
+        <v>662</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1145</v>
+      </c>
+      <c r="G307" t="n">
+        <v>723.25</v>
+      </c>
+      <c r="H307" t="n">
+        <v>805</v>
+      </c>
+      <c r="I307" t="n">
+        <v>636.25</v>
+      </c>
+      <c r="J307" t="n">
+        <v>700</v>
+      </c>
+      <c r="K307" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L307" t="n">
+        <v>759</v>
+      </c>
+      <c r="M307" t="n">
+        <v>1420</v>
+      </c>
+      <c r="N307" t="n">
+        <v>761</v>
+      </c>
+      <c r="O307" t="n">
+        <v>686</v>
+      </c>
+      <c r="P307" t="n">
+        <v>1240</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>785</v>
+      </c>
+      <c r="R307" t="n">
+        <v>690</v>
+      </c>
+      <c r="S307" t="n">
+        <v>1145</v>
+      </c>
+      <c r="T307" t="n">
+        <v>960</v>
+      </c>
+      <c r="U307" t="n">
+        <v>690</v>
+      </c>
+      <c r="V307" t="n">
+        <v>1257.25</v>
+      </c>
+      <c r="W307" t="n">
+        <v>766</v>
+      </c>
+      <c r="X307" t="n">
+        <v>686</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>1245</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>770</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>708</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>1315</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>847</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>797</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>1192</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>830.09</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>860</v>
+      </c>
+      <c r="AH307" t="inlineStr"/>
+      <c r="AI307" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI307"/>
+  <dimension ref="A1:AI308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31456,102 +31456,102 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>757.66</v>
+        <v>809.4400000000001</v>
       </c>
       <c r="C306" t="n">
-        <v>769</v>
+        <v>821</v>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="n">
+        <v>722</v>
+      </c>
+      <c r="F306" t="n">
+        <v>1201.25</v>
+      </c>
+      <c r="G306" t="n">
+        <v>736.5</v>
+      </c>
+      <c r="H306" t="n">
+        <v>785</v>
+      </c>
+      <c r="I306" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="J306" t="n">
         <v>675</v>
       </c>
-      <c r="F306" t="n">
-        <v>1115</v>
-      </c>
-      <c r="G306" t="n">
-        <v>708</v>
-      </c>
-      <c r="H306" t="n">
-        <v>770</v>
-      </c>
-      <c r="I306" t="n">
-        <v>623</v>
-      </c>
-      <c r="J306" t="n">
-        <v>680</v>
-      </c>
       <c r="K306" t="n">
-        <v>1150</v>
+        <v>1195</v>
       </c>
       <c r="L306" t="n">
-        <v>760</v>
+        <v>810</v>
       </c>
       <c r="M306" t="n">
-        <v>1421</v>
+        <v>1403</v>
       </c>
       <c r="N306" t="n">
+        <v>810</v>
+      </c>
+      <c r="O306" t="n">
+        <v>726</v>
+      </c>
+      <c r="P306" t="n">
+        <v>1330</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>895</v>
+      </c>
+      <c r="R306" t="n">
         <v>765</v>
       </c>
-      <c r="O306" t="n">
-        <v>700</v>
-      </c>
-      <c r="P306" t="n">
-        <v>1235</v>
-      </c>
-      <c r="Q306" t="n">
+      <c r="S306" t="n">
+        <v>1206</v>
+      </c>
+      <c r="T306" t="n">
+        <v>1060</v>
+      </c>
+      <c r="U306" t="n">
+        <v>736</v>
+      </c>
+      <c r="V306" t="n">
+        <v>1255</v>
+      </c>
+      <c r="W306" t="n">
         <v>815</v>
       </c>
-      <c r="R306" t="n">
-        <v>706</v>
-      </c>
-      <c r="S306" t="n">
-        <v>1130</v>
-      </c>
-      <c r="T306" t="n">
-        <v>980</v>
-      </c>
-      <c r="U306" t="n">
-        <v>700</v>
-      </c>
-      <c r="V306" t="n">
-        <v>1215.5</v>
-      </c>
-      <c r="W306" t="n">
-        <v>770</v>
-      </c>
       <c r="X306" t="n">
-        <v>700</v>
+        <v>726</v>
       </c>
       <c r="Y306" t="n">
-        <v>1240</v>
+        <v>1335</v>
       </c>
       <c r="Z306" t="n">
-        <v>755</v>
+        <v>795</v>
       </c>
       <c r="AA306" t="n">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="AB306" t="n">
-        <v>1280</v>
+        <v>1350</v>
       </c>
       <c r="AC306" t="n">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="AD306" t="n">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="AE306" t="n">
-        <v>1153</v>
+        <v>1172</v>
       </c>
       <c r="AF306" t="n">
-        <v>835.1900000000001</v>
+        <v>894.96</v>
       </c>
       <c r="AG306" t="n">
-        <v>865</v>
+        <v>925</v>
       </c>
       <c r="AH306" t="inlineStr"/>
       <c r="AI306" t="inlineStr"/>
@@ -31559,105 +31559,208 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>753.21</v>
+        <v>757.66</v>
       </c>
       <c r="C307" t="n">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="n">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="F307" t="n">
-        <v>1145</v>
+        <v>1115</v>
       </c>
       <c r="G307" t="n">
-        <v>723.25</v>
+        <v>708</v>
       </c>
       <c r="H307" t="n">
-        <v>805</v>
+        <v>770</v>
       </c>
       <c r="I307" t="n">
-        <v>636.25</v>
+        <v>623</v>
       </c>
       <c r="J307" t="n">
+        <v>680</v>
+      </c>
+      <c r="K307" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L307" t="n">
+        <v>760</v>
+      </c>
+      <c r="M307" t="n">
+        <v>1421</v>
+      </c>
+      <c r="N307" t="n">
+        <v>765</v>
+      </c>
+      <c r="O307" t="n">
         <v>700</v>
       </c>
-      <c r="K307" t="n">
-        <v>1195</v>
-      </c>
-      <c r="L307" t="n">
-        <v>759</v>
-      </c>
-      <c r="M307" t="n">
-        <v>1420</v>
-      </c>
-      <c r="N307" t="n">
-        <v>761</v>
-      </c>
-      <c r="O307" t="n">
-        <v>686</v>
-      </c>
       <c r="P307" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>815</v>
+      </c>
+      <c r="R307" t="n">
+        <v>706</v>
+      </c>
+      <c r="S307" t="n">
+        <v>1130</v>
+      </c>
+      <c r="T307" t="n">
+        <v>980</v>
+      </c>
+      <c r="U307" t="n">
+        <v>700</v>
+      </c>
+      <c r="V307" t="n">
+        <v>1215.5</v>
+      </c>
+      <c r="W307" t="n">
+        <v>770</v>
+      </c>
+      <c r="X307" t="n">
+        <v>700</v>
+      </c>
+      <c r="Y307" t="n">
         <v>1240</v>
       </c>
-      <c r="Q307" t="n">
-        <v>785</v>
-      </c>
-      <c r="R307" t="n">
-        <v>690</v>
-      </c>
-      <c r="S307" t="n">
-        <v>1145</v>
-      </c>
-      <c r="T307" t="n">
-        <v>960</v>
-      </c>
-      <c r="U307" t="n">
-        <v>690</v>
-      </c>
-      <c r="V307" t="n">
-        <v>1257.25</v>
-      </c>
-      <c r="W307" t="n">
-        <v>766</v>
-      </c>
-      <c r="X307" t="n">
-        <v>686</v>
-      </c>
-      <c r="Y307" t="n">
-        <v>1245</v>
-      </c>
       <c r="Z307" t="n">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="AA307" t="n">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="AB307" t="n">
-        <v>1315</v>
+        <v>1280</v>
       </c>
       <c r="AC307" t="n">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="AD307" t="n">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="AE307" t="n">
-        <v>1192</v>
+        <v>1153</v>
       </c>
       <c r="AF307" t="n">
-        <v>830.09</v>
+        <v>835.1900000000001</v>
       </c>
       <c r="AG307" t="n">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="AH307" t="inlineStr"/>
       <c r="AI307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>753.21</v>
+      </c>
+      <c r="C308" t="n">
+        <v>774</v>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="n">
+        <v>662</v>
+      </c>
+      <c r="F308" t="n">
+        <v>1145</v>
+      </c>
+      <c r="G308" t="n">
+        <v>723.25</v>
+      </c>
+      <c r="H308" t="n">
+        <v>805</v>
+      </c>
+      <c r="I308" t="n">
+        <v>636.25</v>
+      </c>
+      <c r="J308" t="n">
+        <v>700</v>
+      </c>
+      <c r="K308" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L308" t="n">
+        <v>759</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1420</v>
+      </c>
+      <c r="N308" t="n">
+        <v>761</v>
+      </c>
+      <c r="O308" t="n">
+        <v>686</v>
+      </c>
+      <c r="P308" t="n">
+        <v>1240</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>785</v>
+      </c>
+      <c r="R308" t="n">
+        <v>690</v>
+      </c>
+      <c r="S308" t="n">
+        <v>1145</v>
+      </c>
+      <c r="T308" t="n">
+        <v>960</v>
+      </c>
+      <c r="U308" t="n">
+        <v>690</v>
+      </c>
+      <c r="V308" t="n">
+        <v>1257.25</v>
+      </c>
+      <c r="W308" t="n">
+        <v>766</v>
+      </c>
+      <c r="X308" t="n">
+        <v>686</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>1245</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>770</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>708</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>1315</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>847</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>797</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>1192</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>830.09</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>860</v>
+      </c>
+      <c r="AH308" t="inlineStr"/>
+      <c r="AI308" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI308"/>
+  <dimension ref="A1:AI309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31762,6 +31762,109 @@
       <c r="AH308" t="inlineStr"/>
       <c r="AI308" t="inlineStr"/>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>775.39</v>
+      </c>
+      <c r="C309" t="n">
+        <v>796</v>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="n">
+        <v>675</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1175</v>
+      </c>
+      <c r="G309" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="H309" t="n">
+        <v>810</v>
+      </c>
+      <c r="I309" t="n">
+        <v>638.25</v>
+      </c>
+      <c r="J309" t="n">
+        <v>700</v>
+      </c>
+      <c r="K309" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L309" t="n">
+        <v>771</v>
+      </c>
+      <c r="M309" t="n">
+        <v>1425</v>
+      </c>
+      <c r="N309" t="n">
+        <v>778</v>
+      </c>
+      <c r="O309" t="n">
+        <v>683</v>
+      </c>
+      <c r="P309" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>815</v>
+      </c>
+      <c r="R309" t="n">
+        <v>703</v>
+      </c>
+      <c r="S309" t="n">
+        <v>1159</v>
+      </c>
+      <c r="T309" t="n">
+        <v>1025</v>
+      </c>
+      <c r="U309" t="n">
+        <v>703</v>
+      </c>
+      <c r="V309" t="n">
+        <v>1280.75</v>
+      </c>
+      <c r="W309" t="n">
+        <v>783</v>
+      </c>
+      <c r="X309" t="n">
+        <v>683</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>1240</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>805</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>715</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>1310</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>848</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>804</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>1217</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>839.97</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>865</v>
+      </c>
+      <c r="AH309" t="inlineStr"/>
+      <c r="AI309" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI309"/>
+  <dimension ref="A1:AI310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31865,6 +31865,109 @@
       <c r="AH309" t="inlineStr"/>
       <c r="AI309" t="inlineStr"/>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>809.14</v>
+      </c>
+      <c r="C310" t="n">
+        <v>831</v>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="n">
+        <v>683</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1191</v>
+      </c>
+      <c r="G310" t="n">
+        <v>684.75</v>
+      </c>
+      <c r="H310" t="n">
+        <v>792</v>
+      </c>
+      <c r="I310" t="n">
+        <v>647.5</v>
+      </c>
+      <c r="J310" t="n">
+        <v>698</v>
+      </c>
+      <c r="K310" t="n">
+        <v>1220</v>
+      </c>
+      <c r="L310" t="n">
+        <v>815</v>
+      </c>
+      <c r="M310" t="n">
+        <v>1426</v>
+      </c>
+      <c r="N310" t="n">
+        <v>798</v>
+      </c>
+      <c r="O310" t="n">
+        <v>687</v>
+      </c>
+      <c r="P310" t="n">
+        <v>1230</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>849</v>
+      </c>
+      <c r="R310" t="n">
+        <v>718.5</v>
+      </c>
+      <c r="S310" t="n">
+        <v>1185</v>
+      </c>
+      <c r="T310" t="n">
+        <v>1080</v>
+      </c>
+      <c r="U310" t="n">
+        <v>711</v>
+      </c>
+      <c r="V310" t="n">
+        <v>1349.75</v>
+      </c>
+      <c r="W310" t="n">
+        <v>803</v>
+      </c>
+      <c r="X310" t="n">
+        <v>687</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>780</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>730</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>1325</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>866</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>809</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>1247</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>874.96</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>900</v>
+      </c>
+      <c r="AH310" t="inlineStr"/>
+      <c r="AI310" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI310"/>
+  <dimension ref="A1:AI311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31968,6 +31968,109 @@
       <c r="AH310" t="inlineStr"/>
       <c r="AI310" t="inlineStr"/>
     </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>798.09</v>
+      </c>
+      <c r="C311" t="n">
+        <v>826</v>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="n">
+        <v>675</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G311" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="H311" t="n">
+        <v>765</v>
+      </c>
+      <c r="I311" t="n">
+        <v>650.25</v>
+      </c>
+      <c r="J311" t="n">
+        <v>680</v>
+      </c>
+      <c r="K311" t="n">
+        <v>1215</v>
+      </c>
+      <c r="L311" t="n">
+        <v>805</v>
+      </c>
+      <c r="M311" t="n">
+        <v>1421</v>
+      </c>
+      <c r="N311" t="n">
+        <v>797</v>
+      </c>
+      <c r="O311" t="n">
+        <v>680</v>
+      </c>
+      <c r="P311" t="n">
+        <v>1255</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>855</v>
+      </c>
+      <c r="R311" t="n">
+        <v>700</v>
+      </c>
+      <c r="S311" t="n">
+        <v>1223</v>
+      </c>
+      <c r="T311" t="n">
+        <v>1080</v>
+      </c>
+      <c r="U311" t="n">
+        <v>710</v>
+      </c>
+      <c r="V311" t="n">
+        <v>1315</v>
+      </c>
+      <c r="W311" t="n">
+        <v>801</v>
+      </c>
+      <c r="X311" t="n">
+        <v>680</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>1260</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>780</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>735</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>1335</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>864</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>805</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>1227</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>844.95</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>870</v>
+      </c>
+      <c r="AH311" t="inlineStr"/>
+      <c r="AI311" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI311"/>
+  <dimension ref="A1:AI312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32071,6 +32071,109 @@
       <c r="AH311" t="inlineStr"/>
       <c r="AI311" t="inlineStr"/>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>803.96</v>
+      </c>
+      <c r="C312" t="n">
+        <v>831</v>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="F312" t="n">
+        <v>1205</v>
+      </c>
+      <c r="G312" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="H312" t="n">
+        <v>752</v>
+      </c>
+      <c r="I312" t="n">
+        <v>641.25</v>
+      </c>
+      <c r="J312" t="n">
+        <v>682</v>
+      </c>
+      <c r="K312" t="n">
+        <v>1178</v>
+      </c>
+      <c r="L312" t="n">
+        <v>801</v>
+      </c>
+      <c r="M312" t="n">
+        <v>1420</v>
+      </c>
+      <c r="N312" t="n">
+        <v>798</v>
+      </c>
+      <c r="O312" t="n">
+        <v>688</v>
+      </c>
+      <c r="P312" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>861</v>
+      </c>
+      <c r="R312" t="n">
+        <v>701</v>
+      </c>
+      <c r="S312" t="n">
+        <v>1210</v>
+      </c>
+      <c r="T312" t="n">
+        <v>1090</v>
+      </c>
+      <c r="U312" t="n">
+        <v>715</v>
+      </c>
+      <c r="V312" t="n">
+        <v>1288.25</v>
+      </c>
+      <c r="W312" t="n">
+        <v>798</v>
+      </c>
+      <c r="X312" t="n">
+        <v>688</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>1255</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>780</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>1308</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>851</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>806</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>1201</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>854.91</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>880</v>
+      </c>
+      <c r="AH312" t="inlineStr"/>
+      <c r="AI312" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI312"/>
+  <dimension ref="A1:AI313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32174,6 +32174,109 @@
       <c r="AH312" t="inlineStr"/>
       <c r="AI312" t="inlineStr"/>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>823.95</v>
+      </c>
+      <c r="C313" t="n">
+        <v>851</v>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="n">
+        <v>713</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1239.25</v>
+      </c>
+      <c r="G313" t="n">
+        <v>715.75</v>
+      </c>
+      <c r="H313" t="n">
+        <v>775</v>
+      </c>
+      <c r="I313" t="n">
+        <v>664</v>
+      </c>
+      <c r="J313" t="n">
+        <v>704</v>
+      </c>
+      <c r="K313" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L313" t="n">
+        <v>823</v>
+      </c>
+      <c r="M313" t="n">
+        <v>1421</v>
+      </c>
+      <c r="N313" t="n">
+        <v>820</v>
+      </c>
+      <c r="O313" t="n">
+        <v>710</v>
+      </c>
+      <c r="P313" t="n">
+        <v>1255</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>875</v>
+      </c>
+      <c r="R313" t="n">
+        <v>720</v>
+      </c>
+      <c r="S313" t="n">
+        <v>1215</v>
+      </c>
+      <c r="T313" t="n">
+        <v>1095</v>
+      </c>
+      <c r="U313" t="n">
+        <v>740</v>
+      </c>
+      <c r="V313" t="n">
+        <v>1295</v>
+      </c>
+      <c r="W313" t="n">
+        <v>820</v>
+      </c>
+      <c r="X313" t="n">
+        <v>710</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>1260</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>789</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>735</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>1310</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>861</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>814</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>1224</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>884.89</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>905</v>
+      </c>
+      <c r="AH313" t="inlineStr"/>
+      <c r="AI313" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI313"/>
+  <dimension ref="A1:AI314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32277,6 +32277,109 @@
       <c r="AH313" t="inlineStr"/>
       <c r="AI313" t="inlineStr"/>
     </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>849.3099999999999</v>
+      </c>
+      <c r="C314" t="n">
+        <v>875</v>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="n">
+        <v>719</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1235.25</v>
+      </c>
+      <c r="G314" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="H314" t="n">
+        <v>794</v>
+      </c>
+      <c r="I314" t="n">
+        <v>680</v>
+      </c>
+      <c r="J314" t="n">
+        <v>715</v>
+      </c>
+      <c r="K314" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L314" t="n">
+        <v>860</v>
+      </c>
+      <c r="M314" t="n">
+        <v>1396</v>
+      </c>
+      <c r="N314" t="n">
+        <v>850</v>
+      </c>
+      <c r="O314" t="n">
+        <v>730</v>
+      </c>
+      <c r="P314" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>895</v>
+      </c>
+      <c r="R314" t="n">
+        <v>737</v>
+      </c>
+      <c r="S314" t="n">
+        <v>1227</v>
+      </c>
+      <c r="T314" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U314" t="n">
+        <v>745</v>
+      </c>
+      <c r="V314" t="n">
+        <v>1300</v>
+      </c>
+      <c r="W314" t="n">
+        <v>855</v>
+      </c>
+      <c r="X314" t="n">
+        <v>730</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>807</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>743</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>1335</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>872</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>818</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>1232</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>924.98</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>940</v>
+      </c>
+      <c r="AH314" t="inlineStr"/>
+      <c r="AI314" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI314"/>
+  <dimension ref="A1:AI315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32380,6 +32380,109 @@
       <c r="AH314" t="inlineStr"/>
       <c r="AI314" t="inlineStr"/>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>804.96</v>
+      </c>
+      <c r="C315" t="n">
+        <v>823</v>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="n">
+        <v>672</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G315" t="n">
+        <v>683.5</v>
+      </c>
+      <c r="H315" t="n">
+        <v>723</v>
+      </c>
+      <c r="I315" t="n">
+        <v>612</v>
+      </c>
+      <c r="J315" t="n">
+        <v>668</v>
+      </c>
+      <c r="K315" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L315" t="n">
+        <v>820</v>
+      </c>
+      <c r="M315" t="n">
+        <v>1398</v>
+      </c>
+      <c r="N315" t="n">
+        <v>813</v>
+      </c>
+      <c r="O315" t="n">
+        <v>690</v>
+      </c>
+      <c r="P315" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>927.5</v>
+      </c>
+      <c r="R315" t="n">
+        <v>699</v>
+      </c>
+      <c r="S315" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="T315" t="n">
+        <v>850</v>
+      </c>
+      <c r="U315" t="n">
+        <v>705</v>
+      </c>
+      <c r="V315" t="n">
+        <v>1227.5</v>
+      </c>
+      <c r="W315" t="n">
+        <v>815</v>
+      </c>
+      <c r="X315" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>1205</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>760</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>705</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>1270</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>827</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>775</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>1183</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>889.92</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>910</v>
+      </c>
+      <c r="AH315" t="inlineStr"/>
+      <c r="AI315" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI315"/>
+  <dimension ref="A1:AI316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32383,105 +32383,208 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>804.96</v>
+        <v>785.8200000000001</v>
       </c>
       <c r="C315" t="n">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="n">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="F315" t="n">
-        <v>1176</v>
+        <v>1160</v>
       </c>
       <c r="G315" t="n">
-        <v>683.5</v>
+        <v>686.75</v>
       </c>
       <c r="H315" t="n">
-        <v>723</v>
+        <v>745</v>
       </c>
       <c r="I315" t="n">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="J315" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="K315" t="n">
-        <v>1140</v>
+        <v>1190</v>
       </c>
       <c r="L315" t="n">
-        <v>820</v>
+        <v>859</v>
       </c>
       <c r="M315" t="n">
-        <v>1398</v>
+        <v>1377</v>
       </c>
       <c r="N315" t="n">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="O315" t="n">
+        <v>675</v>
+      </c>
+      <c r="P315" t="n">
+        <v>1220</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>875</v>
+      </c>
+      <c r="R315" t="n">
         <v>690</v>
       </c>
-      <c r="P315" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Q315" t="n">
-        <v>927.5</v>
-      </c>
-      <c r="R315" t="n">
-        <v>699</v>
-      </c>
       <c r="S315" t="n">
-        <v>1161.5</v>
+        <v>1175</v>
       </c>
       <c r="T315" t="n">
-        <v>850</v>
+        <v>915</v>
       </c>
       <c r="U315" t="n">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="V315" t="n">
-        <v>1227.5</v>
+        <v>1217.75</v>
       </c>
       <c r="W315" t="n">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="X315" t="n">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="Y315" t="n">
-        <v>1205</v>
+        <v>1225</v>
       </c>
       <c r="Z315" t="n">
         <v>760</v>
       </c>
       <c r="AA315" t="n">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AB315" t="n">
-        <v>1270</v>
+        <v>1285</v>
       </c>
       <c r="AC315" t="n">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AD315" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AE315" t="n">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AF315" t="n">
-        <v>889.92</v>
+        <v>869.88</v>
       </c>
       <c r="AG315" t="n">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="AH315" t="inlineStr"/>
       <c r="AI315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>804.96</v>
+      </c>
+      <c r="C316" t="n">
+        <v>823</v>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="n">
+        <v>672</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G316" t="n">
+        <v>683.5</v>
+      </c>
+      <c r="H316" t="n">
+        <v>723</v>
+      </c>
+      <c r="I316" t="n">
+        <v>612</v>
+      </c>
+      <c r="J316" t="n">
+        <v>668</v>
+      </c>
+      <c r="K316" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L316" t="n">
+        <v>820</v>
+      </c>
+      <c r="M316" t="n">
+        <v>1398</v>
+      </c>
+      <c r="N316" t="n">
+        <v>813</v>
+      </c>
+      <c r="O316" t="n">
+        <v>690</v>
+      </c>
+      <c r="P316" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>927.5</v>
+      </c>
+      <c r="R316" t="n">
+        <v>699</v>
+      </c>
+      <c r="S316" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="T316" t="n">
+        <v>850</v>
+      </c>
+      <c r="U316" t="n">
+        <v>705</v>
+      </c>
+      <c r="V316" t="n">
+        <v>1227.5</v>
+      </c>
+      <c r="W316" t="n">
+        <v>815</v>
+      </c>
+      <c r="X316" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>1205</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>760</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>705</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>1270</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>827</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>775</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>1183</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>889.92</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>910</v>
+      </c>
+      <c r="AH316" t="inlineStr"/>
+      <c r="AI316" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI316"/>
+  <dimension ref="A1:AI317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32383,102 +32383,102 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>785.8200000000001</v>
+        <v>817.6</v>
       </c>
       <c r="C315" t="n">
-        <v>808</v>
+        <v>842</v>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="n">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="F315" t="n">
-        <v>1160</v>
+        <v>1220</v>
       </c>
       <c r="G315" t="n">
-        <v>686.75</v>
+        <v>677.75</v>
       </c>
       <c r="H315" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I315" t="n">
-        <v>629</v>
+        <v>629.75</v>
       </c>
       <c r="J315" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="K315" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="L315" t="n">
-        <v>859</v>
+        <v>829</v>
       </c>
       <c r="M315" t="n">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="N315" t="n">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="O315" t="n">
-        <v>675</v>
+        <v>701</v>
       </c>
       <c r="P315" t="n">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="Q315" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="R315" t="n">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="S315" t="n">
-        <v>1175</v>
+        <v>1225</v>
       </c>
       <c r="T315" t="n">
+        <v>955</v>
+      </c>
+      <c r="U315" t="n">
+        <v>730</v>
+      </c>
+      <c r="V315" t="n">
+        <v>1275.5</v>
+      </c>
+      <c r="W315" t="n">
+        <v>830</v>
+      </c>
+      <c r="X315" t="n">
+        <v>701</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>768</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>718</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>1315</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>827</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>777</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>1192</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>894.89</v>
+      </c>
+      <c r="AG315" t="n">
         <v>915</v>
-      </c>
-      <c r="U315" t="n">
-        <v>700</v>
-      </c>
-      <c r="V315" t="n">
-        <v>1217.75</v>
-      </c>
-      <c r="W315" t="n">
-        <v>800</v>
-      </c>
-      <c r="X315" t="n">
-        <v>675</v>
-      </c>
-      <c r="Y315" t="n">
-        <v>1225</v>
-      </c>
-      <c r="Z315" t="n">
-        <v>760</v>
-      </c>
-      <c r="AA315" t="n">
-        <v>698</v>
-      </c>
-      <c r="AB315" t="n">
-        <v>1285</v>
-      </c>
-      <c r="AC315" t="n">
-        <v>826</v>
-      </c>
-      <c r="AD315" t="n">
-        <v>774</v>
-      </c>
-      <c r="AE315" t="n">
-        <v>1182</v>
-      </c>
-      <c r="AF315" t="n">
-        <v>869.88</v>
-      </c>
-      <c r="AG315" t="n">
-        <v>890</v>
       </c>
       <c r="AH315" t="inlineStr"/>
       <c r="AI315" t="inlineStr"/>
@@ -32486,105 +32486,208 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>804.96</v>
+        <v>785.8200000000001</v>
       </c>
       <c r="C316" t="n">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="n">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="F316" t="n">
-        <v>1176</v>
+        <v>1160</v>
       </c>
       <c r="G316" t="n">
-        <v>683.5</v>
+        <v>686.75</v>
       </c>
       <c r="H316" t="n">
-        <v>723</v>
+        <v>745</v>
       </c>
       <c r="I316" t="n">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="J316" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="K316" t="n">
-        <v>1140</v>
+        <v>1190</v>
       </c>
       <c r="L316" t="n">
-        <v>820</v>
+        <v>859</v>
       </c>
       <c r="M316" t="n">
-        <v>1398</v>
+        <v>1377</v>
       </c>
       <c r="N316" t="n">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="O316" t="n">
+        <v>675</v>
+      </c>
+      <c r="P316" t="n">
+        <v>1220</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>875</v>
+      </c>
+      <c r="R316" t="n">
         <v>690</v>
       </c>
-      <c r="P316" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Q316" t="n">
-        <v>927.5</v>
-      </c>
-      <c r="R316" t="n">
-        <v>699</v>
-      </c>
       <c r="S316" t="n">
-        <v>1161.5</v>
+        <v>1175</v>
       </c>
       <c r="T316" t="n">
-        <v>850</v>
+        <v>915</v>
       </c>
       <c r="U316" t="n">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="V316" t="n">
-        <v>1227.5</v>
+        <v>1217.75</v>
       </c>
       <c r="W316" t="n">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="X316" t="n">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="Y316" t="n">
-        <v>1205</v>
+        <v>1225</v>
       </c>
       <c r="Z316" t="n">
         <v>760</v>
       </c>
       <c r="AA316" t="n">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AB316" t="n">
-        <v>1270</v>
+        <v>1285</v>
       </c>
       <c r="AC316" t="n">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AD316" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AE316" t="n">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AF316" t="n">
-        <v>889.92</v>
+        <v>869.88</v>
       </c>
       <c r="AG316" t="n">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="AH316" t="inlineStr"/>
       <c r="AI316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>804.96</v>
+      </c>
+      <c r="C317" t="n">
+        <v>823</v>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="n">
+        <v>672</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G317" t="n">
+        <v>683.5</v>
+      </c>
+      <c r="H317" t="n">
+        <v>723</v>
+      </c>
+      <c r="I317" t="n">
+        <v>612</v>
+      </c>
+      <c r="J317" t="n">
+        <v>668</v>
+      </c>
+      <c r="K317" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L317" t="n">
+        <v>820</v>
+      </c>
+      <c r="M317" t="n">
+        <v>1398</v>
+      </c>
+      <c r="N317" t="n">
+        <v>813</v>
+      </c>
+      <c r="O317" t="n">
+        <v>690</v>
+      </c>
+      <c r="P317" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>927.5</v>
+      </c>
+      <c r="R317" t="n">
+        <v>699</v>
+      </c>
+      <c r="S317" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="T317" t="n">
+        <v>850</v>
+      </c>
+      <c r="U317" t="n">
+        <v>705</v>
+      </c>
+      <c r="V317" t="n">
+        <v>1227.5</v>
+      </c>
+      <c r="W317" t="n">
+        <v>815</v>
+      </c>
+      <c r="X317" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>1205</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>760</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>705</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>1270</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>827</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>775</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>1183</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>889.92</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>910</v>
+      </c>
+      <c r="AH317" t="inlineStr"/>
+      <c r="AI317" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI317"/>
+  <dimension ref="A1:AI318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32383,102 +32383,102 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>817.6</v>
+        <v>839.86</v>
       </c>
       <c r="C315" t="n">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="n">
-        <v>692</v>
+        <v>715</v>
       </c>
       <c r="F315" t="n">
-        <v>1220</v>
+        <v>1259.25</v>
       </c>
       <c r="G315" t="n">
-        <v>677.75</v>
+        <v>688.5</v>
       </c>
       <c r="H315" t="n">
-        <v>746</v>
+        <v>779</v>
       </c>
       <c r="I315" t="n">
-        <v>629.75</v>
+        <v>667.75</v>
       </c>
       <c r="J315" t="n">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="K315" t="n">
-        <v>1220</v>
+        <v>1250</v>
       </c>
       <c r="L315" t="n">
-        <v>829</v>
+        <v>839</v>
       </c>
       <c r="M315" t="n">
-        <v>1382</v>
+        <v>1397</v>
       </c>
       <c r="N315" t="n">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="O315" t="n">
-        <v>701</v>
+        <v>724</v>
       </c>
       <c r="P315" t="n">
-        <v>1265</v>
+        <v>1285</v>
       </c>
       <c r="Q315" t="n">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="R315" t="n">
-        <v>707</v>
+        <v>730</v>
       </c>
       <c r="S315" t="n">
-        <v>1225</v>
+        <v>1245</v>
       </c>
       <c r="T315" t="n">
-        <v>955</v>
+        <v>990</v>
       </c>
       <c r="U315" t="n">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="V315" t="n">
-        <v>1275.5</v>
+        <v>1363</v>
       </c>
       <c r="W315" t="n">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="X315" t="n">
-        <v>701</v>
+        <v>724</v>
       </c>
       <c r="Y315" t="n">
-        <v>1270</v>
+        <v>1290</v>
       </c>
       <c r="Z315" t="n">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="AA315" t="n">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="AB315" t="n">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="AC315" t="n">
-        <v>827</v>
+        <v>862</v>
       </c>
       <c r="AD315" t="n">
-        <v>777</v>
+        <v>811</v>
       </c>
       <c r="AE315" t="n">
-        <v>1192</v>
+        <v>1217</v>
       </c>
       <c r="AF315" t="n">
-        <v>894.89</v>
+        <v>920.05</v>
       </c>
       <c r="AG315" t="n">
-        <v>915</v>
+        <v>940</v>
       </c>
       <c r="AH315" t="inlineStr"/>
       <c r="AI315" t="inlineStr"/>
@@ -32486,102 +32486,102 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>785.8200000000001</v>
+        <v>817.6</v>
       </c>
       <c r="C316" t="n">
-        <v>808</v>
+        <v>842</v>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="n">
-        <v>663</v>
+        <v>692</v>
       </c>
       <c r="F316" t="n">
-        <v>1160</v>
+        <v>1220</v>
       </c>
       <c r="G316" t="n">
-        <v>686.75</v>
+        <v>677.75</v>
       </c>
       <c r="H316" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I316" t="n">
-        <v>629</v>
+        <v>629.75</v>
       </c>
       <c r="J316" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="K316" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="L316" t="n">
-        <v>859</v>
+        <v>829</v>
       </c>
       <c r="M316" t="n">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="N316" t="n">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="O316" t="n">
-        <v>675</v>
+        <v>701</v>
       </c>
       <c r="P316" t="n">
-        <v>1220</v>
+        <v>1265</v>
       </c>
       <c r="Q316" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="R316" t="n">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="S316" t="n">
-        <v>1175</v>
+        <v>1225</v>
       </c>
       <c r="T316" t="n">
+        <v>955</v>
+      </c>
+      <c r="U316" t="n">
+        <v>730</v>
+      </c>
+      <c r="V316" t="n">
+        <v>1275.5</v>
+      </c>
+      <c r="W316" t="n">
+        <v>830</v>
+      </c>
+      <c r="X316" t="n">
+        <v>701</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>768</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>718</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>1315</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>827</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>777</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>1192</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>894.89</v>
+      </c>
+      <c r="AG316" t="n">
         <v>915</v>
-      </c>
-      <c r="U316" t="n">
-        <v>700</v>
-      </c>
-      <c r="V316" t="n">
-        <v>1217.75</v>
-      </c>
-      <c r="W316" t="n">
-        <v>800</v>
-      </c>
-      <c r="X316" t="n">
-        <v>675</v>
-      </c>
-      <c r="Y316" t="n">
-        <v>1225</v>
-      </c>
-      <c r="Z316" t="n">
-        <v>760</v>
-      </c>
-      <c r="AA316" t="n">
-        <v>698</v>
-      </c>
-      <c r="AB316" t="n">
-        <v>1285</v>
-      </c>
-      <c r="AC316" t="n">
-        <v>826</v>
-      </c>
-      <c r="AD316" t="n">
-        <v>774</v>
-      </c>
-      <c r="AE316" t="n">
-        <v>1182</v>
-      </c>
-      <c r="AF316" t="n">
-        <v>869.88</v>
-      </c>
-      <c r="AG316" t="n">
-        <v>890</v>
       </c>
       <c r="AH316" t="inlineStr"/>
       <c r="AI316" t="inlineStr"/>
@@ -32589,105 +32589,208 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>804.96</v>
+        <v>785.8200000000001</v>
       </c>
       <c r="C317" t="n">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="n">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="F317" t="n">
-        <v>1176</v>
+        <v>1160</v>
       </c>
       <c r="G317" t="n">
-        <v>683.5</v>
+        <v>686.75</v>
       </c>
       <c r="H317" t="n">
-        <v>723</v>
+        <v>745</v>
       </c>
       <c r="I317" t="n">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="J317" t="n">
-        <v>668</v>
+        <v>692</v>
       </c>
       <c r="K317" t="n">
-        <v>1140</v>
+        <v>1190</v>
       </c>
       <c r="L317" t="n">
-        <v>820</v>
+        <v>859</v>
       </c>
       <c r="M317" t="n">
-        <v>1398</v>
+        <v>1377</v>
       </c>
       <c r="N317" t="n">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="O317" t="n">
+        <v>675</v>
+      </c>
+      <c r="P317" t="n">
+        <v>1220</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>875</v>
+      </c>
+      <c r="R317" t="n">
         <v>690</v>
       </c>
-      <c r="P317" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Q317" t="n">
-        <v>927.5</v>
-      </c>
-      <c r="R317" t="n">
-        <v>699</v>
-      </c>
       <c r="S317" t="n">
-        <v>1161.5</v>
+        <v>1175</v>
       </c>
       <c r="T317" t="n">
-        <v>850</v>
+        <v>915</v>
       </c>
       <c r="U317" t="n">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="V317" t="n">
-        <v>1227.5</v>
+        <v>1217.75</v>
       </c>
       <c r="W317" t="n">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="X317" t="n">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="Y317" t="n">
-        <v>1205</v>
+        <v>1225</v>
       </c>
       <c r="Z317" t="n">
         <v>760</v>
       </c>
       <c r="AA317" t="n">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AB317" t="n">
-        <v>1270</v>
+        <v>1285</v>
       </c>
       <c r="AC317" t="n">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AD317" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AE317" t="n">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="AF317" t="n">
-        <v>889.92</v>
+        <v>869.88</v>
       </c>
       <c r="AG317" t="n">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="AH317" t="inlineStr"/>
       <c r="AI317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>804.96</v>
+      </c>
+      <c r="C318" t="n">
+        <v>823</v>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="n">
+        <v>672</v>
+      </c>
+      <c r="F318" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G318" t="n">
+        <v>683.5</v>
+      </c>
+      <c r="H318" t="n">
+        <v>723</v>
+      </c>
+      <c r="I318" t="n">
+        <v>612</v>
+      </c>
+      <c r="J318" t="n">
+        <v>668</v>
+      </c>
+      <c r="K318" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L318" t="n">
+        <v>820</v>
+      </c>
+      <c r="M318" t="n">
+        <v>1398</v>
+      </c>
+      <c r="N318" t="n">
+        <v>813</v>
+      </c>
+      <c r="O318" t="n">
+        <v>690</v>
+      </c>
+      <c r="P318" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>927.5</v>
+      </c>
+      <c r="R318" t="n">
+        <v>699</v>
+      </c>
+      <c r="S318" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="T318" t="n">
+        <v>850</v>
+      </c>
+      <c r="U318" t="n">
+        <v>705</v>
+      </c>
+      <c r="V318" t="n">
+        <v>1227.5</v>
+      </c>
+      <c r="W318" t="n">
+        <v>815</v>
+      </c>
+      <c r="X318" t="n">
+        <v>690</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>1205</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>760</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>705</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>1270</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>827</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>775</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>1183</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>889.92</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>910</v>
+      </c>
+      <c r="AH318" t="inlineStr"/>
+      <c r="AI318" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI318"/>
+  <dimension ref="A1:AI319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32792,6 +32792,109 @@
       <c r="AH318" t="inlineStr"/>
       <c r="AI318" t="inlineStr"/>
     </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>766.04</v>
+      </c>
+      <c r="C319" t="n">
+        <v>783</v>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="n">
+        <v>631</v>
+      </c>
+      <c r="F319" t="n">
+        <v>1101</v>
+      </c>
+      <c r="G319" t="n">
+        <v>660.75</v>
+      </c>
+      <c r="H319" t="n">
+        <v>700</v>
+      </c>
+      <c r="I319" t="n">
+        <v>589</v>
+      </c>
+      <c r="J319" t="n">
+        <v>630</v>
+      </c>
+      <c r="K319" t="n">
+        <v>1090</v>
+      </c>
+      <c r="L319" t="n">
+        <v>775</v>
+      </c>
+      <c r="M319" t="n">
+        <v>1402</v>
+      </c>
+      <c r="N319" t="n">
+        <v>783</v>
+      </c>
+      <c r="O319" t="n">
+        <v>653</v>
+      </c>
+      <c r="P319" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>856</v>
+      </c>
+      <c r="R319" t="n">
+        <v>662</v>
+      </c>
+      <c r="S319" t="n">
+        <v>1115</v>
+      </c>
+      <c r="T319" t="n">
+        <v>780</v>
+      </c>
+      <c r="U319" t="n">
+        <v>667</v>
+      </c>
+      <c r="V319" t="n">
+        <v>1112.75</v>
+      </c>
+      <c r="W319" t="n">
+        <v>790</v>
+      </c>
+      <c r="X319" t="n">
+        <v>653</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>1155</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>740</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>675</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>816</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>768</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>1157</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>904.91</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>925</v>
+      </c>
+      <c r="AH319" t="inlineStr"/>
+      <c r="AI319" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI319"/>
+  <dimension ref="A1:AI320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32895,6 +32895,73 @@
       <c r="AH319" t="inlineStr"/>
       <c r="AI319" t="inlineStr"/>
     </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="n">
+        <v>644.25</v>
+      </c>
+      <c r="H320" t="n">
+        <v>685</v>
+      </c>
+      <c r="I320" t="n">
+        <v>569.5</v>
+      </c>
+      <c r="J320" t="n">
+        <v>605</v>
+      </c>
+      <c r="K320" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L320" t="n">
+        <v>760</v>
+      </c>
+      <c r="M320" t="n">
+        <v>1399</v>
+      </c>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr"/>
+      <c r="S320" t="inlineStr"/>
+      <c r="T320" t="inlineStr"/>
+      <c r="U320" t="inlineStr"/>
+      <c r="V320" t="inlineStr"/>
+      <c r="W320" t="inlineStr"/>
+      <c r="X320" t="inlineStr"/>
+      <c r="Y320" t="inlineStr"/>
+      <c r="Z320" t="n">
+        <v>720</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>665</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>1170</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>799</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>758</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>1132</v>
+      </c>
+      <c r="AF320" t="inlineStr"/>
+      <c r="AG320" t="inlineStr"/>
+      <c r="AH320" t="inlineStr"/>
+      <c r="AI320" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI320"/>
+  <dimension ref="A1:AI321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32962,6 +32962,109 @@
       <c r="AH320" t="inlineStr"/>
       <c r="AI320" t="inlineStr"/>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>757.67</v>
+      </c>
+      <c r="C321" t="n">
+        <v>776</v>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="n">
+        <v>634</v>
+      </c>
+      <c r="F321" t="n">
+        <v>1070.75</v>
+      </c>
+      <c r="G321" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="H321" t="n">
+        <v>700</v>
+      </c>
+      <c r="I321" t="n">
+        <v>573.25</v>
+      </c>
+      <c r="J321" t="n">
+        <v>615</v>
+      </c>
+      <c r="K321" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L321" t="n">
+        <v>750</v>
+      </c>
+      <c r="M321" t="n">
+        <v>1402</v>
+      </c>
+      <c r="N321" t="n">
+        <v>772</v>
+      </c>
+      <c r="O321" t="n">
+        <v>658</v>
+      </c>
+      <c r="P321" t="n">
+        <v>1120</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>848</v>
+      </c>
+      <c r="R321" t="n">
+        <v>640</v>
+      </c>
+      <c r="S321" t="n">
+        <v>1075</v>
+      </c>
+      <c r="T321" t="n">
+        <v>769</v>
+      </c>
+      <c r="U321" t="n">
+        <v>669</v>
+      </c>
+      <c r="V321" t="n">
+        <v>1082.75</v>
+      </c>
+      <c r="W321" t="n">
+        <v>777</v>
+      </c>
+      <c r="X321" t="n">
+        <v>658</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>1125</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>715</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>665</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>781</v>
+      </c>
+      <c r="AD321" t="n">
+        <v>723</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>1076</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>980.11</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH321" t="inlineStr"/>
+      <c r="AI321" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI321"/>
+  <dimension ref="A1:AI322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33065,6 +33065,109 @@
       <c r="AH321" t="inlineStr"/>
       <c r="AI321" t="inlineStr"/>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>743.53</v>
+      </c>
+      <c r="C322" t="n">
+        <v>767</v>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="n">
+        <v>627</v>
+      </c>
+      <c r="F322" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G322" t="n">
+        <v>639.25</v>
+      </c>
+      <c r="H322" t="n">
+        <v>700</v>
+      </c>
+      <c r="I322" t="n">
+        <v>552</v>
+      </c>
+      <c r="J322" t="n">
+        <v>605</v>
+      </c>
+      <c r="K322" t="n">
+        <v>1030</v>
+      </c>
+      <c r="L322" t="n">
+        <v>749</v>
+      </c>
+      <c r="M322" t="n">
+        <v>1395</v>
+      </c>
+      <c r="N322" t="n">
+        <v>758</v>
+      </c>
+      <c r="O322" t="n">
+        <v>650</v>
+      </c>
+      <c r="P322" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>838</v>
+      </c>
+      <c r="R322" t="n">
+        <v>632</v>
+      </c>
+      <c r="S322" t="n">
+        <v>1052</v>
+      </c>
+      <c r="T322" t="n">
+        <v>760</v>
+      </c>
+      <c r="U322" t="n">
+        <v>662</v>
+      </c>
+      <c r="V322" t="n">
+        <v>1048.25</v>
+      </c>
+      <c r="W322" t="n">
+        <v>763</v>
+      </c>
+      <c r="X322" t="n">
+        <v>650</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>1105</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>690</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>650</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>1120</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>771</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>705</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>1087</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>980.04</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH322" t="inlineStr"/>
+      <c r="AI322" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI322"/>
+  <dimension ref="A1:AI323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33168,6 +33168,73 @@
       <c r="AH322" t="inlineStr"/>
       <c r="AI322" t="inlineStr"/>
     </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="n">
+        <v>642.25</v>
+      </c>
+      <c r="H323" t="n">
+        <v>725</v>
+      </c>
+      <c r="I323" t="n">
+        <v>581</v>
+      </c>
+      <c r="J323" t="n">
+        <v>622</v>
+      </c>
+      <c r="K323" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L323" t="n">
+        <v>758</v>
+      </c>
+      <c r="M323" t="n">
+        <v>1408</v>
+      </c>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
+      <c r="S323" t="inlineStr"/>
+      <c r="T323" t="inlineStr"/>
+      <c r="U323" t="inlineStr"/>
+      <c r="V323" t="inlineStr"/>
+      <c r="W323" t="inlineStr"/>
+      <c r="X323" t="inlineStr"/>
+      <c r="Y323" t="inlineStr"/>
+      <c r="Z323" t="n">
+        <v>730</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>670</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>1175</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>786</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>715</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>1132</v>
+      </c>
+      <c r="AF323" t="inlineStr"/>
+      <c r="AG323" t="inlineStr"/>
+      <c r="AH323" t="inlineStr"/>
+      <c r="AI323" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI323"/>
+  <dimension ref="A1:AI324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33235,6 +33235,109 @@
       <c r="AH323" t="inlineStr"/>
       <c r="AI323" t="inlineStr"/>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>751.27</v>
+      </c>
+      <c r="C324" t="n">
+        <v>776</v>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="n">
+        <v>643</v>
+      </c>
+      <c r="F324" t="n">
+        <v>1112.5</v>
+      </c>
+      <c r="G324" t="n">
+        <v>616</v>
+      </c>
+      <c r="H324" t="n">
+        <v>695</v>
+      </c>
+      <c r="I324" t="n">
+        <v>564</v>
+      </c>
+      <c r="J324" t="n">
+        <v>607</v>
+      </c>
+      <c r="K324" t="n">
+        <v>1065</v>
+      </c>
+      <c r="L324" t="n">
+        <v>761</v>
+      </c>
+      <c r="M324" t="n">
+        <v>1409</v>
+      </c>
+      <c r="N324" t="n">
+        <v>767</v>
+      </c>
+      <c r="O324" t="n">
+        <v>665</v>
+      </c>
+      <c r="P324" t="n">
+        <v>1135</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>850</v>
+      </c>
+      <c r="R324" t="n">
+        <v>654</v>
+      </c>
+      <c r="S324" t="n">
+        <v>1080</v>
+      </c>
+      <c r="T324" t="n">
+        <v>820</v>
+      </c>
+      <c r="U324" t="n">
+        <v>700</v>
+      </c>
+      <c r="V324" t="n">
+        <v>1110</v>
+      </c>
+      <c r="W324" t="n">
+        <v>771</v>
+      </c>
+      <c r="X324" t="n">
+        <v>665</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>1145</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>710</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>655</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>1160</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>790</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>718</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>1141</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>1120.11</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AH324" t="inlineStr"/>
+      <c r="AI324" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI324"/>
+  <dimension ref="A1:AI325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33338,6 +33338,109 @@
       <c r="AH324" t="inlineStr"/>
       <c r="AI324" t="inlineStr"/>
     </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>768.47</v>
+      </c>
+      <c r="C325" t="n">
+        <v>794</v>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="n">
+        <v>650</v>
+      </c>
+      <c r="F325" t="n">
+        <v>1165</v>
+      </c>
+      <c r="G325" t="n">
+        <v>633</v>
+      </c>
+      <c r="H325" t="n">
+        <v>699</v>
+      </c>
+      <c r="I325" t="n">
+        <v>570.75</v>
+      </c>
+      <c r="J325" t="n">
+        <v>635</v>
+      </c>
+      <c r="K325" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L325" t="n">
+        <v>781</v>
+      </c>
+      <c r="M325" t="n">
+        <v>1290</v>
+      </c>
+      <c r="N325" t="n">
+        <v>784</v>
+      </c>
+      <c r="O325" t="n">
+        <v>672</v>
+      </c>
+      <c r="P325" t="n">
+        <v>1175</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>855</v>
+      </c>
+      <c r="R325" t="n">
+        <v>661</v>
+      </c>
+      <c r="S325" t="n">
+        <v>1145</v>
+      </c>
+      <c r="T325" t="n">
+        <v>841</v>
+      </c>
+      <c r="U325" t="n">
+        <v>720</v>
+      </c>
+      <c r="V325" t="n">
+        <v>1166.25</v>
+      </c>
+      <c r="W325" t="n">
+        <v>789</v>
+      </c>
+      <c r="X325" t="n">
+        <v>672</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>1185</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>718</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>660</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>777</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>704</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>1172</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>1119.92</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AH325" t="inlineStr"/>
+      <c r="AI325" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI325"/>
+  <dimension ref="A1:AI326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33441,6 +33441,109 @@
       <c r="AH325" t="inlineStr"/>
       <c r="AI325" t="inlineStr"/>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>760.28</v>
+      </c>
+      <c r="C326" t="n">
+        <v>782</v>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="n">
+        <v>632</v>
+      </c>
+      <c r="F326" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G326" t="n">
+        <v>619</v>
+      </c>
+      <c r="H326" t="n">
+        <v>688</v>
+      </c>
+      <c r="I326" t="n">
+        <v>552.25</v>
+      </c>
+      <c r="J326" t="n">
+        <v>595</v>
+      </c>
+      <c r="K326" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L326" t="n">
+        <v>774</v>
+      </c>
+      <c r="M326" t="n">
+        <v>1235</v>
+      </c>
+      <c r="N326" t="n">
+        <v>777</v>
+      </c>
+      <c r="O326" t="n">
+        <v>660</v>
+      </c>
+      <c r="P326" t="n">
+        <v>1155</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>845</v>
+      </c>
+      <c r="R326" t="n">
+        <v>642</v>
+      </c>
+      <c r="S326" t="n">
+        <v>1120</v>
+      </c>
+      <c r="T326" t="n">
+        <v>830</v>
+      </c>
+      <c r="U326" t="n">
+        <v>705</v>
+      </c>
+      <c r="V326" t="n">
+        <v>1176.75</v>
+      </c>
+      <c r="W326" t="n">
+        <v>782</v>
+      </c>
+      <c r="X326" t="n">
+        <v>660</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>1160</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>718</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>635</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>766</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>692</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>1170.04</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>1220</v>
+      </c>
+      <c r="AH326" t="inlineStr"/>
+      <c r="AI326" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI326"/>
+  <dimension ref="A1:AI327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33544,6 +33544,109 @@
       <c r="AH326" t="inlineStr"/>
       <c r="AI326" t="inlineStr"/>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>743.51</v>
+      </c>
+      <c r="C327" t="n">
+        <v>770</v>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="n">
+        <v>614</v>
+      </c>
+      <c r="F327" t="n">
+        <v>1116</v>
+      </c>
+      <c r="G327" t="n">
+        <v>613.75</v>
+      </c>
+      <c r="H327" t="n">
+        <v>679</v>
+      </c>
+      <c r="I327" t="n">
+        <v>548</v>
+      </c>
+      <c r="J327" t="n">
+        <v>590</v>
+      </c>
+      <c r="K327" t="n">
+        <v>1048</v>
+      </c>
+      <c r="L327" t="n">
+        <v>759</v>
+      </c>
+      <c r="M327" t="n">
+        <v>1208</v>
+      </c>
+      <c r="N327" t="n">
+        <v>763</v>
+      </c>
+      <c r="O327" t="n">
+        <v>635</v>
+      </c>
+      <c r="P327" t="n">
+        <v>1072</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>820</v>
+      </c>
+      <c r="R327" t="n">
+        <v>637</v>
+      </c>
+      <c r="S327" t="n">
+        <v>1050</v>
+      </c>
+      <c r="T327" t="n">
+        <v>814</v>
+      </c>
+      <c r="U327" t="n">
+        <v>704</v>
+      </c>
+      <c r="V327" t="n">
+        <v>1064.75</v>
+      </c>
+      <c r="W327" t="n">
+        <v>768</v>
+      </c>
+      <c r="X327" t="n">
+        <v>635</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>1080</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>722</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>633</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>1160</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>747</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>689</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>1112</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>1220.08</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>1250</v>
+      </c>
+      <c r="AH327" t="inlineStr"/>
+      <c r="AI327" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI327"/>
+  <dimension ref="A1:AI328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33647,6 +33647,109 @@
       <c r="AH327" t="inlineStr"/>
       <c r="AI327" t="inlineStr"/>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>753.55</v>
+      </c>
+      <c r="C328" t="n">
+        <v>781</v>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="n">
+        <v>632</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1170.75</v>
+      </c>
+      <c r="G328" t="n">
+        <v>619</v>
+      </c>
+      <c r="H328" t="n">
+        <v>680</v>
+      </c>
+      <c r="I328" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="J328" t="n">
+        <v>605</v>
+      </c>
+      <c r="K328" t="n">
+        <v>1065</v>
+      </c>
+      <c r="L328" t="n">
+        <v>770</v>
+      </c>
+      <c r="M328" t="n">
+        <v>1198</v>
+      </c>
+      <c r="N328" t="n">
+        <v>780</v>
+      </c>
+      <c r="O328" t="n">
+        <v>644</v>
+      </c>
+      <c r="P328" t="n">
+        <v>1130</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>820</v>
+      </c>
+      <c r="R328" t="n">
+        <v>654</v>
+      </c>
+      <c r="S328" t="n">
+        <v>1085</v>
+      </c>
+      <c r="T328" t="n">
+        <v>826</v>
+      </c>
+      <c r="U328" t="n">
+        <v>724</v>
+      </c>
+      <c r="V328" t="n">
+        <v>1111</v>
+      </c>
+      <c r="W328" t="n">
+        <v>783</v>
+      </c>
+      <c r="X328" t="n">
+        <v>644</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>1135</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>742</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>655</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>751</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>691</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>1111</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>1169.97</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AH328" t="inlineStr"/>
+      <c r="AI328" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI328"/>
+  <dimension ref="A1:AI329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33750,6 +33750,109 @@
       <c r="AH328" t="inlineStr"/>
       <c r="AI328" t="inlineStr"/>
     </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>708.75</v>
+      </c>
+      <c r="C329" t="n">
+        <v>738</v>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="n">
+        <v>596</v>
+      </c>
+      <c r="F329" t="n">
+        <v>1136.5</v>
+      </c>
+      <c r="G329" t="n">
+        <v>596.5</v>
+      </c>
+      <c r="H329" t="n">
+        <v>660</v>
+      </c>
+      <c r="I329" t="n">
+        <v>530</v>
+      </c>
+      <c r="J329" t="n">
+        <v>585</v>
+      </c>
+      <c r="K329" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L329" t="n">
+        <v>725</v>
+      </c>
+      <c r="M329" t="n">
+        <v>1138</v>
+      </c>
+      <c r="N329" t="n">
+        <v>747</v>
+      </c>
+      <c r="O329" t="n">
+        <v>625</v>
+      </c>
+      <c r="P329" t="n">
+        <v>1078</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>783</v>
+      </c>
+      <c r="R329" t="n">
+        <v>618</v>
+      </c>
+      <c r="S329" t="n">
+        <v>1033</v>
+      </c>
+      <c r="T329" t="n">
+        <v>770</v>
+      </c>
+      <c r="U329" t="n">
+        <v>669</v>
+      </c>
+      <c r="V329" t="n">
+        <v>1107.25</v>
+      </c>
+      <c r="W329" t="n">
+        <v>750</v>
+      </c>
+      <c r="X329" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>1084</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>705</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>620</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>1140</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>736</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>682</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>1046</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>1170.04</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AH329" t="inlineStr"/>
+      <c r="AI329" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI329"/>
+  <dimension ref="A1:AI330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33853,6 +33853,109 @@
       <c r="AH329" t="inlineStr"/>
       <c r="AI329" t="inlineStr"/>
     </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>705.71</v>
+      </c>
+      <c r="C330" t="n">
+        <v>736</v>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="n">
+        <v>592</v>
+      </c>
+      <c r="F330" t="n">
+        <v>1109.25</v>
+      </c>
+      <c r="G330" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="H330" t="n">
+        <v>655</v>
+      </c>
+      <c r="I330" t="n">
+        <v>536.5</v>
+      </c>
+      <c r="J330" t="n">
+        <v>590</v>
+      </c>
+      <c r="K330" t="n">
+        <v>1040</v>
+      </c>
+      <c r="L330" t="n">
+        <v>722</v>
+      </c>
+      <c r="M330" t="n">
+        <v>1130</v>
+      </c>
+      <c r="N330" t="n">
+        <v>743</v>
+      </c>
+      <c r="O330" t="n">
+        <v>627</v>
+      </c>
+      <c r="P330" t="n">
+        <v>1083</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>760</v>
+      </c>
+      <c r="R330" t="n">
+        <v>619</v>
+      </c>
+      <c r="S330" t="n">
+        <v>1025</v>
+      </c>
+      <c r="T330" t="n">
+        <v>765</v>
+      </c>
+      <c r="U330" t="n">
+        <v>671</v>
+      </c>
+      <c r="V330" t="n">
+        <v>1091</v>
+      </c>
+      <c r="W330" t="n">
+        <v>745</v>
+      </c>
+      <c r="X330" t="n">
+        <v>632</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>1089</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>710</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>623</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>747</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>688</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>1062</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>1184.76</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>1215</v>
+      </c>
+      <c r="AH330" t="inlineStr"/>
+      <c r="AI330" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI330"/>
+  <dimension ref="A1:AI331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33956,6 +33956,109 @@
       <c r="AH330" t="inlineStr"/>
       <c r="AI330" t="inlineStr"/>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>712.4299999999999</v>
+      </c>
+      <c r="C331" t="n">
+        <v>745</v>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="n">
+        <v>593</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1108.75</v>
+      </c>
+      <c r="G331" t="n">
+        <v>617.75</v>
+      </c>
+      <c r="H331" t="n">
+        <v>650</v>
+      </c>
+      <c r="I331" t="n">
+        <v>531.25</v>
+      </c>
+      <c r="J331" t="n">
+        <v>575</v>
+      </c>
+      <c r="K331" t="n">
+        <v>1015</v>
+      </c>
+      <c r="L331" t="n">
+        <v>730</v>
+      </c>
+      <c r="M331" t="n">
+        <v>1128</v>
+      </c>
+      <c r="N331" t="n">
+        <v>750</v>
+      </c>
+      <c r="O331" t="n">
+        <v>627</v>
+      </c>
+      <c r="P331" t="n">
+        <v>1091</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>770</v>
+      </c>
+      <c r="R331" t="n">
+        <v>608</v>
+      </c>
+      <c r="S331" t="n">
+        <v>1035</v>
+      </c>
+      <c r="T331" t="n">
+        <v>780</v>
+      </c>
+      <c r="U331" t="n">
+        <v>671</v>
+      </c>
+      <c r="V331" t="n">
+        <v>1090.75</v>
+      </c>
+      <c r="W331" t="n">
+        <v>755</v>
+      </c>
+      <c r="X331" t="n">
+        <v>632</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>1097</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>699</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>613</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>1120</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>738</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>676</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>1047</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>1196.97</v>
+      </c>
+      <c r="AG331" t="n">
+        <v>1227</v>
+      </c>
+      <c r="AH331" t="inlineStr"/>
+      <c r="AI331" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI331"/>
+  <dimension ref="A1:AI332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34059,6 +34059,109 @@
       <c r="AH331" t="inlineStr"/>
       <c r="AI331" t="inlineStr"/>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>664.1</v>
+      </c>
+      <c r="C332" t="n">
+        <v>704</v>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="n">
+        <v>554</v>
+      </c>
+      <c r="F332" t="n">
+        <v>990</v>
+      </c>
+      <c r="G332" t="n">
+        <v>574</v>
+      </c>
+      <c r="H332" t="n">
+        <v>625</v>
+      </c>
+      <c r="I332" t="n">
+        <v>497</v>
+      </c>
+      <c r="J332" t="n">
+        <v>537</v>
+      </c>
+      <c r="K332" t="n">
+        <v>975</v>
+      </c>
+      <c r="L332" t="n">
+        <v>690</v>
+      </c>
+      <c r="M332" t="n">
+        <v>1125</v>
+      </c>
+      <c r="N332" t="n">
+        <v>702</v>
+      </c>
+      <c r="O332" t="n">
+        <v>587</v>
+      </c>
+      <c r="P332" t="n">
+        <v>1015</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>759</v>
+      </c>
+      <c r="R332" t="n">
+        <v>565</v>
+      </c>
+      <c r="S332" t="n">
+        <v>970</v>
+      </c>
+      <c r="T332" t="n">
+        <v>782</v>
+      </c>
+      <c r="U332" t="n">
+        <v>635</v>
+      </c>
+      <c r="V332" t="n">
+        <v>981.5</v>
+      </c>
+      <c r="W332" t="n">
+        <v>707</v>
+      </c>
+      <c r="X332" t="n">
+        <v>590</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>1021</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>668</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>585</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>1080</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>724</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>663</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>1025</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>1179.97</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>1210</v>
+      </c>
+      <c r="AH332" t="inlineStr"/>
+      <c r="AI332" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI332"/>
+  <dimension ref="A1:AI333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34162,6 +34162,109 @@
       <c r="AH332" t="inlineStr"/>
       <c r="AI332" t="inlineStr"/>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>626.91</v>
+      </c>
+      <c r="C333" t="n">
+        <v>668</v>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="n">
+        <v>511</v>
+      </c>
+      <c r="F333" t="n">
+        <v>955.25</v>
+      </c>
+      <c r="G333" t="n">
+        <v>542</v>
+      </c>
+      <c r="H333" t="n">
+        <v>590</v>
+      </c>
+      <c r="I333" t="n">
+        <v>471.75</v>
+      </c>
+      <c r="J333" t="n">
+        <v>507</v>
+      </c>
+      <c r="K333" t="n">
+        <v>920</v>
+      </c>
+      <c r="L333" t="n">
+        <v>660</v>
+      </c>
+      <c r="M333" t="n">
+        <v>1130</v>
+      </c>
+      <c r="N333" t="n">
+        <v>670</v>
+      </c>
+      <c r="O333" t="n">
+        <v>555</v>
+      </c>
+      <c r="P333" t="n">
+        <v>980</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>705</v>
+      </c>
+      <c r="R333" t="n">
+        <v>522</v>
+      </c>
+      <c r="S333" t="n">
+        <v>946</v>
+      </c>
+      <c r="T333" t="n">
+        <v>760</v>
+      </c>
+      <c r="U333" t="n">
+        <v>596</v>
+      </c>
+      <c r="V333" t="n">
+        <v>932</v>
+      </c>
+      <c r="W333" t="n">
+        <v>675</v>
+      </c>
+      <c r="X333" t="n">
+        <v>558</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>986</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>655</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>565</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>1030</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>687</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>617</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>987</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>1199.92</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>1230</v>
+      </c>
+      <c r="AH333" t="inlineStr"/>
+      <c r="AI333" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI333"/>
+  <dimension ref="A1:AI334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34265,6 +34265,109 @@
       <c r="AH333" t="inlineStr"/>
       <c r="AI333" t="inlineStr"/>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>597.5599999999999</v>
+      </c>
+      <c r="C334" t="n">
+        <v>644</v>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="n">
+        <v>486</v>
+      </c>
+      <c r="F334" t="n">
+        <v>930.75</v>
+      </c>
+      <c r="G334" t="n">
+        <v>536</v>
+      </c>
+      <c r="H334" t="n">
+        <v>575</v>
+      </c>
+      <c r="I334" t="n">
+        <v>451.75</v>
+      </c>
+      <c r="J334" t="n">
+        <v>490</v>
+      </c>
+      <c r="K334" t="n">
+        <v>870</v>
+      </c>
+      <c r="L334" t="n">
+        <v>620</v>
+      </c>
+      <c r="M334" t="n">
+        <v>1128</v>
+      </c>
+      <c r="N334" t="n">
+        <v>641</v>
+      </c>
+      <c r="O334" t="n">
+        <v>530</v>
+      </c>
+      <c r="P334" t="n">
+        <v>955</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>655</v>
+      </c>
+      <c r="R334" t="n">
+        <v>505</v>
+      </c>
+      <c r="S334" t="n">
+        <v>910</v>
+      </c>
+      <c r="T334" t="n">
+        <v>750</v>
+      </c>
+      <c r="U334" t="n">
+        <v>568</v>
+      </c>
+      <c r="V334" t="n">
+        <v>966.75</v>
+      </c>
+      <c r="W334" t="n">
+        <v>646</v>
+      </c>
+      <c r="X334" t="n">
+        <v>533</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>961</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>600</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>530</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>647</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>577</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>952</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>1170.9</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>1201</v>
+      </c>
+      <c r="AH334" t="inlineStr"/>
+      <c r="AI334" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI334"/>
+  <dimension ref="A1:AI335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34368,6 +34368,109 @@
       <c r="AH334" t="inlineStr"/>
       <c r="AI334" t="inlineStr"/>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>602.47</v>
+      </c>
+      <c r="C335" t="n">
+        <v>650</v>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="n">
+        <v>460</v>
+      </c>
+      <c r="F335" t="n">
+        <v>920.5</v>
+      </c>
+      <c r="G335" t="n">
+        <v>544.75</v>
+      </c>
+      <c r="H335" t="n">
+        <v>576</v>
+      </c>
+      <c r="I335" t="n">
+        <v>451.75</v>
+      </c>
+      <c r="J335" t="n">
+        <v>488</v>
+      </c>
+      <c r="K335" t="n">
+        <v>880</v>
+      </c>
+      <c r="L335" t="n">
+        <v>620</v>
+      </c>
+      <c r="M335" t="n">
+        <v>1140</v>
+      </c>
+      <c r="N335" t="n">
+        <v>641</v>
+      </c>
+      <c r="O335" t="n">
+        <v>515</v>
+      </c>
+      <c r="P335" t="n">
+        <v>945</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>660</v>
+      </c>
+      <c r="R335" t="n">
+        <v>505</v>
+      </c>
+      <c r="S335" t="n">
+        <v>880</v>
+      </c>
+      <c r="T335" t="n">
+        <v>750</v>
+      </c>
+      <c r="U335" t="n">
+        <v>600</v>
+      </c>
+      <c r="V335" t="n">
+        <v>1017.5</v>
+      </c>
+      <c r="W335" t="n">
+        <v>646</v>
+      </c>
+      <c r="X335" t="n">
+        <v>518</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>951</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>609</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>533</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>989</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>636</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>578</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>932</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>1070.09</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AH335" t="inlineStr"/>
+      <c r="AI335" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI335"/>
+  <dimension ref="A1:AI336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34471,6 +34471,109 @@
       <c r="AH335" t="inlineStr"/>
       <c r="AI335" t="inlineStr"/>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>602.16</v>
+      </c>
+      <c r="C336" t="n">
+        <v>665</v>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="n">
+        <v>455</v>
+      </c>
+      <c r="F336" t="n">
+        <v>893.25</v>
+      </c>
+      <c r="G336" t="n">
+        <v>544.75</v>
+      </c>
+      <c r="H336" t="n">
+        <v>575</v>
+      </c>
+      <c r="I336" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="J336" t="n">
+        <v>480</v>
+      </c>
+      <c r="K336" t="n">
+        <v>855</v>
+      </c>
+      <c r="L336" t="n">
+        <v>619</v>
+      </c>
+      <c r="M336" t="n">
+        <v>1139</v>
+      </c>
+      <c r="N336" t="n">
+        <v>660</v>
+      </c>
+      <c r="O336" t="n">
+        <v>500</v>
+      </c>
+      <c r="P336" t="n">
+        <v>940</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>658</v>
+      </c>
+      <c r="R336" t="n">
+        <v>485</v>
+      </c>
+      <c r="S336" t="n">
+        <v>861</v>
+      </c>
+      <c r="T336" t="n">
+        <v>720</v>
+      </c>
+      <c r="U336" t="n">
+        <v>593</v>
+      </c>
+      <c r="V336" t="n">
+        <v>962.25</v>
+      </c>
+      <c r="W336" t="n">
+        <v>650</v>
+      </c>
+      <c r="X336" t="n">
+        <v>503</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>946</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>615</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>525</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>961</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>617</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>573</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>907</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>930.05</v>
+      </c>
+      <c r="AG336" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AH336" t="inlineStr"/>
+      <c r="AI336" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI336"/>
+  <dimension ref="A1:AI337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34574,6 +34574,99 @@
       <c r="AH336" t="inlineStr"/>
       <c r="AI336" t="inlineStr"/>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>628.46</v>
+      </c>
+      <c r="C337" t="n">
+        <v>720</v>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="n">
+        <v>479</v>
+      </c>
+      <c r="F337" t="n">
+        <v>911</v>
+      </c>
+      <c r="G337" t="n">
+        <v>567.5</v>
+      </c>
+      <c r="H337" t="n">
+        <v>592</v>
+      </c>
+      <c r="I337" t="n">
+        <v>454.75</v>
+      </c>
+      <c r="J337" t="n">
+        <v>490</v>
+      </c>
+      <c r="K337" t="n">
+        <v>868</v>
+      </c>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="n">
+        <v>686</v>
+      </c>
+      <c r="O337" t="n">
+        <v>513</v>
+      </c>
+      <c r="P337" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>683</v>
+      </c>
+      <c r="R337" t="n">
+        <v>485</v>
+      </c>
+      <c r="S337" t="n">
+        <v>865</v>
+      </c>
+      <c r="T337" t="n">
+        <v>725</v>
+      </c>
+      <c r="U337" t="n">
+        <v>605</v>
+      </c>
+      <c r="V337" t="n">
+        <v>990</v>
+      </c>
+      <c r="W337" t="n">
+        <v>675</v>
+      </c>
+      <c r="X337" t="n">
+        <v>516</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>956</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>630</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>540</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC337" t="inlineStr"/>
+      <c r="AD337" t="inlineStr"/>
+      <c r="AE337" t="inlineStr"/>
+      <c r="AF337" t="n">
+        <v>829.99</v>
+      </c>
+      <c r="AG337" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AH337" t="inlineStr"/>
+      <c r="AI337" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI337"/>
+  <dimension ref="A1:AI338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34667,6 +34667,109 @@
       <c r="AH337" t="inlineStr"/>
       <c r="AI337" t="inlineStr"/>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>611.1799999999999</v>
+      </c>
+      <c r="C338" t="n">
+        <v>720</v>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="n">
+        <v>474</v>
+      </c>
+      <c r="F338" t="n">
+        <v>933.5</v>
+      </c>
+      <c r="G338" t="n">
+        <v>549.75</v>
+      </c>
+      <c r="H338" t="n">
+        <v>588</v>
+      </c>
+      <c r="I338" t="n">
+        <v>437.75</v>
+      </c>
+      <c r="J338" t="n">
+        <v>485</v>
+      </c>
+      <c r="K338" t="n">
+        <v>860</v>
+      </c>
+      <c r="L338" t="n">
+        <v>640</v>
+      </c>
+      <c r="M338" t="n">
+        <v>1134</v>
+      </c>
+      <c r="N338" t="n">
+        <v>669</v>
+      </c>
+      <c r="O338" t="n">
+        <v>500</v>
+      </c>
+      <c r="P338" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>665</v>
+      </c>
+      <c r="R338" t="n">
+        <v>470</v>
+      </c>
+      <c r="S338" t="n">
+        <v>870</v>
+      </c>
+      <c r="T338" t="n">
+        <v>705</v>
+      </c>
+      <c r="U338" t="n">
+        <v>605</v>
+      </c>
+      <c r="V338" t="n">
+        <v>1031.5</v>
+      </c>
+      <c r="W338" t="n">
+        <v>663</v>
+      </c>
+      <c r="X338" t="n">
+        <v>503</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>965</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>622</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>527</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>968</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>620</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>578</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>920</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>779.98</v>
+      </c>
+      <c r="AG338" t="n">
+        <v>1050</v>
+      </c>
+      <c r="AH338" t="inlineStr"/>
+      <c r="AI338" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI338"/>
+  <dimension ref="A1:AI339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34770,6 +34770,109 @@
       <c r="AH338" t="inlineStr"/>
       <c r="AI338" t="inlineStr"/>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>598.02</v>
+      </c>
+      <c r="C339" t="n">
+        <v>720</v>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="n">
+        <v>463</v>
+      </c>
+      <c r="F339" t="n">
+        <v>897.75</v>
+      </c>
+      <c r="G339" t="n">
+        <v>549.75</v>
+      </c>
+      <c r="H339" t="n">
+        <v>589</v>
+      </c>
+      <c r="I339" t="n">
+        <v>437</v>
+      </c>
+      <c r="J339" t="n">
+        <v>480</v>
+      </c>
+      <c r="K339" t="n">
+        <v>856</v>
+      </c>
+      <c r="L339" t="n">
+        <v>660</v>
+      </c>
+      <c r="M339" t="n">
+        <v>1132</v>
+      </c>
+      <c r="N339" t="n">
+        <v>664</v>
+      </c>
+      <c r="O339" t="n">
+        <v>483</v>
+      </c>
+      <c r="P339" t="n">
+        <v>931</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>665</v>
+      </c>
+      <c r="R339" t="n">
+        <v>460</v>
+      </c>
+      <c r="S339" t="n">
+        <v>850</v>
+      </c>
+      <c r="T339" t="n">
+        <v>693.25</v>
+      </c>
+      <c r="U339" t="n">
+        <v>597</v>
+      </c>
+      <c r="V339" t="n">
+        <v>945</v>
+      </c>
+      <c r="W339" t="n">
+        <v>663</v>
+      </c>
+      <c r="X339" t="n">
+        <v>486</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>936</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>622</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>515</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>978</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>620</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>576</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>930</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>700.08</v>
+      </c>
+      <c r="AG339" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH339" t="inlineStr"/>
+      <c r="AI339" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI339"/>
+  <dimension ref="A1:AI340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34873,6 +34873,109 @@
       <c r="AH339" t="inlineStr"/>
       <c r="AI339" t="inlineStr"/>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>592.3200000000001</v>
+      </c>
+      <c r="C340" t="n">
+        <v>715</v>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="n">
+        <v>464</v>
+      </c>
+      <c r="F340" t="n">
+        <v>879</v>
+      </c>
+      <c r="G340" t="n">
+        <v>537.75</v>
+      </c>
+      <c r="H340" t="n">
+        <v>584</v>
+      </c>
+      <c r="I340" t="n">
+        <v>414.25</v>
+      </c>
+      <c r="J340" t="n">
+        <v>467</v>
+      </c>
+      <c r="K340" t="n">
+        <v>855</v>
+      </c>
+      <c r="L340" t="n">
+        <v>635</v>
+      </c>
+      <c r="M340" t="n">
+        <v>1129</v>
+      </c>
+      <c r="N340" t="n">
+        <v>658</v>
+      </c>
+      <c r="O340" t="n">
+        <v>480</v>
+      </c>
+      <c r="P340" t="n">
+        <v>938</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>669</v>
+      </c>
+      <c r="R340" t="n">
+        <v>460</v>
+      </c>
+      <c r="S340" t="n">
+        <v>877</v>
+      </c>
+      <c r="T340" t="n">
+        <v>679</v>
+      </c>
+      <c r="U340" t="n">
+        <v>565</v>
+      </c>
+      <c r="V340" t="n">
+        <v>978</v>
+      </c>
+      <c r="W340" t="n">
+        <v>658</v>
+      </c>
+      <c r="X340" t="n">
+        <v>483</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>943</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>605</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>495</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>960</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>607</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>571</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>927</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>679.73</v>
+      </c>
+      <c r="AG340" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH340" t="inlineStr"/>
+      <c r="AI340" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI340"/>
+  <dimension ref="A1:AI341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34976,6 +34976,109 @@
       <c r="AH340" t="inlineStr"/>
       <c r="AI340" t="inlineStr"/>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>575.51</v>
+      </c>
+      <c r="C341" t="n">
+        <v>710</v>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="n">
+        <v>448</v>
+      </c>
+      <c r="F341" t="n">
+        <v>874</v>
+      </c>
+      <c r="G341" t="n">
+        <v>546</v>
+      </c>
+      <c r="H341" t="n">
+        <v>590</v>
+      </c>
+      <c r="I341" t="n">
+        <v>420.25</v>
+      </c>
+      <c r="J341" t="n">
+        <v>455</v>
+      </c>
+      <c r="K341" t="n">
+        <v>880</v>
+      </c>
+      <c r="L341" t="n">
+        <v>627</v>
+      </c>
+      <c r="M341" t="n">
+        <v>1130</v>
+      </c>
+      <c r="N341" t="n">
+        <v>645</v>
+      </c>
+      <c r="O341" t="n">
+        <v>460</v>
+      </c>
+      <c r="P341" t="n">
+        <v>943</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>716.25</v>
+      </c>
+      <c r="R341" t="n">
+        <v>450</v>
+      </c>
+      <c r="S341" t="n">
+        <v>935.75</v>
+      </c>
+      <c r="T341" t="n">
+        <v>660.25</v>
+      </c>
+      <c r="U341" t="n">
+        <v>515</v>
+      </c>
+      <c r="V341" t="n">
+        <v>972</v>
+      </c>
+      <c r="W341" t="n">
+        <v>645</v>
+      </c>
+      <c r="X341" t="n">
+        <v>460</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>948</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>585</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>486</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>965</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>608</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>572</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>937</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>680.08</v>
+      </c>
+      <c r="AG341" t="n">
+        <v>930</v>
+      </c>
+      <c r="AH341" t="inlineStr"/>
+      <c r="AI341" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI341"/>
+  <dimension ref="A1:AI342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35079,6 +35079,109 @@
       <c r="AH341" t="inlineStr"/>
       <c r="AI341" t="inlineStr"/>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>575.47</v>
+      </c>
+      <c r="C342" t="n">
+        <v>708</v>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="n">
+        <v>448</v>
+      </c>
+      <c r="F342" t="n">
+        <v>896.5</v>
+      </c>
+      <c r="G342" t="n">
+        <v>526</v>
+      </c>
+      <c r="H342" t="n">
+        <v>578</v>
+      </c>
+      <c r="I342" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="J342" t="n">
+        <v>445</v>
+      </c>
+      <c r="K342" t="n">
+        <v>855</v>
+      </c>
+      <c r="L342" t="n">
+        <v>632</v>
+      </c>
+      <c r="M342" t="n">
+        <v>1127</v>
+      </c>
+      <c r="N342" t="n">
+        <v>650</v>
+      </c>
+      <c r="O342" t="n">
+        <v>464</v>
+      </c>
+      <c r="P342" t="n">
+        <v>942</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>675</v>
+      </c>
+      <c r="R342" t="n">
+        <v>460</v>
+      </c>
+      <c r="S342" t="n">
+        <v>975</v>
+      </c>
+      <c r="T342" t="n">
+        <v>637</v>
+      </c>
+      <c r="U342" t="n">
+        <v>510</v>
+      </c>
+      <c r="V342" t="n">
+        <v>936</v>
+      </c>
+      <c r="W342" t="n">
+        <v>650</v>
+      </c>
+      <c r="X342" t="n">
+        <v>464</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>947</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>596</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>954</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>598</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>557</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>927</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>674.92</v>
+      </c>
+      <c r="AG342" t="n">
+        <v>920</v>
+      </c>
+      <c r="AH342" t="inlineStr"/>
+      <c r="AI342" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI342"/>
+  <dimension ref="A1:AI343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35182,6 +35182,109 @@
       <c r="AH342" t="inlineStr"/>
       <c r="AI342" t="inlineStr"/>
     </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>589.79</v>
+      </c>
+      <c r="C343" t="n">
+        <v>720</v>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="n">
+        <v>452</v>
+      </c>
+      <c r="F343" t="n">
+        <v>917</v>
+      </c>
+      <c r="G343" t="n">
+        <v>539.75</v>
+      </c>
+      <c r="H343" t="n">
+        <v>590</v>
+      </c>
+      <c r="I343" t="n">
+        <v>408.25</v>
+      </c>
+      <c r="J343" t="n">
+        <v>455</v>
+      </c>
+      <c r="K343" t="n">
+        <v>880</v>
+      </c>
+      <c r="L343" t="n">
+        <v>643</v>
+      </c>
+      <c r="M343" t="n">
+        <v>1057</v>
+      </c>
+      <c r="N343" t="n">
+        <v>670</v>
+      </c>
+      <c r="O343" t="n">
+        <v>473</v>
+      </c>
+      <c r="P343" t="n">
+        <v>955</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>685</v>
+      </c>
+      <c r="R343" t="n">
+        <v>498</v>
+      </c>
+      <c r="S343" t="n">
+        <v>1045</v>
+      </c>
+      <c r="T343" t="n">
+        <v>665.25</v>
+      </c>
+      <c r="U343" t="n">
+        <v>514</v>
+      </c>
+      <c r="V343" t="n">
+        <v>942.75</v>
+      </c>
+      <c r="W343" t="n">
+        <v>670</v>
+      </c>
+      <c r="X343" t="n">
+        <v>473</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>960</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>585</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>468</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>955</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>583</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>547</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>927</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>685.13</v>
+      </c>
+      <c r="AG343" t="n">
+        <v>870</v>
+      </c>
+      <c r="AH343" t="inlineStr"/>
+      <c r="AI343" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI343"/>
+  <dimension ref="A1:AI344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35285,6 +35285,109 @@
       <c r="AH343" t="inlineStr"/>
       <c r="AI343" t="inlineStr"/>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>589.65</v>
+      </c>
+      <c r="C344" t="n">
+        <v>715</v>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="n">
+        <v>451</v>
+      </c>
+      <c r="F344" t="n">
+        <v>914.75</v>
+      </c>
+      <c r="G344" t="n">
+        <v>539.75</v>
+      </c>
+      <c r="H344" t="n">
+        <v>588</v>
+      </c>
+      <c r="I344" t="n">
+        <v>405.75</v>
+      </c>
+      <c r="J344" t="n">
+        <v>450</v>
+      </c>
+      <c r="K344" t="n">
+        <v>905</v>
+      </c>
+      <c r="L344" t="n">
+        <v>643</v>
+      </c>
+      <c r="M344" t="n">
+        <v>992</v>
+      </c>
+      <c r="N344" t="n">
+        <v>660</v>
+      </c>
+      <c r="O344" t="n">
+        <v>467</v>
+      </c>
+      <c r="P344" t="n">
+        <v>949</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>680</v>
+      </c>
+      <c r="R344" t="n">
+        <v>499</v>
+      </c>
+      <c r="S344" t="n">
+        <v>1073.75</v>
+      </c>
+      <c r="T344" t="n">
+        <v>665</v>
+      </c>
+      <c r="U344" t="n">
+        <v>504</v>
+      </c>
+      <c r="V344" t="n">
+        <v>920</v>
+      </c>
+      <c r="W344" t="n">
+        <v>660</v>
+      </c>
+      <c r="X344" t="n">
+        <v>467</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>954</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>590</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>582</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>542</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>932</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>670.1</v>
+      </c>
+      <c r="AG344" t="n">
+        <v>800</v>
+      </c>
+      <c r="AH344" t="inlineStr"/>
+      <c r="AI344" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI344"/>
+  <dimension ref="A1:AI345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35388,6 +35388,109 @@
       <c r="AH344" t="inlineStr"/>
       <c r="AI344" t="inlineStr"/>
     </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>577.02</v>
+      </c>
+      <c r="C345" t="n">
+        <v>700</v>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="n">
+        <v>435</v>
+      </c>
+      <c r="F345" t="n">
+        <v>925.5</v>
+      </c>
+      <c r="G345" t="n">
+        <v>536</v>
+      </c>
+      <c r="H345" t="n">
+        <v>580</v>
+      </c>
+      <c r="I345" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="J345" t="n">
+        <v>447</v>
+      </c>
+      <c r="K345" t="n">
+        <v>910</v>
+      </c>
+      <c r="L345" t="n">
+        <v>615</v>
+      </c>
+      <c r="M345" t="n">
+        <v>928</v>
+      </c>
+      <c r="N345" t="n">
+        <v>652</v>
+      </c>
+      <c r="O345" t="n">
+        <v>460</v>
+      </c>
+      <c r="P345" t="n">
+        <v>940</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>666</v>
+      </c>
+      <c r="R345" t="n">
+        <v>481.25</v>
+      </c>
+      <c r="S345" t="n">
+        <v>980</v>
+      </c>
+      <c r="T345" t="n">
+        <v>649</v>
+      </c>
+      <c r="U345" t="n">
+        <v>482</v>
+      </c>
+      <c r="V345" t="n">
+        <v>924.5</v>
+      </c>
+      <c r="W345" t="n">
+        <v>652</v>
+      </c>
+      <c r="X345" t="n">
+        <v>460</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>942</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>589</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>469</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>992</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>580</v>
+      </c>
+      <c r="AD345" t="n">
+        <v>539</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>937</v>
+      </c>
+      <c r="AF345" t="n">
+        <v>656.63</v>
+      </c>
+      <c r="AG345" t="n">
+        <v>715</v>
+      </c>
+      <c r="AH345" t="inlineStr"/>
+      <c r="AI345" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI345"/>
+  <dimension ref="A1:AI346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35491,6 +35491,109 @@
       <c r="AH345" t="inlineStr"/>
       <c r="AI345" t="inlineStr"/>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>571.5599999999999</v>
+      </c>
+      <c r="C346" t="n">
+        <v>675</v>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="n">
+        <v>429</v>
+      </c>
+      <c r="F346" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="G346" t="n">
+        <v>523.75</v>
+      </c>
+      <c r="H346" t="n">
+        <v>570</v>
+      </c>
+      <c r="I346" t="n">
+        <v>392</v>
+      </c>
+      <c r="J346" t="n">
+        <v>442</v>
+      </c>
+      <c r="K346" t="n">
+        <v>925</v>
+      </c>
+      <c r="L346" t="n">
+        <v>607</v>
+      </c>
+      <c r="M346" t="n">
+        <v>925</v>
+      </c>
+      <c r="N346" t="n">
+        <v>645</v>
+      </c>
+      <c r="O346" t="n">
+        <v>465</v>
+      </c>
+      <c r="P346" t="n">
+        <v>952</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>680</v>
+      </c>
+      <c r="R346" t="n">
+        <v>529.75</v>
+      </c>
+      <c r="S346" t="n">
+        <v>1045.25</v>
+      </c>
+      <c r="T346" t="n">
+        <v>674.25</v>
+      </c>
+      <c r="U346" t="n">
+        <v>495</v>
+      </c>
+      <c r="V346" t="n">
+        <v>942.75</v>
+      </c>
+      <c r="W346" t="n">
+        <v>645</v>
+      </c>
+      <c r="X346" t="n">
+        <v>465</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>954</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>580</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>467</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>1006</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>573</v>
+      </c>
+      <c r="AD346" t="n">
+        <v>512</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>920</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>640.0599999999999</v>
+      </c>
+      <c r="AG346" t="n">
+        <v>690</v>
+      </c>
+      <c r="AH346" t="inlineStr"/>
+      <c r="AI346" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI346"/>
+  <dimension ref="A1:AI347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35594,6 +35594,99 @@
       <c r="AH346" t="inlineStr"/>
       <c r="AI346" t="inlineStr"/>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>562.15</v>
+      </c>
+      <c r="C347" t="n">
+        <v>660</v>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="n">
+        <v>433</v>
+      </c>
+      <c r="F347" t="n">
+        <v>892.25</v>
+      </c>
+      <c r="G347" t="n">
+        <v>516</v>
+      </c>
+      <c r="H347" t="n">
+        <v>572</v>
+      </c>
+      <c r="I347" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="J347" t="n">
+        <v>440</v>
+      </c>
+      <c r="K347" t="n">
+        <v>920</v>
+      </c>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="n">
+        <v>645</v>
+      </c>
+      <c r="O347" t="n">
+        <v>459</v>
+      </c>
+      <c r="P347" t="n">
+        <v>930</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>678</v>
+      </c>
+      <c r="R347" t="n">
+        <v>527</v>
+      </c>
+      <c r="S347" t="n">
+        <v>995</v>
+      </c>
+      <c r="T347" t="n">
+        <v>653.75</v>
+      </c>
+      <c r="U347" t="n">
+        <v>503</v>
+      </c>
+      <c r="V347" t="n">
+        <v>921.75</v>
+      </c>
+      <c r="W347" t="n">
+        <v>645</v>
+      </c>
+      <c r="X347" t="n">
+        <v>459</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>932</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>578</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>465</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>982</v>
+      </c>
+      <c r="AC347" t="inlineStr"/>
+      <c r="AD347" t="inlineStr"/>
+      <c r="AE347" t="inlineStr"/>
+      <c r="AF347" t="n">
+        <v>630.0599999999999</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>650</v>
+      </c>
+      <c r="AH347" t="inlineStr"/>
+      <c r="AI347" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI347"/>
+  <dimension ref="A1:AI348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35687,6 +35687,109 @@
       <c r="AH347" t="inlineStr"/>
       <c r="AI347" t="inlineStr"/>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>551.97</v>
+      </c>
+      <c r="C348" t="n">
+        <v>642</v>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="n">
+        <v>434</v>
+      </c>
+      <c r="F348" t="n">
+        <v>906.75</v>
+      </c>
+      <c r="G348" t="n">
+        <v>514</v>
+      </c>
+      <c r="H348" t="n">
+        <v>558</v>
+      </c>
+      <c r="I348" t="n">
+        <v>402</v>
+      </c>
+      <c r="J348" t="n">
+        <v>435</v>
+      </c>
+      <c r="K348" t="n">
+        <v>940</v>
+      </c>
+      <c r="L348" t="n">
+        <v>596</v>
+      </c>
+      <c r="M348" t="n">
+        <v>924</v>
+      </c>
+      <c r="N348" t="n">
+        <v>635</v>
+      </c>
+      <c r="O348" t="n">
+        <v>455</v>
+      </c>
+      <c r="P348" t="n">
+        <v>931</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>665</v>
+      </c>
+      <c r="R348" t="n">
+        <v>504</v>
+      </c>
+      <c r="S348" t="n">
+        <v>980</v>
+      </c>
+      <c r="T348" t="n">
+        <v>664.25</v>
+      </c>
+      <c r="U348" t="n">
+        <v>519.75</v>
+      </c>
+      <c r="V348" t="n">
+        <v>928</v>
+      </c>
+      <c r="W348" t="n">
+        <v>635</v>
+      </c>
+      <c r="X348" t="n">
+        <v>455</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>935</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>576</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>464</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>572</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>513</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>962</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>614.96</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>630</v>
+      </c>
+      <c r="AH348" t="inlineStr"/>
+      <c r="AI348" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI348"/>
+  <dimension ref="A1:AI349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35790,6 +35790,109 @@
       <c r="AH348" t="inlineStr"/>
       <c r="AI348" t="inlineStr"/>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>561.95</v>
+      </c>
+      <c r="C349" t="n">
+        <v>645</v>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="n">
+        <v>438</v>
+      </c>
+      <c r="F349" t="n">
+        <v>900.5</v>
+      </c>
+      <c r="G349" t="n">
+        <v>526</v>
+      </c>
+      <c r="H349" t="n">
+        <v>568</v>
+      </c>
+      <c r="I349" t="n">
+        <v>413.75</v>
+      </c>
+      <c r="J349" t="n">
+        <v>445</v>
+      </c>
+      <c r="K349" t="n">
+        <v>960</v>
+      </c>
+      <c r="L349" t="n">
+        <v>604</v>
+      </c>
+      <c r="M349" t="n">
+        <v>925</v>
+      </c>
+      <c r="N349" t="n">
+        <v>635</v>
+      </c>
+      <c r="O349" t="n">
+        <v>455</v>
+      </c>
+      <c r="P349" t="n">
+        <v>937</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>665</v>
+      </c>
+      <c r="R349" t="n">
+        <v>504</v>
+      </c>
+      <c r="S349" t="n">
+        <v>975</v>
+      </c>
+      <c r="T349" t="n">
+        <v>650</v>
+      </c>
+      <c r="U349" t="n">
+        <v>510</v>
+      </c>
+      <c r="V349" t="n">
+        <v>912</v>
+      </c>
+      <c r="W349" t="n">
+        <v>637</v>
+      </c>
+      <c r="X349" t="n">
+        <v>455</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>941</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>575</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>472</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>1035</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>592</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>518</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>957</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>615.14</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>630</v>
+      </c>
+      <c r="AH349" t="inlineStr"/>
+      <c r="AI349" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI349"/>
+  <dimension ref="A1:AI350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35893,6 +35893,109 @@
       <c r="AH349" t="inlineStr"/>
       <c r="AI349" t="inlineStr"/>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>601.77</v>
+      </c>
+      <c r="C350" t="n">
+        <v>670</v>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="n">
+        <v>476</v>
+      </c>
+      <c r="F350" t="n">
+        <v>920</v>
+      </c>
+      <c r="G350" t="n">
+        <v>571</v>
+      </c>
+      <c r="H350" t="n">
+        <v>605</v>
+      </c>
+      <c r="I350" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="J350" t="n">
+        <v>480</v>
+      </c>
+      <c r="K350" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L350" t="n">
+        <v>643</v>
+      </c>
+      <c r="M350" t="n">
+        <v>929</v>
+      </c>
+      <c r="N350" t="n">
+        <v>660</v>
+      </c>
+      <c r="O350" t="n">
+        <v>485</v>
+      </c>
+      <c r="P350" t="n">
+        <v>957</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>685</v>
+      </c>
+      <c r="R350" t="n">
+        <v>520</v>
+      </c>
+      <c r="S350" t="n">
+        <v>985</v>
+      </c>
+      <c r="T350" t="n">
+        <v>728.5</v>
+      </c>
+      <c r="U350" t="n">
+        <v>550</v>
+      </c>
+      <c r="V350" t="n">
+        <v>920.25</v>
+      </c>
+      <c r="W350" t="n">
+        <v>665</v>
+      </c>
+      <c r="X350" t="n">
+        <v>485</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>961</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>620</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>1110</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>652</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>562</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>1097</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>655.04</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>670</v>
+      </c>
+      <c r="AH350" t="inlineStr"/>
+      <c r="AI350" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI350"/>
+  <dimension ref="A1:AI351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35996,6 +35996,109 @@
       <c r="AH350" t="inlineStr"/>
       <c r="AI350" t="inlineStr"/>
     </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>610.02</v>
+      </c>
+      <c r="C351" t="n">
+        <v>678</v>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="n">
+        <v>472</v>
+      </c>
+      <c r="F351" t="n">
+        <v>985.25</v>
+      </c>
+      <c r="G351" t="n">
+        <v>558</v>
+      </c>
+      <c r="H351" t="n">
+        <v>603</v>
+      </c>
+      <c r="I351" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="J351" t="n">
+        <v>478</v>
+      </c>
+      <c r="K351" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L351" t="n">
+        <v>661</v>
+      </c>
+      <c r="M351" t="n">
+        <v>931</v>
+      </c>
+      <c r="N351" t="n">
+        <v>666</v>
+      </c>
+      <c r="O351" t="n">
+        <v>480</v>
+      </c>
+      <c r="P351" t="n">
+        <v>1002</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>698</v>
+      </c>
+      <c r="R351" t="n">
+        <v>514</v>
+      </c>
+      <c r="S351" t="n">
+        <v>1025</v>
+      </c>
+      <c r="T351" t="n">
+        <v>685</v>
+      </c>
+      <c r="U351" t="n">
+        <v>539</v>
+      </c>
+      <c r="V351" t="n">
+        <v>965.75</v>
+      </c>
+      <c r="W351" t="n">
+        <v>669</v>
+      </c>
+      <c r="X351" t="n">
+        <v>480</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>1006</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>617</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>492</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>1110</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>632</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>557</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>1057</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>670.1</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>685</v>
+      </c>
+      <c r="AH351" t="inlineStr"/>
+      <c r="AI351" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI351"/>
+  <dimension ref="A1:AI352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36099,6 +36099,109 @@
       <c r="AH351" t="inlineStr"/>
       <c r="AI351" t="inlineStr"/>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>614.53</v>
+      </c>
+      <c r="C352" t="n">
+        <v>680</v>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="n">
+        <v>477</v>
+      </c>
+      <c r="F352" t="n">
+        <v>965.75</v>
+      </c>
+      <c r="G352" t="n">
+        <v>560</v>
+      </c>
+      <c r="H352" t="n">
+        <v>603</v>
+      </c>
+      <c r="I352" t="n">
+        <v>431</v>
+      </c>
+      <c r="J352" t="n">
+        <v>472</v>
+      </c>
+      <c r="K352" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L352" t="n">
+        <v>659</v>
+      </c>
+      <c r="M352" t="n">
+        <v>934</v>
+      </c>
+      <c r="N352" t="n">
+        <v>673</v>
+      </c>
+      <c r="O352" t="n">
+        <v>484</v>
+      </c>
+      <c r="P352" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>705</v>
+      </c>
+      <c r="R352" t="n">
+        <v>525</v>
+      </c>
+      <c r="S352" t="n">
+        <v>1005</v>
+      </c>
+      <c r="T352" t="n">
+        <v>734.5</v>
+      </c>
+      <c r="U352" t="n">
+        <v>570.25</v>
+      </c>
+      <c r="V352" t="n">
+        <v>981.25</v>
+      </c>
+      <c r="W352" t="n">
+        <v>676</v>
+      </c>
+      <c r="X352" t="n">
+        <v>484</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>1003</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>620</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>508</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>1120</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>631</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>556</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>689.84</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>705</v>
+      </c>
+      <c r="AH352" t="inlineStr"/>
+      <c r="AI352" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI352"/>
+  <dimension ref="A1:AI353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36202,6 +36202,109 @@
       <c r="AH352" t="inlineStr"/>
       <c r="AI352" t="inlineStr"/>
     </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>638.3</v>
+      </c>
+      <c r="C353" t="n">
+        <v>700</v>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="n">
+        <v>490</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1032</v>
+      </c>
+      <c r="G353" t="n">
+        <v>589</v>
+      </c>
+      <c r="H353" t="n">
+        <v>635</v>
+      </c>
+      <c r="I353" t="n">
+        <v>453</v>
+      </c>
+      <c r="J353" t="n">
+        <v>488</v>
+      </c>
+      <c r="K353" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L353" t="n">
+        <v>705</v>
+      </c>
+      <c r="M353" t="n">
+        <v>938</v>
+      </c>
+      <c r="N353" t="n">
+        <v>682</v>
+      </c>
+      <c r="O353" t="n">
+        <v>498</v>
+      </c>
+      <c r="P353" t="n">
+        <v>1044</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>720</v>
+      </c>
+      <c r="R353" t="n">
+        <v>536</v>
+      </c>
+      <c r="S353" t="n">
+        <v>1045</v>
+      </c>
+      <c r="T353" t="n">
+        <v>720.25</v>
+      </c>
+      <c r="U353" t="n">
+        <v>640</v>
+      </c>
+      <c r="V353" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="W353" t="n">
+        <v>682</v>
+      </c>
+      <c r="X353" t="n">
+        <v>498</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>1048</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>638</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>522</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>1112</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>672</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>582</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>715.1</v>
+      </c>
+      <c r="AG353" t="n">
+        <v>730</v>
+      </c>
+      <c r="AH353" t="inlineStr"/>
+      <c r="AI353" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI353"/>
+  <dimension ref="A1:AI354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36305,6 +36305,109 @@
       <c r="AH353" t="inlineStr"/>
       <c r="AI353" t="inlineStr"/>
     </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>705.61</v>
+      </c>
+      <c r="C354" t="n">
+        <v>770</v>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="n">
+        <v>555</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G354" t="n">
+        <v>613</v>
+      </c>
+      <c r="H354" t="n">
+        <v>678</v>
+      </c>
+      <c r="I354" t="n">
+        <v>470.75</v>
+      </c>
+      <c r="J354" t="n">
+        <v>530</v>
+      </c>
+      <c r="K354" t="n">
+        <v>1148</v>
+      </c>
+      <c r="L354" t="n">
+        <v>749</v>
+      </c>
+      <c r="M354" t="n">
+        <v>939</v>
+      </c>
+      <c r="N354" t="n">
+        <v>750</v>
+      </c>
+      <c r="O354" t="n">
+        <v>552</v>
+      </c>
+      <c r="P354" t="n">
+        <v>1170</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>770</v>
+      </c>
+      <c r="R354" t="n">
+        <v>584</v>
+      </c>
+      <c r="S354" t="n">
+        <v>1120</v>
+      </c>
+      <c r="T354" t="n">
+        <v>781</v>
+      </c>
+      <c r="U354" t="n">
+        <v>697</v>
+      </c>
+      <c r="V354" t="n">
+        <v>1140.25</v>
+      </c>
+      <c r="W354" t="n">
+        <v>750</v>
+      </c>
+      <c r="X354" t="n">
+        <v>552</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>1175</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>695</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>560</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>1205</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>682</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>586</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>1207</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>800.14</v>
+      </c>
+      <c r="AG354" t="n">
+        <v>810</v>
+      </c>
+      <c r="AH354" t="inlineStr"/>
+      <c r="AI354" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI354"/>
+  <dimension ref="A1:AI355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36408,6 +36408,109 @@
       <c r="AH354" t="inlineStr"/>
       <c r="AI354" t="inlineStr"/>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>707.97</v>
+      </c>
+      <c r="C355" t="n">
+        <v>785</v>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="n">
+        <v>568</v>
+      </c>
+      <c r="F355" t="n">
+        <v>1172</v>
+      </c>
+      <c r="G355" t="n">
+        <v>601.75</v>
+      </c>
+      <c r="H355" t="n">
+        <v>674</v>
+      </c>
+      <c r="I355" t="n">
+        <v>474.75</v>
+      </c>
+      <c r="J355" t="n">
+        <v>535</v>
+      </c>
+      <c r="K355" t="n">
+        <v>1156</v>
+      </c>
+      <c r="L355" t="n">
+        <v>749</v>
+      </c>
+      <c r="M355" t="n">
+        <v>938</v>
+      </c>
+      <c r="N355" t="n">
+        <v>752</v>
+      </c>
+      <c r="O355" t="n">
+        <v>580</v>
+      </c>
+      <c r="P355" t="n">
+        <v>1155</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>772</v>
+      </c>
+      <c r="R355" t="n">
+        <v>580</v>
+      </c>
+      <c r="S355" t="n">
+        <v>1075</v>
+      </c>
+      <c r="T355" t="n">
+        <v>832.5</v>
+      </c>
+      <c r="U355" t="n">
+        <v>705</v>
+      </c>
+      <c r="V355" t="n">
+        <v>1110.25</v>
+      </c>
+      <c r="W355" t="n">
+        <v>755</v>
+      </c>
+      <c r="X355" t="n">
+        <v>580</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>1160</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>687</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>552</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>1238</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>692</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>612</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>1187</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>800.02</v>
+      </c>
+      <c r="AG355" t="n">
+        <v>810</v>
+      </c>
+      <c r="AH355" t="inlineStr"/>
+      <c r="AI355" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI355"/>
+  <dimension ref="A1:AI356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36511,6 +36511,109 @@
       <c r="AH355" t="inlineStr"/>
       <c r="AI355" t="inlineStr"/>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>681.72</v>
+      </c>
+      <c r="C356" t="n">
+        <v>770</v>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="n">
+        <v>540</v>
+      </c>
+      <c r="F356" t="n">
+        <v>1097</v>
+      </c>
+      <c r="G356" t="n">
+        <v>593.75</v>
+      </c>
+      <c r="H356" t="n">
+        <v>660</v>
+      </c>
+      <c r="I356" t="n">
+        <v>481.25</v>
+      </c>
+      <c r="J356" t="n">
+        <v>530</v>
+      </c>
+      <c r="K356" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L356" t="n">
+        <v>738</v>
+      </c>
+      <c r="M356" t="n">
+        <v>943</v>
+      </c>
+      <c r="N356" t="n">
+        <v>730</v>
+      </c>
+      <c r="O356" t="n">
+        <v>568</v>
+      </c>
+      <c r="P356" t="n">
+        <v>1145</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>759</v>
+      </c>
+      <c r="R356" t="n">
+        <v>580</v>
+      </c>
+      <c r="S356" t="n">
+        <v>1070</v>
+      </c>
+      <c r="T356" t="n">
+        <v>843.75</v>
+      </c>
+      <c r="U356" t="n">
+        <v>705</v>
+      </c>
+      <c r="V356" t="n">
+        <v>1150</v>
+      </c>
+      <c r="W356" t="n">
+        <v>733</v>
+      </c>
+      <c r="X356" t="n">
+        <v>568</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>685</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>558</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>1230</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>682</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>611</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>1172</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>780.0700000000001</v>
+      </c>
+      <c r="AG356" t="n">
+        <v>790</v>
+      </c>
+      <c r="AH356" t="inlineStr"/>
+      <c r="AI356" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI356"/>
+  <dimension ref="A1:AI357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36614,6 +36614,109 @@
       <c r="AH356" t="inlineStr"/>
       <c r="AI356" t="inlineStr"/>
     </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>685.14</v>
+      </c>
+      <c r="C357" t="n">
+        <v>777</v>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="n">
+        <v>544</v>
+      </c>
+      <c r="F357" t="n">
+        <v>1141.25</v>
+      </c>
+      <c r="G357" t="n">
+        <v>601.25</v>
+      </c>
+      <c r="H357" t="n">
+        <v>650</v>
+      </c>
+      <c r="I357" t="n">
+        <v>490.75</v>
+      </c>
+      <c r="J357" t="n">
+        <v>539</v>
+      </c>
+      <c r="K357" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L357" t="n">
+        <v>742</v>
+      </c>
+      <c r="M357" t="n">
+        <v>939</v>
+      </c>
+      <c r="N357" t="n">
+        <v>730</v>
+      </c>
+      <c r="O357" t="n">
+        <v>570</v>
+      </c>
+      <c r="P357" t="n">
+        <v>1164</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>765</v>
+      </c>
+      <c r="R357" t="n">
+        <v>593</v>
+      </c>
+      <c r="S357" t="n">
+        <v>1143</v>
+      </c>
+      <c r="T357" t="n">
+        <v>852.25</v>
+      </c>
+      <c r="U357" t="n">
+        <v>714</v>
+      </c>
+      <c r="V357" t="n">
+        <v>1209.75</v>
+      </c>
+      <c r="W357" t="n">
+        <v>733</v>
+      </c>
+      <c r="X357" t="n">
+        <v>570</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>1169</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>686</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>565</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>1240</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>697</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>622</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>1217</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>764.92</v>
+      </c>
+      <c r="AG357" t="n">
+        <v>775</v>
+      </c>
+      <c r="AH357" t="inlineStr"/>
+      <c r="AI357" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI357"/>
+  <dimension ref="A1:AI358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36717,6 +36717,109 @@
       <c r="AH357" t="inlineStr"/>
       <c r="AI357" t="inlineStr"/>
     </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>706.63</v>
+      </c>
+      <c r="C358" t="n">
+        <v>798</v>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="n">
+        <v>569</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1190.25</v>
+      </c>
+      <c r="G358" t="n">
+        <v>608.75</v>
+      </c>
+      <c r="H358" t="n">
+        <v>664</v>
+      </c>
+      <c r="I358" t="n">
+        <v>498</v>
+      </c>
+      <c r="J358" t="n">
+        <v>547</v>
+      </c>
+      <c r="K358" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L358" t="n">
+        <v>757</v>
+      </c>
+      <c r="M358" t="n">
+        <v>937</v>
+      </c>
+      <c r="N358" t="n">
+        <v>755</v>
+      </c>
+      <c r="O358" t="n">
+        <v>598</v>
+      </c>
+      <c r="P358" t="n">
+        <v>1174</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>792</v>
+      </c>
+      <c r="R358" t="n">
+        <v>590</v>
+      </c>
+      <c r="S358" t="n">
+        <v>1123</v>
+      </c>
+      <c r="T358" t="n">
+        <v>810</v>
+      </c>
+      <c r="U358" t="n">
+        <v>740</v>
+      </c>
+      <c r="V358" t="n">
+        <v>1175.25</v>
+      </c>
+      <c r="W358" t="n">
+        <v>758</v>
+      </c>
+      <c r="X358" t="n">
+        <v>598</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>1179</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>695</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>575</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>1270</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>717</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>647</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>1217</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>780.2</v>
+      </c>
+      <c r="AG358" t="n">
+        <v>800</v>
+      </c>
+      <c r="AH358" t="inlineStr"/>
+      <c r="AI358" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI358"/>
+  <dimension ref="A1:AI359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36820,6 +36820,109 @@
       <c r="AH358" t="inlineStr"/>
       <c r="AI358" t="inlineStr"/>
     </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>710.58</v>
+      </c>
+      <c r="C359" t="n">
+        <v>792</v>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="n">
+        <v>578</v>
+      </c>
+      <c r="F359" t="n">
+        <v>1185.75</v>
+      </c>
+      <c r="G359" t="n">
+        <v>635.25</v>
+      </c>
+      <c r="H359" t="n">
+        <v>672</v>
+      </c>
+      <c r="I359" t="n">
+        <v>511.25</v>
+      </c>
+      <c r="J359" t="n">
+        <v>550</v>
+      </c>
+      <c r="K359" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L359" t="n">
+        <v>771</v>
+      </c>
+      <c r="M359" t="n">
+        <v>941</v>
+      </c>
+      <c r="N359" t="n">
+        <v>765</v>
+      </c>
+      <c r="O359" t="n">
+        <v>605</v>
+      </c>
+      <c r="P359" t="n">
+        <v>1179</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>792</v>
+      </c>
+      <c r="R359" t="n">
+        <v>595</v>
+      </c>
+      <c r="S359" t="n">
+        <v>1150</v>
+      </c>
+      <c r="T359" t="n">
+        <v>795</v>
+      </c>
+      <c r="U359" t="n">
+        <v>740</v>
+      </c>
+      <c r="V359" t="n">
+        <v>1165.25</v>
+      </c>
+      <c r="W359" t="n">
+        <v>766</v>
+      </c>
+      <c r="X359" t="n">
+        <v>605</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>1184</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>705</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>580</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>1285</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>735</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>655</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>1218</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>785.03</v>
+      </c>
+      <c r="AG359" t="n">
+        <v>805</v>
+      </c>
+      <c r="AH359" t="inlineStr"/>
+      <c r="AI359" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI359"/>
+  <dimension ref="A1:AI360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36923,6 +36923,109 @@
       <c r="AH359" t="inlineStr"/>
       <c r="AI359" t="inlineStr"/>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>758.78</v>
+      </c>
+      <c r="C360" t="n">
+        <v>875</v>
+      </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="n">
+        <v>626</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1249.75</v>
+      </c>
+      <c r="G360" t="n">
+        <v>634.75</v>
+      </c>
+      <c r="H360" t="n">
+        <v>697</v>
+      </c>
+      <c r="I360" t="n">
+        <v>519.25</v>
+      </c>
+      <c r="J360" t="n">
+        <v>570</v>
+      </c>
+      <c r="K360" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L360" t="n">
+        <v>843</v>
+      </c>
+      <c r="M360" t="n">
+        <v>950</v>
+      </c>
+      <c r="N360" t="n">
+        <v>795</v>
+      </c>
+      <c r="O360" t="n">
+        <v>645</v>
+      </c>
+      <c r="P360" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>832</v>
+      </c>
+      <c r="R360" t="n">
+        <v>640</v>
+      </c>
+      <c r="S360" t="n">
+        <v>1210.5</v>
+      </c>
+      <c r="T360" t="n">
+        <v>881.75</v>
+      </c>
+      <c r="U360" t="n">
+        <v>770</v>
+      </c>
+      <c r="V360" t="n">
+        <v>1272.25</v>
+      </c>
+      <c r="W360" t="n">
+        <v>796</v>
+      </c>
+      <c r="X360" t="n">
+        <v>645</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>1240</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>722</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>586</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>762</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>642</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>1212</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>817.86</v>
+      </c>
+      <c r="AG360" t="n">
+        <v>843</v>
+      </c>
+      <c r="AH360" t="inlineStr"/>
+      <c r="AI360" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI360"/>
+  <dimension ref="A1:AI361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37026,6 +37026,109 @@
       <c r="AH360" t="inlineStr"/>
       <c r="AI360" t="inlineStr"/>
     </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>759.95</v>
+      </c>
+      <c r="C361" t="n">
+        <v>877</v>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="n">
+        <v>631</v>
+      </c>
+      <c r="F361" t="n">
+        <v>1280.25</v>
+      </c>
+      <c r="G361" t="n">
+        <v>665.75</v>
+      </c>
+      <c r="H361" t="n">
+        <v>699</v>
+      </c>
+      <c r="I361" t="n">
+        <v>539.5</v>
+      </c>
+      <c r="J361" t="n">
+        <v>582</v>
+      </c>
+      <c r="K361" t="n">
+        <v>1257</v>
+      </c>
+      <c r="L361" t="n">
+        <v>853</v>
+      </c>
+      <c r="M361" t="n">
+        <v>1148</v>
+      </c>
+      <c r="N361" t="n">
+        <v>796</v>
+      </c>
+      <c r="O361" t="n">
+        <v>656</v>
+      </c>
+      <c r="P361" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>834</v>
+      </c>
+      <c r="R361" t="n">
+        <v>643</v>
+      </c>
+      <c r="S361" t="n">
+        <v>1240</v>
+      </c>
+      <c r="T361" t="n">
+        <v>852</v>
+      </c>
+      <c r="U361" t="n">
+        <v>770</v>
+      </c>
+      <c r="V361" t="n">
+        <v>1290.25</v>
+      </c>
+      <c r="W361" t="n">
+        <v>797</v>
+      </c>
+      <c r="X361" t="n">
+        <v>656</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>729</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>605</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>1326</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>787</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>652</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>1222</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>819.91</v>
+      </c>
+      <c r="AG361" t="n">
+        <v>845</v>
+      </c>
+      <c r="AH361" t="inlineStr"/>
+      <c r="AI361" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI361"/>
+  <dimension ref="A1:AI362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37129,6 +37129,109 @@
       <c r="AH361" t="inlineStr"/>
       <c r="AI361" t="inlineStr"/>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>749.63</v>
+      </c>
+      <c r="C362" t="n">
+        <v>877</v>
+      </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="n">
+        <v>625</v>
+      </c>
+      <c r="F362" t="n">
+        <v>1272.75</v>
+      </c>
+      <c r="G362" t="n">
+        <v>640.25</v>
+      </c>
+      <c r="H362" t="n">
+        <v>689</v>
+      </c>
+      <c r="I362" t="n">
+        <v>520</v>
+      </c>
+      <c r="J362" t="n">
+        <v>569</v>
+      </c>
+      <c r="K362" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L362" t="n">
+        <v>829</v>
+      </c>
+      <c r="M362" t="n">
+        <v>1348</v>
+      </c>
+      <c r="N362" t="n">
+        <v>788</v>
+      </c>
+      <c r="O362" t="n">
+        <v>660</v>
+      </c>
+      <c r="P362" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>824</v>
+      </c>
+      <c r="R362" t="n">
+        <v>630</v>
+      </c>
+      <c r="S362" t="n">
+        <v>1230</v>
+      </c>
+      <c r="T362" t="n">
+        <v>884.25</v>
+      </c>
+      <c r="U362" t="n">
+        <v>750</v>
+      </c>
+      <c r="V362" t="n">
+        <v>1255.25</v>
+      </c>
+      <c r="W362" t="n">
+        <v>789</v>
+      </c>
+      <c r="X362" t="n">
+        <v>660</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>720</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>589</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>1310</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>777</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>622</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>1217</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>807.03</v>
+      </c>
+      <c r="AG362" t="n">
+        <v>832</v>
+      </c>
+      <c r="AH362" t="inlineStr"/>
+      <c r="AI362" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI362"/>
+  <dimension ref="A1:AI363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37232,6 +37232,109 @@
       <c r="AH362" t="inlineStr"/>
       <c r="AI362" t="inlineStr"/>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>710.04</v>
+      </c>
+      <c r="C363" t="n">
+        <v>845</v>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="n">
+        <v>582</v>
+      </c>
+      <c r="F363" t="n">
+        <v>1230.5</v>
+      </c>
+      <c r="G363" t="n">
+        <v>616</v>
+      </c>
+      <c r="H363" t="n">
+        <v>665</v>
+      </c>
+      <c r="I363" t="n">
+        <v>493.75</v>
+      </c>
+      <c r="J363" t="n">
+        <v>535</v>
+      </c>
+      <c r="K363" t="n">
+        <v>1261</v>
+      </c>
+      <c r="L363" t="n">
+        <v>788</v>
+      </c>
+      <c r="M363" t="n">
+        <v>1351</v>
+      </c>
+      <c r="N363" t="n">
+        <v>758</v>
+      </c>
+      <c r="O363" t="n">
+        <v>630</v>
+      </c>
+      <c r="P363" t="n">
+        <v>1213</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>775</v>
+      </c>
+      <c r="R363" t="n">
+        <v>594</v>
+      </c>
+      <c r="S363" t="n">
+        <v>1167</v>
+      </c>
+      <c r="T363" t="n">
+        <v>836</v>
+      </c>
+      <c r="U363" t="n">
+        <v>700</v>
+      </c>
+      <c r="V363" t="n">
+        <v>1190.25</v>
+      </c>
+      <c r="W363" t="n">
+        <v>759</v>
+      </c>
+      <c r="X363" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>1218</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>722</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>590</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>1290</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>743</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>591</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>1217</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>769.9299999999999</v>
+      </c>
+      <c r="AG363" t="n">
+        <v>795</v>
+      </c>
+      <c r="AH363" t="inlineStr"/>
+      <c r="AI363" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI363"/>
+  <dimension ref="A1:AI364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37335,6 +37335,109 @@
       <c r="AH363" t="inlineStr"/>
       <c r="AI363" t="inlineStr"/>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>694.38</v>
+      </c>
+      <c r="C364" t="n">
+        <v>828</v>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="n">
+        <v>560</v>
+      </c>
+      <c r="F364" t="n">
+        <v>1190.25</v>
+      </c>
+      <c r="G364" t="n">
+        <v>596.25</v>
+      </c>
+      <c r="H364" t="n">
+        <v>647</v>
+      </c>
+      <c r="I364" t="n">
+        <v>469</v>
+      </c>
+      <c r="J364" t="n">
+        <v>522</v>
+      </c>
+      <c r="K364" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L364" t="n">
+        <v>780</v>
+      </c>
+      <c r="M364" t="n">
+        <v>1354</v>
+      </c>
+      <c r="N364" t="n">
+        <v>745</v>
+      </c>
+      <c r="O364" t="n">
+        <v>610</v>
+      </c>
+      <c r="P364" t="n">
+        <v>1208</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>765</v>
+      </c>
+      <c r="R364" t="n">
+        <v>580</v>
+      </c>
+      <c r="S364" t="n">
+        <v>1150</v>
+      </c>
+      <c r="T364" t="n">
+        <v>780</v>
+      </c>
+      <c r="U364" t="n">
+        <v>663</v>
+      </c>
+      <c r="V364" t="n">
+        <v>1236</v>
+      </c>
+      <c r="W364" t="n">
+        <v>746</v>
+      </c>
+      <c r="X364" t="n">
+        <v>610</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>1213</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>695</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>560</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>1282</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>726</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>541</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>1222</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>753.89</v>
+      </c>
+      <c r="AG364" t="n">
+        <v>779</v>
+      </c>
+      <c r="AH364" t="inlineStr"/>
+      <c r="AI364" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI364"/>
+  <dimension ref="A1:AI365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37438,6 +37438,109 @@
       <c r="AH364" t="inlineStr"/>
       <c r="AI364" t="inlineStr"/>
     </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>711.72</v>
+      </c>
+      <c r="C365" t="n">
+        <v>838</v>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="n">
+        <v>568</v>
+      </c>
+      <c r="F365" t="n">
+        <v>1205.75</v>
+      </c>
+      <c r="G365" t="n">
+        <v>638.75</v>
+      </c>
+      <c r="H365" t="n">
+        <v>667</v>
+      </c>
+      <c r="I365" t="n">
+        <v>494.5</v>
+      </c>
+      <c r="J365" t="n">
+        <v>540</v>
+      </c>
+      <c r="K365" t="n">
+        <v>1293</v>
+      </c>
+      <c r="L365" t="n">
+        <v>806</v>
+      </c>
+      <c r="M365" t="n">
+        <v>1345</v>
+      </c>
+      <c r="N365" t="n">
+        <v>767</v>
+      </c>
+      <c r="O365" t="n">
+        <v>638</v>
+      </c>
+      <c r="P365" t="n">
+        <v>1241</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>790</v>
+      </c>
+      <c r="R365" t="n">
+        <v>600</v>
+      </c>
+      <c r="S365" t="n">
+        <v>1190</v>
+      </c>
+      <c r="T365" t="n">
+        <v>825.5</v>
+      </c>
+      <c r="U365" t="n">
+        <v>680</v>
+      </c>
+      <c r="V365" t="n">
+        <v>1256.5</v>
+      </c>
+      <c r="W365" t="n">
+        <v>768</v>
+      </c>
+      <c r="X365" t="n">
+        <v>638</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>1246</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>733</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>578</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>1333</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>755</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>556</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>1262</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>760.38</v>
+      </c>
+      <c r="AG365" t="n">
+        <v>785</v>
+      </c>
+      <c r="AH365" t="inlineStr"/>
+      <c r="AI365" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI365"/>
+  <dimension ref="A1:AI366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37541,6 +37541,109 @@
       <c r="AH365" t="inlineStr"/>
       <c r="AI365" t="inlineStr"/>
     </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>741.98</v>
+      </c>
+      <c r="C366" t="n">
+        <v>855</v>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="n">
+        <v>592</v>
+      </c>
+      <c r="F366" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G366" t="n">
+        <v>630.75</v>
+      </c>
+      <c r="H366" t="n">
+        <v>680</v>
+      </c>
+      <c r="I366" t="n">
+        <v>484.75</v>
+      </c>
+      <c r="J366" t="n">
+        <v>535</v>
+      </c>
+      <c r="K366" t="n">
+        <v>1290</v>
+      </c>
+      <c r="L366" t="n">
+        <v>811</v>
+      </c>
+      <c r="M366" t="n">
+        <v>1344</v>
+      </c>
+      <c r="N366" t="n">
+        <v>798</v>
+      </c>
+      <c r="O366" t="n">
+        <v>653</v>
+      </c>
+      <c r="P366" t="n">
+        <v>1278</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>815</v>
+      </c>
+      <c r="R366" t="n">
+        <v>620.25</v>
+      </c>
+      <c r="S366" t="n">
+        <v>1225</v>
+      </c>
+      <c r="T366" t="n">
+        <v>810</v>
+      </c>
+      <c r="U366" t="n">
+        <v>678</v>
+      </c>
+      <c r="V366" t="n">
+        <v>1269</v>
+      </c>
+      <c r="W366" t="n">
+        <v>798</v>
+      </c>
+      <c r="X366" t="n">
+        <v>653</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>1283</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>720</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>560</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>1335</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>765</v>
+      </c>
+      <c r="AD366" t="n">
+        <v>571</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>1261</v>
+      </c>
+      <c r="AF366" t="n">
+        <v>785.09</v>
+      </c>
+      <c r="AG366" t="n">
+        <v>810</v>
+      </c>
+      <c r="AH366" t="inlineStr"/>
+      <c r="AI366" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI366"/>
+  <dimension ref="A1:AI367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37644,6 +37644,109 @@
       <c r="AH366" t="inlineStr"/>
       <c r="AI366" t="inlineStr"/>
     </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>741.5700000000001</v>
+      </c>
+      <c r="C367" t="n">
+        <v>855</v>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="n">
+        <v>580</v>
+      </c>
+      <c r="F367" t="n">
+        <v>1216</v>
+      </c>
+      <c r="G367" t="n">
+        <v>636.5</v>
+      </c>
+      <c r="H367" t="n">
+        <v>680</v>
+      </c>
+      <c r="I367" t="n">
+        <v>488</v>
+      </c>
+      <c r="J367" t="n">
+        <v>534</v>
+      </c>
+      <c r="K367" t="n">
+        <v>1294</v>
+      </c>
+      <c r="L367" t="n">
+        <v>832</v>
+      </c>
+      <c r="M367" t="n">
+        <v>1352</v>
+      </c>
+      <c r="N367" t="n">
+        <v>794</v>
+      </c>
+      <c r="O367" t="n">
+        <v>630</v>
+      </c>
+      <c r="P367" t="n">
+        <v>1258</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>818</v>
+      </c>
+      <c r="R367" t="n">
+        <v>605</v>
+      </c>
+      <c r="S367" t="n">
+        <v>1205</v>
+      </c>
+      <c r="T367" t="n">
+        <v>832.25</v>
+      </c>
+      <c r="U367" t="n">
+        <v>668</v>
+      </c>
+      <c r="V367" t="n">
+        <v>1231</v>
+      </c>
+      <c r="W367" t="n">
+        <v>794</v>
+      </c>
+      <c r="X367" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y367" t="n">
+        <v>1263</v>
+      </c>
+      <c r="Z367" t="n">
+        <v>715</v>
+      </c>
+      <c r="AA367" t="n">
+        <v>558</v>
+      </c>
+      <c r="AB367" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AC367" t="n">
+        <v>772</v>
+      </c>
+      <c r="AD367" t="n">
+        <v>572</v>
+      </c>
+      <c r="AE367" t="n">
+        <v>1266</v>
+      </c>
+      <c r="AF367" t="n">
+        <v>770</v>
+      </c>
+      <c r="AG367" t="n">
+        <v>795</v>
+      </c>
+      <c r="AH367" t="inlineStr"/>
+      <c r="AI367" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI367"/>
+  <dimension ref="A1:AI368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37747,6 +37747,109 @@
       <c r="AH367" t="inlineStr"/>
       <c r="AI367" t="inlineStr"/>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>748.55</v>
+      </c>
+      <c r="C368" t="n">
+        <v>858</v>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="n">
+        <v>565</v>
+      </c>
+      <c r="F368" t="n">
+        <v>1195.75</v>
+      </c>
+      <c r="G368" t="n">
+        <v>596.5</v>
+      </c>
+      <c r="H368" t="n">
+        <v>664</v>
+      </c>
+      <c r="I368" t="n">
+        <v>467</v>
+      </c>
+      <c r="J368" t="n">
+        <v>518</v>
+      </c>
+      <c r="K368" t="n">
+        <v>1218</v>
+      </c>
+      <c r="L368" t="n">
+        <v>823</v>
+      </c>
+      <c r="M368" t="n">
+        <v>1351</v>
+      </c>
+      <c r="N368" t="n">
+        <v>785</v>
+      </c>
+      <c r="O368" t="n">
+        <v>609</v>
+      </c>
+      <c r="P368" t="n">
+        <v>1230</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>827</v>
+      </c>
+      <c r="R368" t="n">
+        <v>597</v>
+      </c>
+      <c r="S368" t="n">
+        <v>1185</v>
+      </c>
+      <c r="T368" t="n">
+        <v>825</v>
+      </c>
+      <c r="U368" t="n">
+        <v>659</v>
+      </c>
+      <c r="V368" t="n">
+        <v>1229.25</v>
+      </c>
+      <c r="W368" t="n">
+        <v>785</v>
+      </c>
+      <c r="X368" t="n">
+        <v>609</v>
+      </c>
+      <c r="Y368" t="n">
+        <v>1235</v>
+      </c>
+      <c r="Z368" t="n">
+        <v>698</v>
+      </c>
+      <c r="AA368" t="n">
+        <v>551</v>
+      </c>
+      <c r="AB368" t="n">
+        <v>1295</v>
+      </c>
+      <c r="AC368" t="n">
+        <v>709</v>
+      </c>
+      <c r="AD368" t="n">
+        <v>546</v>
+      </c>
+      <c r="AE368" t="n">
+        <v>1192</v>
+      </c>
+      <c r="AF368" t="n">
+        <v>769.98</v>
+      </c>
+      <c r="AG368" t="n">
+        <v>795</v>
+      </c>
+      <c r="AH368" t="inlineStr"/>
+      <c r="AI368" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI368"/>
+  <dimension ref="A1:AI369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37850,6 +37850,109 @@
       <c r="AH368" t="inlineStr"/>
       <c r="AI368" t="inlineStr"/>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>751.26</v>
+      </c>
+      <c r="C369" t="n">
+        <v>863</v>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="n">
+        <v>590</v>
+      </c>
+      <c r="F369" t="n">
+        <v>1137.5</v>
+      </c>
+      <c r="G369" t="n">
+        <v>576.5</v>
+      </c>
+      <c r="H369" t="n">
+        <v>640</v>
+      </c>
+      <c r="I369" t="n">
+        <v>453.25</v>
+      </c>
+      <c r="J369" t="n">
+        <v>502</v>
+      </c>
+      <c r="K369" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L369" t="n">
+        <v>818</v>
+      </c>
+      <c r="M369" t="n">
+        <v>1352</v>
+      </c>
+      <c r="N369" t="n">
+        <v>795</v>
+      </c>
+      <c r="O369" t="n">
+        <v>615</v>
+      </c>
+      <c r="P369" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>835</v>
+      </c>
+      <c r="R369" t="n">
+        <v>618</v>
+      </c>
+      <c r="S369" t="n">
+        <v>1130</v>
+      </c>
+      <c r="T369" t="n">
+        <v>820</v>
+      </c>
+      <c r="U369" t="n">
+        <v>679</v>
+      </c>
+      <c r="V369" t="n">
+        <v>1162</v>
+      </c>
+      <c r="W369" t="n">
+        <v>795</v>
+      </c>
+      <c r="X369" t="n">
+        <v>615</v>
+      </c>
+      <c r="Y369" t="n">
+        <v>1205</v>
+      </c>
+      <c r="Z369" t="n">
+        <v>680</v>
+      </c>
+      <c r="AA369" t="n">
+        <v>548</v>
+      </c>
+      <c r="AB369" t="n">
+        <v>1236</v>
+      </c>
+      <c r="AC369" t="n">
+        <v>674</v>
+      </c>
+      <c r="AD369" t="n">
+        <v>536</v>
+      </c>
+      <c r="AE369" t="n">
+        <v>1077</v>
+      </c>
+      <c r="AF369" t="n">
+        <v>773.03</v>
+      </c>
+      <c r="AG369" t="n">
+        <v>798</v>
+      </c>
+      <c r="AH369" t="inlineStr"/>
+      <c r="AI369" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI369"/>
+  <dimension ref="A1:AI370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37953,6 +37953,109 @@
       <c r="AH369" t="inlineStr"/>
       <c r="AI369" t="inlineStr"/>
     </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>712.99</v>
+      </c>
+      <c r="C370" t="n">
+        <v>829</v>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="n">
+        <v>577</v>
+      </c>
+      <c r="F370" t="n">
+        <v>1090.5</v>
+      </c>
+      <c r="G370" t="n">
+        <v>568.25</v>
+      </c>
+      <c r="H370" t="n">
+        <v>620</v>
+      </c>
+      <c r="I370" t="n">
+        <v>443.75</v>
+      </c>
+      <c r="J370" t="n">
+        <v>502</v>
+      </c>
+      <c r="K370" t="n">
+        <v>1149</v>
+      </c>
+      <c r="L370" t="n">
+        <v>793</v>
+      </c>
+      <c r="M370" t="n">
+        <v>1347</v>
+      </c>
+      <c r="N370" t="n">
+        <v>780</v>
+      </c>
+      <c r="O370" t="n">
+        <v>600</v>
+      </c>
+      <c r="P370" t="n">
+        <v>1165</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>815</v>
+      </c>
+      <c r="R370" t="n">
+        <v>609</v>
+      </c>
+      <c r="S370" t="n">
+        <v>1088</v>
+      </c>
+      <c r="T370" t="n">
+        <v>775</v>
+      </c>
+      <c r="U370" t="n">
+        <v>670</v>
+      </c>
+      <c r="V370" t="n">
+        <v>1110.25</v>
+      </c>
+      <c r="W370" t="n">
+        <v>780</v>
+      </c>
+      <c r="X370" t="n">
+        <v>600</v>
+      </c>
+      <c r="Y370" t="n">
+        <v>1170</v>
+      </c>
+      <c r="Z370" t="n">
+        <v>640</v>
+      </c>
+      <c r="AA370" t="n">
+        <v>524</v>
+      </c>
+      <c r="AB370" t="n">
+        <v>1210</v>
+      </c>
+      <c r="AC370" t="n">
+        <v>677</v>
+      </c>
+      <c r="AD370" t="n">
+        <v>535</v>
+      </c>
+      <c r="AE370" t="n">
+        <v>1099</v>
+      </c>
+      <c r="AF370" t="n">
+        <v>730.05</v>
+      </c>
+      <c r="AG370" t="n">
+        <v>755</v>
+      </c>
+      <c r="AH370" t="inlineStr"/>
+      <c r="AI370" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI370"/>
+  <dimension ref="A1:AI371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38056,6 +38056,109 @@
       <c r="AH370" t="inlineStr"/>
       <c r="AI370" t="inlineStr"/>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>710.08</v>
+      </c>
+      <c r="C371" t="n">
+        <v>827</v>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="n">
+        <v>580</v>
+      </c>
+      <c r="F371" t="n">
+        <v>1106.75</v>
+      </c>
+      <c r="G371" t="n">
+        <v>575.75</v>
+      </c>
+      <c r="H371" t="n">
+        <v>618</v>
+      </c>
+      <c r="I371" t="n">
+        <v>457.25</v>
+      </c>
+      <c r="J371" t="n">
+        <v>497</v>
+      </c>
+      <c r="K371" t="n">
+        <v>1124</v>
+      </c>
+      <c r="L371" t="n">
+        <v>784</v>
+      </c>
+      <c r="M371" t="n">
+        <v>1346</v>
+      </c>
+      <c r="N371" t="n">
+        <v>780</v>
+      </c>
+      <c r="O371" t="n">
+        <v>595</v>
+      </c>
+      <c r="P371" t="n">
+        <v>1170</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>814</v>
+      </c>
+      <c r="R371" t="n">
+        <v>610</v>
+      </c>
+      <c r="S371" t="n">
+        <v>1083</v>
+      </c>
+      <c r="T371" t="n">
+        <v>790.25</v>
+      </c>
+      <c r="U371" t="n">
+        <v>660</v>
+      </c>
+      <c r="V371" t="n">
+        <v>1133.5</v>
+      </c>
+      <c r="W371" t="n">
+        <v>780</v>
+      </c>
+      <c r="X371" t="n">
+        <v>595</v>
+      </c>
+      <c r="Y371" t="n">
+        <v>1175</v>
+      </c>
+      <c r="Z371" t="n">
+        <v>649</v>
+      </c>
+      <c r="AA371" t="n">
+        <v>526</v>
+      </c>
+      <c r="AB371" t="n">
+        <v>1198</v>
+      </c>
+      <c r="AC371" t="n">
+        <v>697</v>
+      </c>
+      <c r="AD371" t="n">
+        <v>545</v>
+      </c>
+      <c r="AE371" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AF371" t="n">
+        <v>735.21</v>
+      </c>
+      <c r="AG371" t="n">
+        <v>760</v>
+      </c>
+      <c r="AH371" t="inlineStr"/>
+      <c r="AI371" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI371"/>
+  <dimension ref="A1:AI372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38159,6 +38159,109 @@
       <c r="AH371" t="inlineStr"/>
       <c r="AI371" t="inlineStr"/>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>743.76</v>
+      </c>
+      <c r="C372" t="n">
+        <v>845</v>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="n">
+        <v>606</v>
+      </c>
+      <c r="F372" t="n">
+        <v>1145</v>
+      </c>
+      <c r="G372" t="n">
+        <v>584.75</v>
+      </c>
+      <c r="H372" t="n">
+        <v>636</v>
+      </c>
+      <c r="I372" t="n">
+        <v>466.25</v>
+      </c>
+      <c r="J372" t="n">
+        <v>514</v>
+      </c>
+      <c r="K372" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L372" t="n">
+        <v>798</v>
+      </c>
+      <c r="M372" t="n">
+        <v>1348</v>
+      </c>
+      <c r="N372" t="n">
+        <v>810</v>
+      </c>
+      <c r="O372" t="n">
+        <v>621</v>
+      </c>
+      <c r="P372" t="n">
+        <v>1211</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>840</v>
+      </c>
+      <c r="R372" t="n">
+        <v>637</v>
+      </c>
+      <c r="S372" t="n">
+        <v>1124</v>
+      </c>
+      <c r="T372" t="n">
+        <v>795.5</v>
+      </c>
+      <c r="U372" t="n">
+        <v>660</v>
+      </c>
+      <c r="V372" t="n">
+        <v>1174.25</v>
+      </c>
+      <c r="W372" t="n">
+        <v>810</v>
+      </c>
+      <c r="X372" t="n">
+        <v>621</v>
+      </c>
+      <c r="Y372" t="n">
+        <v>1216</v>
+      </c>
+      <c r="Z372" t="n">
+        <v>677</v>
+      </c>
+      <c r="AA372" t="n">
+        <v>547</v>
+      </c>
+      <c r="AB372" t="n">
+        <v>1256</v>
+      </c>
+      <c r="AC372" t="n">
+        <v>692</v>
+      </c>
+      <c r="AD372" t="n">
+        <v>546</v>
+      </c>
+      <c r="AE372" t="n">
+        <v>1172</v>
+      </c>
+      <c r="AF372" t="n">
+        <v>774.86</v>
+      </c>
+      <c r="AG372" t="n">
+        <v>800</v>
+      </c>
+      <c r="AH372" t="inlineStr"/>
+      <c r="AI372" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI372"/>
+  <dimension ref="A1:AI373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38262,6 +38262,73 @@
       <c r="AH372" t="inlineStr"/>
       <c r="AI372" t="inlineStr"/>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="n">
+        <v>602.75</v>
+      </c>
+      <c r="H373" t="n">
+        <v>648</v>
+      </c>
+      <c r="I373" t="n">
+        <v>480.75</v>
+      </c>
+      <c r="J373" t="n">
+        <v>525</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1246</v>
+      </c>
+      <c r="L373" t="n">
+        <v>818</v>
+      </c>
+      <c r="M373" t="n">
+        <v>1350</v>
+      </c>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr"/>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
+      <c r="S373" t="inlineStr"/>
+      <c r="T373" t="inlineStr"/>
+      <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr"/>
+      <c r="W373" t="inlineStr"/>
+      <c r="X373" t="inlineStr"/>
+      <c r="Y373" t="inlineStr"/>
+      <c r="Z373" t="n">
+        <v>685</v>
+      </c>
+      <c r="AA373" t="n">
+        <v>568</v>
+      </c>
+      <c r="AB373" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AC373" t="n">
+        <v>717</v>
+      </c>
+      <c r="AD373" t="n">
+        <v>602</v>
+      </c>
+      <c r="AE373" t="n">
+        <v>1275</v>
+      </c>
+      <c r="AF373" t="inlineStr"/>
+      <c r="AG373" t="inlineStr"/>
+      <c r="AH373" t="inlineStr"/>
+      <c r="AI373" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI373"/>
+  <dimension ref="A1:AI374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38329,6 +38329,109 @@
       <c r="AH373" t="inlineStr"/>
       <c r="AI373" t="inlineStr"/>
     </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>758.17</v>
+      </c>
+      <c r="C374" t="n">
+        <v>865</v>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="n">
+        <v>627</v>
+      </c>
+      <c r="F374" t="n">
+        <v>1232.75</v>
+      </c>
+      <c r="G374" t="n">
+        <v>606.25</v>
+      </c>
+      <c r="H374" t="n">
+        <v>654</v>
+      </c>
+      <c r="I374" t="n">
+        <v>486.25</v>
+      </c>
+      <c r="J374" t="n">
+        <v>528</v>
+      </c>
+      <c r="K374" t="n">
+        <v>1265</v>
+      </c>
+      <c r="L374" t="n">
+        <v>816</v>
+      </c>
+      <c r="M374" t="n">
+        <v>1349</v>
+      </c>
+      <c r="N374" t="n">
+        <v>824</v>
+      </c>
+      <c r="O374" t="n">
+        <v>635</v>
+      </c>
+      <c r="P374" t="n">
+        <v>1281</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>850</v>
+      </c>
+      <c r="R374" t="n">
+        <v>664</v>
+      </c>
+      <c r="S374" t="n">
+        <v>1222</v>
+      </c>
+      <c r="T374" t="n">
+        <v>820</v>
+      </c>
+      <c r="U374" t="n">
+        <v>660</v>
+      </c>
+      <c r="V374" t="n">
+        <v>1235</v>
+      </c>
+      <c r="W374" t="n">
+        <v>824</v>
+      </c>
+      <c r="X374" t="n">
+        <v>635</v>
+      </c>
+      <c r="Y374" t="n">
+        <v>1286</v>
+      </c>
+      <c r="Z374" t="n">
+        <v>700</v>
+      </c>
+      <c r="AA374" t="n">
+        <v>578</v>
+      </c>
+      <c r="AB374" t="n">
+        <v>1365</v>
+      </c>
+      <c r="AC374" t="n">
+        <v>732</v>
+      </c>
+      <c r="AD374" t="n">
+        <v>596.5</v>
+      </c>
+      <c r="AE374" t="n">
+        <v>1266</v>
+      </c>
+      <c r="AF374" t="n">
+        <v>806.84</v>
+      </c>
+      <c r="AG374" t="n">
+        <v>817</v>
+      </c>
+      <c r="AH374" t="inlineStr"/>
+      <c r="AI374" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI374"/>
+  <dimension ref="A1:AI375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38432,6 +38432,109 @@
       <c r="AH374" t="inlineStr"/>
       <c r="AI374" t="inlineStr"/>
     </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>746.17</v>
+      </c>
+      <c r="C375" t="n">
+        <v>840</v>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="n">
+        <v>631</v>
+      </c>
+      <c r="F375" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G375" t="n">
+        <v>609.75</v>
+      </c>
+      <c r="H375" t="n">
+        <v>662</v>
+      </c>
+      <c r="I375" t="n">
+        <v>491.5</v>
+      </c>
+      <c r="J375" t="n">
+        <v>544</v>
+      </c>
+      <c r="K375" t="n">
+        <v>1255</v>
+      </c>
+      <c r="L375" t="n">
+        <v>807</v>
+      </c>
+      <c r="M375" t="n">
+        <v>1344</v>
+      </c>
+      <c r="N375" t="n">
+        <v>814</v>
+      </c>
+      <c r="O375" t="n">
+        <v>631</v>
+      </c>
+      <c r="P375" t="n">
+        <v>1255</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>838</v>
+      </c>
+      <c r="R375" t="n">
+        <v>640</v>
+      </c>
+      <c r="S375" t="n">
+        <v>1200</v>
+      </c>
+      <c r="T375" t="n">
+        <v>813</v>
+      </c>
+      <c r="U375" t="n">
+        <v>650</v>
+      </c>
+      <c r="V375" t="n">
+        <v>1236.25</v>
+      </c>
+      <c r="W375" t="n">
+        <v>814</v>
+      </c>
+      <c r="X375" t="n">
+        <v>631</v>
+      </c>
+      <c r="Y375" t="n">
+        <v>1260</v>
+      </c>
+      <c r="Z375" t="n">
+        <v>695</v>
+      </c>
+      <c r="AA375" t="n">
+        <v>580</v>
+      </c>
+      <c r="AB375" t="n">
+        <v>1353</v>
+      </c>
+      <c r="AC375" t="n">
+        <v>735</v>
+      </c>
+      <c r="AD375" t="n">
+        <v>597</v>
+      </c>
+      <c r="AE375" t="n">
+        <v>1282</v>
+      </c>
+      <c r="AF375" t="n">
+        <v>795.17</v>
+      </c>
+      <c r="AG375" t="n">
+        <v>805</v>
+      </c>
+      <c r="AH375" t="inlineStr"/>
+      <c r="AI375" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI375"/>
+  <dimension ref="A1:AI376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38535,6 +38535,109 @@
       <c r="AH375" t="inlineStr"/>
       <c r="AI375" t="inlineStr"/>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>743.7</v>
+      </c>
+      <c r="C376" t="n">
+        <v>818</v>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="n">
+        <v>627</v>
+      </c>
+      <c r="F376" t="n">
+        <v>1221.5</v>
+      </c>
+      <c r="G376" t="n">
+        <v>610</v>
+      </c>
+      <c r="H376" t="n">
+        <v>655</v>
+      </c>
+      <c r="I376" t="n">
+        <v>495.25</v>
+      </c>
+      <c r="J376" t="n">
+        <v>530</v>
+      </c>
+      <c r="K376" t="n">
+        <v>1244</v>
+      </c>
+      <c r="L376" t="n">
+        <v>805</v>
+      </c>
+      <c r="M376" t="n">
+        <v>1339</v>
+      </c>
+      <c r="N376" t="n">
+        <v>810</v>
+      </c>
+      <c r="O376" t="n">
+        <v>633</v>
+      </c>
+      <c r="P376" t="n">
+        <v>1254</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>820</v>
+      </c>
+      <c r="R376" t="n">
+        <v>645</v>
+      </c>
+      <c r="S376" t="n">
+        <v>1202.75</v>
+      </c>
+      <c r="T376" t="n">
+        <v>818.75</v>
+      </c>
+      <c r="U376" t="n">
+        <v>650</v>
+      </c>
+      <c r="V376" t="n">
+        <v>1258.25</v>
+      </c>
+      <c r="W376" t="n">
+        <v>810</v>
+      </c>
+      <c r="X376" t="n">
+        <v>633</v>
+      </c>
+      <c r="Y376" t="n">
+        <v>1259</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>688</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>578</v>
+      </c>
+      <c r="AB376" t="n">
+        <v>1344</v>
+      </c>
+      <c r="AC376" t="n">
+        <v>702</v>
+      </c>
+      <c r="AD376" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="AE376" t="n">
+        <v>1287</v>
+      </c>
+      <c r="AF376" t="n">
+        <v>792.28</v>
+      </c>
+      <c r="AG376" t="n">
+        <v>802</v>
+      </c>
+      <c r="AH376" t="inlineStr"/>
+      <c r="AI376" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI376"/>
+  <dimension ref="A1:AI377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38638,6 +38638,109 @@
       <c r="AH376" t="inlineStr"/>
       <c r="AI376" t="inlineStr"/>
     </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>752.38</v>
+      </c>
+      <c r="C377" t="n">
+        <v>827</v>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="n">
+        <v>637</v>
+      </c>
+      <c r="F377" t="n">
+        <v>1245.5</v>
+      </c>
+      <c r="G377" t="n">
+        <v>609.25</v>
+      </c>
+      <c r="H377" t="n">
+        <v>648</v>
+      </c>
+      <c r="I377" t="n">
+        <v>500.25</v>
+      </c>
+      <c r="J377" t="n">
+        <v>533</v>
+      </c>
+      <c r="K377" t="n">
+        <v>1244</v>
+      </c>
+      <c r="L377" t="n">
+        <v>811</v>
+      </c>
+      <c r="M377" t="n">
+        <v>1335</v>
+      </c>
+      <c r="N377" t="n">
+        <v>819</v>
+      </c>
+      <c r="O377" t="n">
+        <v>630</v>
+      </c>
+      <c r="P377" t="n">
+        <v>1265</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>829</v>
+      </c>
+      <c r="R377" t="n">
+        <v>642</v>
+      </c>
+      <c r="S377" t="n">
+        <v>1200</v>
+      </c>
+      <c r="T377" t="n">
+        <v>835.25</v>
+      </c>
+      <c r="U377" t="n">
+        <v>620</v>
+      </c>
+      <c r="V377" t="n">
+        <v>1266</v>
+      </c>
+      <c r="W377" t="n">
+        <v>819</v>
+      </c>
+      <c r="X377" t="n">
+        <v>630</v>
+      </c>
+      <c r="Y377" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Z377" t="n">
+        <v>683</v>
+      </c>
+      <c r="AA377" t="n">
+        <v>588</v>
+      </c>
+      <c r="AB377" t="n">
+        <v>1349</v>
+      </c>
+      <c r="AC377" t="n">
+        <v>699</v>
+      </c>
+      <c r="AD377" t="n">
+        <v>574.5</v>
+      </c>
+      <c r="AE377" t="n">
+        <v>1253</v>
+      </c>
+      <c r="AF377" t="n">
+        <v>800.96</v>
+      </c>
+      <c r="AG377" t="n">
+        <v>811</v>
+      </c>
+      <c r="AH377" t="inlineStr"/>
+      <c r="AI377" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI377"/>
+  <dimension ref="A1:AI378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38741,6 +38741,109 @@
       <c r="AH377" t="inlineStr"/>
       <c r="AI377" t="inlineStr"/>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>747.9400000000001</v>
+      </c>
+      <c r="C378" t="n">
+        <v>832</v>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="n">
+        <v>645</v>
+      </c>
+      <c r="F378" t="n">
+        <v>1246.75</v>
+      </c>
+      <c r="G378" t="n">
+        <v>605</v>
+      </c>
+      <c r="H378" t="n">
+        <v>662</v>
+      </c>
+      <c r="I378" t="n">
+        <v>515.75</v>
+      </c>
+      <c r="J378" t="n">
+        <v>550</v>
+      </c>
+      <c r="K378" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L378" t="n">
+        <v>815</v>
+      </c>
+      <c r="M378" t="n">
+        <v>1371</v>
+      </c>
+      <c r="N378" t="n">
+        <v>817</v>
+      </c>
+      <c r="O378" t="n">
+        <v>643</v>
+      </c>
+      <c r="P378" t="n">
+        <v>1264</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>820</v>
+      </c>
+      <c r="R378" t="n">
+        <v>649</v>
+      </c>
+      <c r="S378" t="n">
+        <v>1189</v>
+      </c>
+      <c r="T378" t="n">
+        <v>848.75</v>
+      </c>
+      <c r="U378" t="n">
+        <v>620</v>
+      </c>
+      <c r="V378" t="n">
+        <v>1279.25</v>
+      </c>
+      <c r="W378" t="n">
+        <v>817</v>
+      </c>
+      <c r="X378" t="n">
+        <v>643</v>
+      </c>
+      <c r="Y378" t="n">
+        <v>1269</v>
+      </c>
+      <c r="Z378" t="n">
+        <v>675</v>
+      </c>
+      <c r="AA378" t="n">
+        <v>586</v>
+      </c>
+      <c r="AB378" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AC378" t="n">
+        <v>705</v>
+      </c>
+      <c r="AD378" t="n">
+        <v>577</v>
+      </c>
+      <c r="AE378" t="n">
+        <v>1282</v>
+      </c>
+      <c r="AF378" t="n">
+        <v>804.89</v>
+      </c>
+      <c r="AG378" t="n">
+        <v>815</v>
+      </c>
+      <c r="AH378" t="inlineStr"/>
+      <c r="AI378" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI378"/>
+  <dimension ref="A1:AI379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38844,6 +38844,109 @@
       <c r="AH378" t="inlineStr"/>
       <c r="AI378" t="inlineStr"/>
     </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>752.29</v>
+      </c>
+      <c r="C379" t="n">
+        <v>835</v>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="n">
+        <v>662</v>
+      </c>
+      <c r="F379" t="n">
+        <v>1274.5</v>
+      </c>
+      <c r="G379" t="n">
+        <v>619</v>
+      </c>
+      <c r="H379" t="n">
+        <v>664</v>
+      </c>
+      <c r="I379" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="J379" t="n">
+        <v>576</v>
+      </c>
+      <c r="K379" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L379" t="n">
+        <v>817</v>
+      </c>
+      <c r="M379" t="n">
+        <v>1374</v>
+      </c>
+      <c r="N379" t="n">
+        <v>810</v>
+      </c>
+      <c r="O379" t="n">
+        <v>650</v>
+      </c>
+      <c r="P379" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>824</v>
+      </c>
+      <c r="R379" t="n">
+        <v>671</v>
+      </c>
+      <c r="S379" t="n">
+        <v>1210</v>
+      </c>
+      <c r="T379" t="n">
+        <v>856</v>
+      </c>
+      <c r="U379" t="n">
+        <v>642</v>
+      </c>
+      <c r="V379" t="n">
+        <v>1310.25</v>
+      </c>
+      <c r="W379" t="n">
+        <v>810</v>
+      </c>
+      <c r="X379" t="n">
+        <v>650</v>
+      </c>
+      <c r="Y379" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Z379" t="n">
+        <v>694</v>
+      </c>
+      <c r="AA379" t="n">
+        <v>595</v>
+      </c>
+      <c r="AB379" t="n">
+        <v>1394</v>
+      </c>
+      <c r="AC379" t="n">
+        <v>706</v>
+      </c>
+      <c r="AD379" t="n">
+        <v>580</v>
+      </c>
+      <c r="AE379" t="n">
+        <v>1284</v>
+      </c>
+      <c r="AF379" t="n">
+        <v>807.98</v>
+      </c>
+      <c r="AG379" t="n">
+        <v>818</v>
+      </c>
+      <c r="AH379" t="inlineStr"/>
+      <c r="AI379" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI379"/>
+  <dimension ref="A1:AI380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38947,6 +38947,109 @@
       <c r="AH379" t="inlineStr"/>
       <c r="AI379" t="inlineStr"/>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>746.97</v>
+      </c>
+      <c r="C380" t="n">
+        <v>831</v>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="n">
+        <v>670</v>
+      </c>
+      <c r="F380" t="n">
+        <v>1265</v>
+      </c>
+      <c r="G380" t="n">
+        <v>621.25</v>
+      </c>
+      <c r="H380" t="n">
+        <v>662</v>
+      </c>
+      <c r="I380" t="n">
+        <v>541.75</v>
+      </c>
+      <c r="J380" t="n">
+        <v>618</v>
+      </c>
+      <c r="K380" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L380" t="n">
+        <v>814</v>
+      </c>
+      <c r="M380" t="n">
+        <v>1375</v>
+      </c>
+      <c r="N380" t="n">
+        <v>807</v>
+      </c>
+      <c r="O380" t="n">
+        <v>655</v>
+      </c>
+      <c r="P380" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>871</v>
+      </c>
+      <c r="R380" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="S380" t="n">
+        <v>1242</v>
+      </c>
+      <c r="T380" t="n">
+        <v>855.25</v>
+      </c>
+      <c r="U380" t="n">
+        <v>643</v>
+      </c>
+      <c r="V380" t="n">
+        <v>1322.75</v>
+      </c>
+      <c r="W380" t="n">
+        <v>807</v>
+      </c>
+      <c r="X380" t="n">
+        <v>655</v>
+      </c>
+      <c r="Y380" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Z380" t="n">
+        <v>695</v>
+      </c>
+      <c r="AA380" t="n">
+        <v>605</v>
+      </c>
+      <c r="AB380" t="n">
+        <v>1396</v>
+      </c>
+      <c r="AC380" t="n">
+        <v>704</v>
+      </c>
+      <c r="AD380" t="n">
+        <v>579</v>
+      </c>
+      <c r="AE380" t="n">
+        <v>1291</v>
+      </c>
+      <c r="AF380" t="n">
+        <v>807.1</v>
+      </c>
+      <c r="AG380" t="n">
+        <v>817</v>
+      </c>
+      <c r="AH380" t="inlineStr"/>
+      <c r="AI380" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI380"/>
+  <dimension ref="A1:AI381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39050,6 +39050,109 @@
       <c r="AH380" t="inlineStr"/>
       <c r="AI380" t="inlineStr"/>
     </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>748.62</v>
+      </c>
+      <c r="C381" t="n">
+        <v>835</v>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="n">
+        <v>680</v>
+      </c>
+      <c r="F381" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G381" t="n">
+        <v>624.25</v>
+      </c>
+      <c r="H381" t="n">
+        <v>665</v>
+      </c>
+      <c r="I381" t="n">
+        <v>518</v>
+      </c>
+      <c r="J381" t="n">
+        <v>591</v>
+      </c>
+      <c r="K381" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L381" t="n">
+        <v>816</v>
+      </c>
+      <c r="M381" t="n">
+        <v>1379</v>
+      </c>
+      <c r="N381" t="n">
+        <v>815</v>
+      </c>
+      <c r="O381" t="n">
+        <v>660</v>
+      </c>
+      <c r="P381" t="n">
+        <v>1285</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>835</v>
+      </c>
+      <c r="R381" t="n">
+        <v>688</v>
+      </c>
+      <c r="S381" t="n">
+        <v>1225</v>
+      </c>
+      <c r="T381" t="n">
+        <v>855.5</v>
+      </c>
+      <c r="U381" t="n">
+        <v>645</v>
+      </c>
+      <c r="V381" t="n">
+        <v>1282.25</v>
+      </c>
+      <c r="W381" t="n">
+        <v>815</v>
+      </c>
+      <c r="X381" t="n">
+        <v>660</v>
+      </c>
+      <c r="Y381" t="n">
+        <v>1290</v>
+      </c>
+      <c r="Z381" t="n">
+        <v>700</v>
+      </c>
+      <c r="AA381" t="n">
+        <v>611</v>
+      </c>
+      <c r="AB381" t="n">
+        <v>1363</v>
+      </c>
+      <c r="AC381" t="n">
+        <v>713</v>
+      </c>
+      <c r="AD381" t="n">
+        <v>582</v>
+      </c>
+      <c r="AE381" t="n">
+        <v>1297</v>
+      </c>
+      <c r="AF381" t="n">
+        <v>815.03</v>
+      </c>
+      <c r="AG381" t="n">
+        <v>825</v>
+      </c>
+      <c r="AH381" t="inlineStr"/>
+      <c r="AI381" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
